--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -772,7 +772,7 @@
         <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1739,10 +1739,10 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="G8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="G11" t="n">
         <v>3.65</v>
@@ -2518,7 +2518,7 @@
         <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
         <v>3.9</v>
@@ -2712,7 +2712,7 @@
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
         <v>2.72</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
         <v>3.65</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>1.65</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>1.98</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
         <v>4.2</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>1.01</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G20" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H20" t="n">
         <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
@@ -4282,7 +4282,7 @@
         <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4455,10 +4455,10 @@
         <v>5.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
         <v>1.67</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>1.01</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G23" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
         <v>1.66</v>
       </c>
       <c r="H25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
         <v>6.2</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
         <v>4.7</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
         <v>1.73</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G27" t="n">
         <v>1.55</v>
@@ -5616,13 +5616,13 @@
         <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
         <v>4.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
         <v>5.1</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -5995,52 +5995,52 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="G29" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I29" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S29" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
         <v>1.65</v>
       </c>
       <c r="U29" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,85 +6049,85 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF29" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AG29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>30</v>
       </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>60</v>
-      </c>
       <c r="AK29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL29" t="n">
         <v>32</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
       </c>
       <c r="AM29" t="n">
         <v>100</v>
       </c>
       <c r="AN29" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AP29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV29" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>11</v>
       </c>
       <c r="AW29" t="n">
         <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
@@ -6139,26 +6139,26 @@
         <v>28</v>
       </c>
       <c r="BB29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD29" t="n">
         <v>25</v>
       </c>
       <c r="BE29" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BF29" t="n">
         <v>12.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G30" t="n">
         <v>2.66</v>
@@ -6198,7 +6198,7 @@
         <v>2.82</v>
       </c>
       <c r="I30" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
@@ -6222,7 +6222,7 @@
         <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>
@@ -6383,170 +6383,170 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G31" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="n">
         <v>3.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="O31" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P31" t="n">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 01:09:37</t>
+          <t>2026-05-10 03:41:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>440</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>660</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.02</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>770</v>
       </c>
       <c r="J7" t="n">
         <v>6.2</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -1930,13 +1930,13 @@
         <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G11" t="n">
         <v>3.65</v>
       </c>
       <c r="H11" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="I11" t="n">
         <v>2.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
         <v>3.9</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -2897,13 +2897,13 @@
         <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I13" t="n">
         <v>3.25</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
         <v>3.4</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlitiki Enosi Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
         <v>3.65</v>
       </c>
       <c r="J15" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="H18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
         <v>950</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
         <v>950</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G20" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
         <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
         <v>4.3</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
         <v>2.84</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J21" t="n">
         <v>2.48</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G23" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.65</v>
       </c>
       <c r="G25" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I25" t="n">
         <v>6.2</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K25" t="n">
         <v>4.7</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>1.88</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>3.95</v>
@@ -5446,7 +5446,7 @@
         <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5610,19 @@
         <v>1.54</v>
       </c>
       <c r="G27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K27" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>3.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
@@ -5816,7 +5816,7 @@
         <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>2.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="G29" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I29" t="n">
         <v>3.2</v>
       </c>
-      <c r="I29" t="n">
-        <v>3.3</v>
-      </c>
       <c r="J29" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6019,22 +6019,22 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T29" t="n">
         <v>1.65</v>
@@ -6052,82 +6052,82 @@
         <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB29" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>34</v>
       </c>
-      <c r="AF29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>30</v>
-      </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AM29" t="n">
         <v>100</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP29" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT29" t="n">
         <v>11.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
@@ -6139,10 +6139,10 @@
         <v>28</v>
       </c>
       <c r="BB29" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC29" t="n">
         <v>21</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>19.5</v>
       </c>
       <c r="BD29" t="n">
         <v>25</v>
@@ -6151,14 +6151,14 @@
         <v>32</v>
       </c>
       <c r="BF29" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G30" t="n">
         <v>2.66</v>
@@ -6198,7 +6198,7 @@
         <v>2.82</v>
       </c>
       <c r="I30" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>
@@ -6386,25 +6386,25 @@
         <v>2.38</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="H31" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I31" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="J31" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L31" t="n">
         <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
         <v>2.94</v>
@@ -6413,37 +6413,37 @@
         <v>1.45</v>
       </c>
       <c r="P31" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="U31" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="X31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA31" t="n">
         <v>85</v>
@@ -6452,10 +6452,10 @@
         <v>9.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>60</v>
@@ -6488,16 +6488,16 @@
         <v>36</v>
       </c>
       <c r="AO31" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP31" t="n">
         <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>4.9</v>
@@ -6509,16 +6509,16 @@
         <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.8</v>
+        <v>36</v>
       </c>
       <c r="AX31" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
         <v>4.2</v>
@@ -6546,7 +6546,201 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 03:41:43</t>
+          <t>2026-05-10 06:12:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medel</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Internacional de Bogot</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K32" t="n">
+        <v>950</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-10 06:12:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.01</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I8" t="n">
         <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>3.7</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.86</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
         <v>2.44</v>
@@ -2515,7 +2515,7 @@
         <v>2.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
         <v>3.75</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
         <v>1.97</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
         <v>2.28</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
         <v>1.84</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I13" t="n">
         <v>3.25</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlitiki Enosi Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -3464,32 +3464,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.1</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I17" t="n">
         <v>5.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
         <v>4.7</v>
@@ -3700,7 +3700,7 @@
         <v>2.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,61 +4046,61 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>910</v>
+        <v>1.77</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>850</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>1.77</v>
+        <v>2.64</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>2.54</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,33 +4429,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>1000</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="Y22" t="n">
         <v>1000</v>
       </c>
-      <c r="J22" t="n">
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
         <v>1.01</v>
       </c>
-      <c r="K22" t="n">
-        <v>950</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="AQ22" t="n">
         <v>1.01</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,28 +4822,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Plzen</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
         <v>4.4</v>
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,61 +5016,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="G24" t="n">
-        <v>2.48</v>
+        <v>1.67</v>
       </c>
       <c r="H24" t="n">
-        <v>2.94</v>
+        <v>5.6</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
         <v>4.4</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.46</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,123 +5079,123 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="G25" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -5404,31 +5404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="G26" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="G27" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>English Sky Bet Championship</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,66 +5787,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.86</v>
+        <v>2.46</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H28" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,33 +5981,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="G29" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="H29" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
         <v>3.7</v>
@@ -6019,28 +6019,28 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="U29" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,123 +6049,123 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD29" t="n">
         <v>13</v>
       </c>
-      <c r="AC29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>14</v>
-      </c>
       <c r="AE29" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AF29" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ29" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM29" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AP29" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW29" t="n">
         <v>19.5</v>
       </c>
-      <c r="AS29" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>20</v>
-      </c>
       <c r="AX29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BB29" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BC29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG29" t="n">
         <v>21</v>
       </c>
-      <c r="BD29" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>20</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="G30" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="H30" t="n">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
       <c r="I30" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.86</v>
+        <v>2.34</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,378 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atletico Nacional Medel</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Internacional de Bogot</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="K31" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 06:12:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>20:20:00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medel</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Internacional de Bogot</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K32" t="n">
-        <v>950</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-05-10 06:12:19</t>
+          <t>2026-05-10 08:41:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>2.5</v>
       </c>
       <c r="G3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H3" t="n">
         <v>2.94</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.76</v>
       </c>
       <c r="I3" t="n">
         <v>3.6</v>
@@ -966,16 +966,16 @@
         <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
@@ -993,16 +993,16 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.44</v>
       </c>
       <c r="I4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
@@ -1169,7 +1169,7 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.34</v>
@@ -1190,7 +1190,7 @@
         <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V4" t="n">
         <v>3</v>
@@ -1220,13 +1220,13 @@
         <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AF4" t="n">
         <v>110</v>
       </c>
       <c r="AG4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AH4" t="n">
         <v>32</v>
@@ -1277,38 +1277,38 @@
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA4" t="n">
         <v>40</v>
       </c>
       <c r="BB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC4" t="n">
-        <v>10</v>
-      </c>
       <c r="BD4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE4" t="n">
         <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
         <v>7.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
         <v>34</v>
@@ -1405,34 +1405,34 @@
         <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
         <v>60</v>
@@ -1441,10 +1441,10 @@
         <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
         <v>9.199999999999999</v>
@@ -1453,10 +1453,10 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1468,7 +1468,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1480,29 +1480,29 @@
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -1545,158 +1545,158 @@
         <v>660</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -2106,25 +2106,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Metalist 1925</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Kryvbas Krivyi Rih</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>550</v>
+        <v>420</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>660</v>
+        <v>750</v>
       </c>
       <c r="J9" t="n">
         <v>1.02</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -2300,25 +2300,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kryvbas Krivyi Rih</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>550</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>750</v>
+        <v>660</v>
       </c>
       <c r="J10" t="n">
         <v>1.02</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H11" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I11" t="n">
         <v>2.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
         <v>3.75</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
         <v>2.28</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
         <v>3.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>1.84</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athlitiki Enosi Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -3270,50 +3270,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.3</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,61 +3852,61 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>370</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I18" t="n">
-        <v>430</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,61 +4046,61 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>1.77</v>
+        <v>370</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>430</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,116 +4109,116 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>2.34</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
         <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
         <v>50</v>
       </c>
       <c r="AA24" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
         <v>10.5</v>
@@ -5103,7 +5103,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
         <v>10.5</v>
@@ -5115,10 +5115,10 @@
         <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL24" t="n">
         <v>34</v>
@@ -5142,7 +5142,7 @@
         <v>34</v>
       </c>
       <c r="AS24" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AT24" t="n">
         <v>8.6</v>
@@ -5184,11 +5184,11 @@
         <v>7</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
         <v>2.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>St Mirren</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U28" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.38</v>
-      </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y28" t="n">
-        <v>15</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB28" t="n">
-        <v>13</v>
+        <v>950</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>950</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="AE28" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AH28" t="n">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
         <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
         <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN28" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AP28" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>19.5</v>
+        <v>8</v>
       </c>
       <c r="AS28" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AY28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE28" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BF28" t="n">
         <v>14</v>
       </c>
-      <c r="BA28" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>32</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG28" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,66 +5981,66 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="G29" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="I29" t="n">
-        <v>2.96</v>
+        <v>4.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="U29" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,123 +6049,123 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AA29" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AB29" t="n">
         <v>12.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG29" t="n">
         <v>13</v>
       </c>
-      <c r="AE29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>21</v>
       </c>
-      <c r="AG29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>17</v>
-      </c>
       <c r="AI29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL29" t="n">
         <v>40</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>38</v>
-      </c>
       <c r="AM29" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN29" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP29" t="n">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>17.5</v>
+        <v>3.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AT29" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY29" t="n">
-        <v>10.5</v>
+        <v>3.2</v>
       </c>
       <c r="AZ29" t="n">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="BB29" t="n">
-        <v>32</v>
+        <v>3.7</v>
       </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>3.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>23</v>
+        <v>3.85</v>
       </c>
       <c r="BE29" t="n">
-        <v>34</v>
+        <v>4.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,378 +6175,960 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Dundee Utd</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="G30" t="n">
-        <v>2.52</v>
+        <v>1.86</v>
       </c>
       <c r="H30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT30" t="n">
         <v>3.55</v>
       </c>
-      <c r="I30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="AU30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD30" t="n">
         <v>4.3</v>
       </c>
-      <c r="T30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X30" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB30" t="n">
+      <c r="BE30" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BF30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.6</v>
       </c>
-      <c r="BD30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 08:41:24</t>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>English Sky Bet Championship</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-05-10 11:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-10 11:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-05-10 11:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Atletico Nacional Medel</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Internacional de Bogot</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F34" t="n">
         <v>1.04</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G34" t="n">
         <v>1000</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H34" t="n">
         <v>1.04</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I34" t="n">
         <v>1000</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J34" t="n">
         <v>1.01</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K34" t="n">
         <v>950</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q34" t="n">
         <v>1.01</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-05-10 08:41:24</t>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-10 11:07:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>2.88</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="n">
         <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -993,13 +993,13 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
         <v>1.53</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z4" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z4" t="n">
-        <v>8</v>
-      </c>
       <c r="AA4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AF4" t="n">
         <v>110</v>
       </c>
       <c r="AG4" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="AK4" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AL4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="AN4" t="n">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="AO4" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AX4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB4" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>11</v>
-      </c>
       <c r="BC4" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1366,13 +1366,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1396,7 +1396,7 @@
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
         <v>34</v>
@@ -1405,7 +1405,7 @@
         <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
         <v>8.800000000000001</v>
@@ -1429,7 +1429,7 @@
         <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1453,10 +1453,10 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1468,7 +1468,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1480,29 +1480,29 @@
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G6" t="n">
         <v>440</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I6" t="n">
         <v>660</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Indian Super League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mohun Bagan Super Giants</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.33</v>
       </c>
-      <c r="H7" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" t="n">
-        <v>770</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Indian Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Mohun Bagan Super Giants</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kryvbas Krivyi Rih</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G9" t="n">
-        <v>420</v>
+        <v>1.33</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Metalist 1925</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
-        <v>550</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>660</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Slovacko</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Banik Ostrava</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.88</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>550</v>
       </c>
       <c r="H11" t="n">
-        <v>2.42</v>
+        <v>1.2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>660</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,184 +2683,184 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mlada Boleslav</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dukla Prague</t>
+          <t>Kryvbas Krivyi Rih</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>420</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>750</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zlin</t>
+          <t>Slovacko</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Banik Ostrava</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>950</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.68</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Mlada Boleslav</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Dukla Prague</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Zlin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlitiki Enosi Larissa</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="G15" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="K15" t="n">
         <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.66</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="H16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.35</v>
       </c>
-      <c r="I16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
         <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>1.78</v>
+        <v>2.62</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BC17" t="n">
         <v>1.57</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>2.22</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>10</v>
       </c>
-      <c r="AO18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>32</v>
+        <v>1.55</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>1.59</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>1.51</v>
       </c>
       <c r="BD18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BF18" t="n">
         <v>21</v>
       </c>
-      <c r="BE18" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>9</v>
-      </c>
       <c r="BG18" t="n">
-        <v>32</v>
+        <v>1.59</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="G19" t="n">
-        <v>370</v>
+        <v>1.78</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>430</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,55 +4235,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="G20" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="I20" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.54</v>
       </c>
-      <c r="K20" t="n">
-        <v>950</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.84</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4291,10 +4291,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,116 +4303,116 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -4429,33 +4429,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="H21" t="n">
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Plzen</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74</v>
+        <v>1.81</v>
       </c>
       <c r="H22" t="n">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,66 +5011,66 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>6.2</v>
+        <v>100</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.24</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.22</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,123 +5079,123 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,33 +5205,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="G25" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="K25" t="n">
         <v>4.6</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,42 +5399,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.54</v>
+        <v>2.46</v>
       </c>
       <c r="G26" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6</v>
+        <v>2.84</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="J26" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5455,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,123 +5467,123 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,66 +5593,66 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P27" t="n">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5661,123 +5661,123 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St Mirren</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="H28" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,42 +5981,42 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="G29" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="K29" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>3.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6049,123 +6049,123 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,42 +6175,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dundee Utd</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="G30" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="H30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.6</v>
       </c>
-      <c r="I30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5</v>
-      </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6231,10 +6231,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6243,116 +6243,116 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6410,16 +6410,16 @@
         <v>4.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P31" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -6452,7 +6452,7 @@
         <v>12.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD31" t="n">
         <v>14</v>
@@ -6485,7 +6485,7 @@
         <v>100</v>
       </c>
       <c r="AN31" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6509,10 +6509,10 @@
         <v>7.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
@@ -6527,26 +6527,26 @@
         <v>28</v>
       </c>
       <c r="BB31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
       </c>
       <c r="BD31" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
         <v>32</v>
       </c>
       <c r="BF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G32" t="n">
         <v>2.66</v>
       </c>
       <c r="H32" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I32" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>3.6</v>
@@ -6607,7 +6607,7 @@
         <v>1.29</v>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
         <v>1.87</v>
@@ -6637,7 +6637,7 @@
         <v>13</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="n">
         <v>50</v>
@@ -6667,13 +6667,13 @@
         <v>100</v>
       </c>
       <c r="AJ32" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK32" t="n">
         <v>29</v>
       </c>
       <c r="AL32" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
@@ -6682,10 +6682,10 @@
         <v>22</v>
       </c>
       <c r="AO32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ32" t="n">
         <v>11.5</v>
@@ -6697,16 +6697,16 @@
         <v>25</v>
       </c>
       <c r="AT32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU32" t="n">
         <v>7.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX32" t="n">
         <v>15</v>
@@ -6724,7 +6724,7 @@
         <v>32</v>
       </c>
       <c r="BC32" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD32" t="n">
         <v>23</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G33" t="n">
         <v>2.52</v>
       </c>
       <c r="H33" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I33" t="n">
         <v>3.8</v>
@@ -6819,10 +6819,10 @@
         <v>1.93</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X33" t="n">
         <v>11.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J34" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 11:07:57</t>
+          <t>2026-05-10 13:31:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
         <v>2.78</v>
@@ -981,13 +981,13 @@
         <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
         <v>2.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
         <v>4.2</v>
@@ -996,125 +996,125 @@
         <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="I4" t="n">
         <v>1.41</v>
@@ -1160,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1184,22 +1184,22 @@
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>3.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
         <v>9</v>
@@ -1214,7 +1214,7 @@
         <v>32</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD4" t="n">
         <v>11.5</v>
@@ -1235,31 +1235,31 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="AK4" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AL4" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AM4" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AN4" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AO4" t="n">
         <v>7.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
         <v>9</v>
@@ -1268,7 +1268,7 @@
         <v>18.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1277,38 +1277,38 @@
         <v>12.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC4" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC4" t="n">
-        <v>6</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
         <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -1742,10 +1742,10 @@
         <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
@@ -1754,7 +1754,7 @@
         <v>2.28</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
         <v>1.45</v>
@@ -1763,10 +1763,10 @@
         <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1781,10 +1781,10 @@
         <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
@@ -1796,7 +1796,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1808,19 +1808,19 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.81</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
         <v>2.42</v>
@@ -1939,7 +1939,7 @@
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -2115,112 +2115,112 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="G9" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>770</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N9" t="n">
         <v>6.2</v>
       </c>
-      <c r="K9" t="n">
-        <v>26</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.56</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>440</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN9" t="n">
         <v>4</v>
       </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AP9" t="n">
         <v>1.03</v>
@@ -2235,10 +2235,10 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AV9" t="n">
         <v>1.03</v>
@@ -2247,10 +2247,10 @@
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>1.03</v>
@@ -2259,10 +2259,10 @@
         <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BD9" t="n">
         <v>1.03</v>
@@ -2271,14 +2271,14 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -2363,10 +2363,10 @@
         <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>38</v>
@@ -2375,10 +2375,10 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
@@ -2387,10 +2387,10 @@
         <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>26</v>
@@ -2423,10 +2423,10 @@
         <v>4.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AT10" t="n">
         <v>3.8</v>
@@ -2438,7 +2438,7 @@
         <v>2.36</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AX10" t="n">
         <v>4.6</v>
@@ -2450,29 +2450,29 @@
         <v>2.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF10" t="n">
         <v>5.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Metalist 1925</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Kryvbas Krivyi Rih</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>420</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>750</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.2</v>
       </c>
-      <c r="G11" t="n">
-        <v>550</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="P11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.2</v>
       </c>
-      <c r="I11" t="n">
-        <v>660</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.01</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kryvbas Krivyi Rih</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>420</v>
+        <v>550</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>750</v>
+        <v>660</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1.01</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H13" t="n">
         <v>2.44</v>
@@ -2903,13 +2903,13 @@
         <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -2924,16 +2924,16 @@
         <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U13" t="n">
         <v>2.16</v>
@@ -2945,7 +2945,7 @@
         <v>1.45</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -2960,7 +2960,7 @@
         <v>15.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
         <v>14.5</v>
@@ -2972,10 +2972,10 @@
         <v>26</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
         <v>48</v>
@@ -2984,7 +2984,7 @@
         <v>60</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
@@ -2999,16 +2999,16 @@
         <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
         <v>9.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
         <v>10.5</v>
@@ -3020,31 +3020,31 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3127,10 +3127,10 @@
         <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
         <v>1.34</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -3282,28 +3282,28 @@
         <v>2.86</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>2.74</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.47</v>
@@ -3315,134 +3315,134 @@
         <v>2.36</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
         <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X15" t="n">
         <v>11.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
         <v>11</v>
       </c>
-      <c r="Z15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AW15" t="n">
-        <v>1.95</v>
+        <v>5.7</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.95</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.95</v>
+        <v>5.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.95</v>
+        <v>5.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.95</v>
+        <v>5.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.95</v>
+        <v>5.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.95</v>
+        <v>5.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.95</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.95</v>
+        <v>5.7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="G16" t="n">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AA16" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="AB16" t="n">
         <v>8.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
         <v>11</v>
       </c>
-      <c r="AG16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF16" t="n">
         <v>21</v>
       </c>
-      <c r="AO16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -3658,46 +3658,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="H17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J17" t="n">
         <v>3.35</v>
       </c>
-      <c r="I17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>1.76</v>
+        <v>2.98</v>
       </c>
       <c r="O17" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
         <v>2.2</v>
@@ -3706,131 +3706,131 @@
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" t="n">
         <v>9</v>
       </c>
-      <c r="AD17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB17" t="n">
         <v>18</v>
       </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.57</v>
+        <v>5.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.64</v>
+        <v>5.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.64</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.64</v>
+        <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.64</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlitiki Enosi Larissa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
         <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC18" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC18" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO18" t="n">
         <v>65</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX18" t="n">
         <v>11</v>
       </c>
-      <c r="AW18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.59</v>
+        <v>4.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.51</v>
+        <v>4.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.59</v>
+        <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.59</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.59</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -4073,159 +4073,159 @@
         <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
         <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="I20" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P20" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK20" t="n">
         <v>36</v>
       </c>
-      <c r="AE20" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="AL20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>410</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AR20" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>15</v>
+        <v>3.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>3.95</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>370</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I21" t="n">
-        <v>430</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="G22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.81</v>
       </c>
-      <c r="H22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
       <c r="X22" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z22" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB22" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>65</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>2.12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>2.1</v>
       </c>
       <c r="AR22" t="n">
-        <v>32</v>
+        <v>2.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>40</v>
+        <v>2.26</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="AV22" t="n">
-        <v>16.5</v>
+        <v>2.1</v>
       </c>
       <c r="AW22" t="n">
-        <v>29</v>
+        <v>2.22</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.800000000000001</v>
+        <v>2.06</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>2.12</v>
       </c>
       <c r="BA22" t="n">
-        <v>32</v>
+        <v>2.24</v>
       </c>
       <c r="BB22" t="n">
-        <v>16</v>
+        <v>2.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>15</v>
+        <v>2.14</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>2.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>38</v>
+        <v>2.3</v>
       </c>
       <c r="BF22" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>32</v>
+        <v>2.3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>1.81</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Beer Sheva</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>1.8</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="I24" t="n">
-        <v>100</v>
+        <v>8.4</v>
       </c>
       <c r="J24" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.56</v>
+        <v>370</v>
       </c>
       <c r="H25" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3.15</v>
+        <v>430</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Czech 1 Liga</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,60 +5399,60 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sparta Prague</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Plzen</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>2.7</v>
+        <v>910</v>
       </c>
       <c r="H26" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>3.15</v>
+        <v>850</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P26" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5461,10 +5461,10 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5521,52 +5521,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="G27" t="n">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="I27" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X27" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP27" t="n">
         <v>4.2</v>
       </c>
-      <c r="K27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>17</v>
-      </c>
       <c r="AQ27" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>42</v>
+        <v>5.4</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.6</v>
+        <v>3.55</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>32</v>
+        <v>5.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="BA27" t="n">
-        <v>32</v>
+        <v>5.4</v>
       </c>
       <c r="BB27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF27" t="n">
         <v>14</v>
       </c>
-      <c r="BC27" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>7</v>
-      </c>
       <c r="BG27" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Hapoel Beer Sheva</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>1.96</v>
+        <v>100</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>4.6</v>
+        <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.62</v>
+        <v>1.17</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>South African Premier Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>TS Galaxy FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.54</v>
+        <v>7.2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.55</v>
+        <v>14.5</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>1.38</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>1.47</v>
       </c>
       <c r="J29" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Czech 1 Liga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sparta Prague</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.86</v>
       </c>
-      <c r="G30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="R30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS30" t="n">
         <v>4.7</v>
       </c>
-      <c r="J30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K30" t="n">
+      <c r="AT30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA30" t="n">
         <v>4.6</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,184 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="G31" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I31" t="n">
         <v>3.15</v>
       </c>
-      <c r="I31" t="n">
-        <v>3.2</v>
-      </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M31" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="R31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T31" t="n">
         <v>1.45</v>
       </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.68</v>
-      </c>
       <c r="U31" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X31" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD31" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AE31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG31" t="n">
         <v>14.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>12</v>
       </c>
       <c r="AH31" t="n">
         <v>16</v>
       </c>
       <c r="AI31" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AJ31" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK31" t="n">
         <v>25</v>
       </c>
       <c r="AL31" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM31" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AN31" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AP31" t="n">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="AR31" t="n">
         <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>28</v>
+        <v>4.7</v>
       </c>
       <c r="AT31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV31" t="n">
         <v>11</v>
       </c>
-      <c r="AU31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>12</v>
-      </c>
       <c r="AW31" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AY31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ31" t="n">
-        <v>14</v>
-      </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>4.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BF31" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG31" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="G32" t="n">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="H32" t="n">
-        <v>2.82</v>
+        <v>5.5</v>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O32" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U32" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="X32" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Z32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>20</v>
       </c>
-      <c r="AA32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE32" t="n">
+      <c r="AR32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG32" t="n">
         <v>34</v>
       </c>
-      <c r="AF32" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>21</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,378 +6757,1542 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="G33" t="n">
-        <v>2.52</v>
+        <v>1.96</v>
       </c>
       <c r="H33" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>2.94</v>
+        <v>2.32</v>
       </c>
       <c r="O33" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="R33" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>1.62</v>
       </c>
       <c r="T33" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="U33" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W33" t="n">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM33" t="n">
         <v>85</v>
       </c>
-      <c r="AB33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>160</v>
-      </c>
       <c r="AN33" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>9</v>
+        <v>1.18</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.800000000000001</v>
+        <v>1.18</v>
       </c>
       <c r="AR33" t="n">
-        <v>18</v>
+        <v>1.15</v>
       </c>
       <c r="AS33" t="n">
-        <v>5</v>
+        <v>1.18</v>
       </c>
       <c r="AT33" t="n">
-        <v>7.4</v>
+        <v>1.18</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.4</v>
+        <v>1.18</v>
       </c>
       <c r="AV33" t="n">
-        <v>11.5</v>
+        <v>1.12</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.9</v>
+        <v>1.18</v>
       </c>
       <c r="AX33" t="n">
-        <v>11</v>
+        <v>1.18</v>
       </c>
       <c r="AY33" t="n">
-        <v>10</v>
+        <v>1.18</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.3</v>
+        <v>1.18</v>
       </c>
       <c r="BA33" t="n">
-        <v>5</v>
+        <v>1.18</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.7</v>
+        <v>1.18</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.7</v>
+        <v>1.12</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.9</v>
+        <v>1.14</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.2</v>
+        <v>1.16</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.7</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
-        <v>5</v>
+        <v>1.18</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 13:31:53</t>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Swiss Super League</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Luzern</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FC Zurich</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X34" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-10 15:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Swiss Super League</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Lausanne</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="X35" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-05-10 15:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>English Sky Bet Championship</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-05-10 15:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Calcio Avellino SSD</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-05-10 15:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-05-10 15:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-05-10 15:51:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Atletico Nacional Medel</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Internacional de Bogot</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F40" t="n">
         <v>1.5</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G40" t="n">
         <v>1.66</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H40" t="n">
         <v>4.5</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I40" t="n">
         <v>9.4</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J40" t="n">
         <v>3.75</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K40" t="n">
         <v>4.9</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q40" t="n">
         <v>1.69</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-05-10 13:31:53</t>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-05-10 15:51:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH40"/>
+  <dimension ref="A1:BH44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -772,7 +772,7 @@
         <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -963,7 +963,7 @@
         <v>3.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
         <v>3.4</v>
@@ -975,7 +975,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
@@ -984,22 +984,22 @@
         <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
         <v>1.93</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
         <v>1.55</v>
@@ -1050,7 +1050,7 @@
         <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
         <v>36</v>
@@ -1065,10 +1065,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1080,41 +1080,41 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
         <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G4" t="n">
         <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1175,31 +1175,31 @@
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V4" t="n">
         <v>3.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>9</v>
@@ -1211,43 +1211,43 @@
         <v>11</v>
       </c>
       <c r="AB4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>16</v>
       </c>
       <c r="AF4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AK4" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AL4" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AM4" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AN4" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AO4" t="n">
         <v>7.4</v>
@@ -1256,19 +1256,19 @@
         <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4" t="n">
         <v>18.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1277,38 +1277,38 @@
         <v>12.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1366,13 +1366,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1402,7 +1402,7 @@
         <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
         <v>8.4</v>
@@ -1417,7 +1417,7 @@
         <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
@@ -1426,25 +1426,25 @@
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN5" t="n">
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
         <v>9.199999999999999</v>
@@ -1453,10 +1453,10 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1468,7 +1468,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1480,29 +1480,29 @@
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -1745,13 +1745,13 @@
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O7" t="n">
         <v>1.62</v>
@@ -1763,16 +1763,16 @@
         <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
         <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V7" t="n">
         <v>1.6</v>
@@ -1790,7 +1790,7 @@
         <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -1799,98 +1799,98 @@
         <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
         <v>70</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.48</v>
+        <v>5.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.56</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="BB7" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="BD7" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="BE7" t="n">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="BF7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.19</v>
       </c>
       <c r="G9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="H9" t="n">
         <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="K9" t="n">
         <v>9</v>
@@ -2148,13 +2148,13 @@
         <v>2.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
         <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
         <v>2.26</v>
@@ -2163,7 +2163,7 @@
         <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
         <v>5.5</v>
@@ -2223,16 +2223,16 @@
         <v>610</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2241,10 +2241,10 @@
         <v>13.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
         <v>6.2</v>
@@ -2253,10 +2253,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
         <v>6.4</v>
@@ -2265,20 +2265,20 @@
         <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF9" t="n">
         <v>2.76</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>2.1</v>
@@ -2321,7 +2321,7 @@
         <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>3.65</v>
@@ -2357,7 +2357,7 @@
         <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
         <v>1.9</v>
@@ -2369,7 +2369,7 @@
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2381,10 +2381,10 @@
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2396,7 +2396,7 @@
         <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
         <v>27</v>
@@ -2414,65 +2414,65 @@
         <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AS10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD10" t="n">
         <v>1.45</v>
       </c>
-      <c r="AT10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BE10" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
         <v>1.2</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -2891,52 +2891,52 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
         <v>2.6</v>
       </c>
       <c r="J13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.35</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
         <v>1.62</v>
@@ -2948,19 +2948,19 @@
         <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
         <v>46</v>
       </c>
       <c r="AB13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>14.5</v>
@@ -2969,7 +2969,7 @@
         <v>29</v>
       </c>
       <c r="AF13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -2993,22 +2993,22 @@
         <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AO13" t="n">
         <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ13" t="n">
         <v>9.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>10.5</v>
@@ -3020,31 +3020,31 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX13" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX13" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC13" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H14" t="n">
         <v>3.45</v>
@@ -3100,10 +3100,10 @@
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3136,7 +3136,7 @@
         <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X14" t="n">
         <v>16.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G15" t="n">
         <v>3.25</v>
@@ -3294,7 +3294,7 @@
         <v>2.74</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.46</v>
@@ -3303,7 +3303,7 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
         <v>1.47</v>
@@ -3321,28 +3321,28 @@
         <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
         <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
         <v>1.45</v>
       </c>
       <c r="X15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
         <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB15" t="n">
         <v>970</v>
@@ -3351,7 +3351,7 @@
         <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>46</v>
@@ -3387,16 +3387,16 @@
         <v>48</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ15" t="n">
         <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT15" t="n">
         <v>8</v>
@@ -3408,41 +3408,41 @@
         <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF15" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W18" t="n">
         <v>1.67</v>
@@ -3969,7 +3969,7 @@
         <v>65</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
         <v>8.800000000000001</v>
@@ -3999,7 +3999,7 @@
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>4.8</v>
@@ -4011,7 +4011,7 @@
         <v>4.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>34</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
         <v>4.9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
@@ -4094,7 +4094,7 @@
         <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T19" t="n">
         <v>1.71</v>
@@ -4148,7 +4148,7 @@
         <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
         <v>2.4</v>
@@ -4264,7 +4264,7 @@
         <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.42</v>
@@ -4357,10 +4357,10 @@
         <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AR20" t="n">
         <v>3.9</v>
@@ -4369,25 +4369,25 @@
         <v>4.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>2.96</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="AW20" t="n">
         <v>4.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>3.35</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA20" t="n">
         <v>4.2</v>
@@ -4405,14 +4405,14 @@
         <v>4.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>19</v>
+        <v>3.9</v>
       </c>
       <c r="BG20" t="n">
         <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4461,31 +4461,31 @@
         <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P21" t="n">
         <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U21" t="n">
         <v>2.2</v>
@@ -4497,7 +4497,7 @@
         <v>1.83</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
         <v>17.5</v>
@@ -4512,13 +4512,13 @@
         <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
         <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF21" t="n">
         <v>16.5</v>
@@ -4530,7 +4530,7 @@
         <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ21" t="n">
         <v>32</v>
@@ -4545,10 +4545,10 @@
         <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP21" t="n">
         <v>14</v>
@@ -4557,10 +4557,10 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT21" t="n">
         <v>9.199999999999999</v>
@@ -4572,7 +4572,7 @@
         <v>13.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4584,29 +4584,29 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF21" t="n">
         <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G22" t="n">
         <v>2.2</v>
@@ -4646,37 +4646,37 @@
         <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O22" t="n">
         <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
         <v>1.47</v>
@@ -4688,7 +4688,7 @@
         <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
         <v>25</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G23" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
         <v>5.2</v>
@@ -4849,13 +4849,13 @@
         <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
         <v>1.27</v>
@@ -4864,16 +4864,16 @@
         <v>2.12</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.82</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.8</v>
       </c>
       <c r="U23" t="n">
         <v>2.14</v>
@@ -4885,7 +4885,7 @@
         <v>2.24</v>
       </c>
       <c r="X23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="n">
         <v>19.5</v>
@@ -4897,7 +4897,7 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>9.199999999999999</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>1.8</v>
+        <v>910</v>
       </c>
       <c r="H24" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>8.4</v>
+        <v>850</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.54</v>
+        <v>1.43</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>5.1</v>
+        <v>1.43</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
         <v>430</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5243,13 +5243,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O25" t="n">
         <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
         <v>1.18</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G26" t="n">
-        <v>910</v>
+        <v>1.8</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="I26" t="n">
-        <v>850</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>2.54</v>
       </c>
       <c r="O26" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.43</v>
+        <v>2.54</v>
       </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.43</v>
+        <v>5.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
         <v>2.28</v>
@@ -5619,16 +5619,16 @@
         <v>4.1</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
         <v>3.5</v>
@@ -5637,7 +5637,7 @@
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
         <v>2.02</v>
@@ -5646,7 +5646,7 @@
         <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="T27" t="n">
         <v>1.8</v>
@@ -5661,7 +5661,7 @@
         <v>1.78</v>
       </c>
       <c r="X27" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y27" t="n">
         <v>16.5</v>
@@ -5673,28 +5673,28 @@
         <v>95</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
         <v>9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE27" t="n">
         <v>50</v>
       </c>
       <c r="AF27" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AI27" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AJ27" t="n">
         <v>29</v>
@@ -5706,7 +5706,7 @@
         <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
         <v>23</v>
@@ -5715,62 +5715,62 @@
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF27" t="n">
         <v>14</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H28" t="n">
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K28" t="n">
         <v>950</v>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.17</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>5.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -6040,7 +6040,7 @@
         <v>2.28</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V29" t="n">
         <v>3.1</v>
@@ -6049,25 +6049,25 @@
         <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AA29" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AB29" t="n">
         <v>34</v>
       </c>
       <c r="AC29" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD29" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
         <v>3.85</v>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6392,10 +6392,10 @@
         <v>2.9</v>
       </c>
       <c r="I31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K31" t="n">
         <v>4.4</v>
@@ -6428,13 +6428,13 @@
         <v>1.45</v>
       </c>
       <c r="U31" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W31" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X31" t="n">
         <v>34</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6586,46 +6586,46 @@
         <v>5.5</v>
       </c>
       <c r="I32" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K32" t="n">
         <v>4.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
         <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="T32" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
         <v>2.46</v>
@@ -6676,7 +6676,7 @@
         <v>32</v>
       </c>
       <c r="AM32" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN32" t="n">
         <v>8.4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -6762,28 +6762,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1.88</v>
       </c>
       <c r="G33" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I33" t="n">
         <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
         <v>4.6</v>
@@ -6792,52 +6792,52 @@
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="O33" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="S33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="T33" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W33" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y33" t="n">
         <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC33" t="n">
         <v>1000</v>
@@ -6849,7 +6849,7 @@
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG33" t="n">
         <v>1000</v>
@@ -6864,77 +6864,77 @@
         <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM33" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.14</v>
+        <v>18</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.16</v>
+        <v>1.51</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -7007,10 +7007,10 @@
         <v>1.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V34" t="n">
         <v>1.2</v>
@@ -7046,7 +7046,7 @@
         <v>18</v>
       </c>
       <c r="AG34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH34" t="n">
         <v>20</v>
@@ -7076,13 +7076,13 @@
         <v>4.3</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR34" t="n">
         <v>4.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT34" t="n">
         <v>13</v>
@@ -7121,14 +7121,14 @@
         <v>4.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BG34" t="n">
         <v>24</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
@@ -7150,28 +7150,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>1.88</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H35" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
         <v>4.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K35" t="n">
         <v>4.6</v>
@@ -7180,25 +7180,25 @@
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="O35" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P35" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="R35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S35" t="n">
         <v>1.6</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.53</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7207,25 +7207,25 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W35" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="X35" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
         <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA35" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
         <v>1000</v>
@@ -7237,7 +7237,7 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
         <v>1000</v>
@@ -7252,84 +7252,84 @@
         <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL35" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM35" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AV35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BD35" t="n">
         <v>1.27</v>
       </c>
-      <c r="AW35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>18</v>
-      </c>
       <c r="BE35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG35" t="n">
         <v>1.32</v>
       </c>
-      <c r="BF35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="H36" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="I36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J36" t="n">
         <v>3.15</v>
       </c>
-      <c r="J36" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K36" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>4.3</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R36" t="n">
         <v>1.27</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W36" t="n">
         <v>1.43</v>
       </c>
-      <c r="S36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR36" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS36" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AT36" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AU36" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV36" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW36" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX36" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ36" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA36" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BB36" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,191 +7533,191 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>St Mirren</t>
         </is>
       </c>
       <c r="F37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U37" t="n">
         <v>2.18</v>
       </c>
-      <c r="G37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I37" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,191 +7727,191 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.58</v>
+        <v>1.93</v>
       </c>
       <c r="G38" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="I38" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K38" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M38" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V38" t="n">
         <v>1.29</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Z38" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AA38" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AB38" t="n">
         <v>12.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG38" t="n">
         <v>13</v>
       </c>
-      <c r="AE38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH38" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="AK38" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL38" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN38" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>17.5</v>
+        <v>4</v>
       </c>
       <c r="AS38" t="n">
-        <v>25</v>
+        <v>4.3</v>
       </c>
       <c r="AT38" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AU38" t="n">
         <v>7.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW38" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX38" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AY38" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ38" t="n">
         <v>14.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>24</v>
+        <v>4.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>32</v>
+        <v>3.9</v>
       </c>
       <c r="BC38" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="BE38" t="n">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BF38" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,378 +7921,1154 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Dundee Utd</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="G39" t="n">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="H39" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="J39" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="K39" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="R39" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
-        <v>4.3</v>
+        <v>2.76</v>
       </c>
       <c r="T39" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="U39" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="W39" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="X39" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="Y39" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AA39" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AB39" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC39" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD39" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE39" t="n">
         <v>60</v>
       </c>
       <c r="AF39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP39" t="n">
         <v>17</v>
       </c>
-      <c r="AG39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW39" t="n">
         <v>9</v>
       </c>
-      <c r="AQ39" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>5</v>
-      </c>
       <c r="AX39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BD39" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BG39" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 15:51:15</t>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>English Sky Bet Championship</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-05-10 18:08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Italian Serie B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Calcio Avellino SSD</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-05-10 18:08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-05-10 18:08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sao Bernardo</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-05-10 18:08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>20:20:00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Atletico Nacional Medel</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Internacional de Bogot</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F44" t="n">
         <v>1.5</v>
       </c>
-      <c r="G40" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K40" t="n">
+      <c r="G44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q44" t="n">
         <v>1.69</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="inlineStr">
-        <is>
-          <t>2026-05-10 15:51:15</t>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-05-10 18:08:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -1169,16 +1169,16 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
@@ -1187,10 +1187,10 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>3.25</v>
@@ -1199,10 +1199,10 @@
         <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
         <v>7.2</v>
@@ -1211,10 +1211,10 @@
         <v>11</v>
       </c>
       <c r="AB4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1223,7 +1223,7 @@
         <v>16</v>
       </c>
       <c r="AF4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
         <v>38</v>
@@ -1235,16 +1235,16 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="AK4" t="n">
         <v>220</v>
       </c>
       <c r="AL4" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AN4" t="n">
         <v>380</v>
@@ -1253,7 +1253,7 @@
         <v>7.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>7</v>
@@ -1262,7 +1262,7 @@
         <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
         <v>18.5</v>
@@ -1277,38 +1277,38 @@
         <v>12.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.4</v>
+        <v>95</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>95</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>95</v>
       </c>
       <c r="BG4" t="n">
         <v>6.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
         <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
         <v>1.93</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
         <v>1.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N7" t="n">
         <v>2.36</v>
@@ -1772,7 +1772,7 @@
         <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
         <v>1.6</v>
@@ -1826,7 +1826,7 @@
         <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
         <v>120</v>
@@ -1865,7 +1865,7 @@
         <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA7" t="n">
         <v>2.36</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.19</v>
       </c>
       <c r="G9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="H9" t="n">
         <v>19</v>
@@ -2127,7 +2127,7 @@
         <v>26</v>
       </c>
       <c r="J9" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="n">
         <v>9</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>420</v>
+        <v>990</v>
       </c>
       <c r="H11" t="n">
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>750</v>
+        <v>990</v>
       </c>
       <c r="J11" t="n">
         <v>1.04</v>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
         <v>1.2</v>
@@ -2542,13 +2542,13 @@
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="H12" t="n">
         <v>1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>660</v>
+        <v>870</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
         <v>6.2</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
         <v>2.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
         <v>2.32</v>
@@ -3100,7 +3100,7 @@
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
         <v>2.72</v>
@@ -3330,7 +3330,7 @@
         <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
         <v>11</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
         <v>15.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
         <v>180</v>
@@ -3784,7 +3784,7 @@
         <v>5.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
         <v>6.2</v>
@@ -3805,7 +3805,7 @@
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
@@ -3814,23 +3814,23 @@
         <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
         <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -3870,13 +3870,13 @@
         <v>3.35</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
         <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
         <v>1.42</v>
@@ -3909,7 +3909,7 @@
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
         <v>1.67</v>
@@ -3972,7 +3972,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>18</v>
@@ -3981,10 +3981,10 @@
         <v>4.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
         <v>11.5</v>
@@ -3996,7 +3996,7 @@
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
         <v>17</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -4112,13 +4112,13 @@
         <v>25</v>
       </c>
       <c r="Y19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z19" t="n">
         <v>55</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB19" t="n">
         <v>13</v>
@@ -4142,7 +4142,7 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
         <v>22</v>
@@ -4160,10 +4160,10 @@
         <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ19" t="n">
         <v>3.9</v>
@@ -4172,43 +4172,43 @@
         <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU19" t="n">
         <v>3.35</v>
       </c>
-      <c r="AU19" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AV19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW19" t="n">
         <v>4.3</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA19" t="n">
         <v>4.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF19" t="n">
         <v>6.2</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -4267,13 +4267,13 @@
         <v>3.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O20" t="n">
         <v>1.44</v>
@@ -4291,7 +4291,7 @@
         <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U20" t="n">
         <v>1.89</v>
@@ -4321,7 +4321,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE20" t="n">
         <v>70</v>
@@ -4342,7 +4342,7 @@
         <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
         <v>65</v>
@@ -4354,65 +4354,65 @@
         <v>32</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.96</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AW20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB20" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BC20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BD20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF20" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
         <v>3.5</v>
@@ -4494,7 +4494,7 @@
         <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
@@ -4670,7 +4670,7 @@
         <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
@@ -4685,7 +4685,7 @@
         <v>1.83</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
         <v>1.83</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="H23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I23" t="n">
         <v>4.9</v>
       </c>
-      <c r="I23" t="n">
-        <v>5.2</v>
-      </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.37</v>
@@ -4855,61 +4855,61 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
         <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X23" t="n">
         <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
         <v>65</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
@@ -4921,7 +4921,7 @@
         <v>65</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>18.5</v>
@@ -4936,19 +4936,19 @@
         <v>10.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ23" t="n">
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT23" t="n">
         <v>8.800000000000001</v>
@@ -4960,25 +4960,25 @@
         <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>16</v>
       </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD23" t="n">
         <v>22</v>
@@ -4987,14 +4987,14 @@
         <v>38</v>
       </c>
       <c r="BF23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BG23" t="n">
         <v>48</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -5243,13 +5243,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.18</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
         <v>1.18</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.64</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H26" t="n">
         <v>6.6</v>
@@ -5455,7 +5455,7 @@
         <v>5.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
         <v>1.6</v>
@@ -5497,7 +5497,7 @@
         <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="n">
         <v>200</v>
@@ -5512,7 +5512,7 @@
         <v>75</v>
       </c>
       <c r="AM26" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AN26" t="n">
         <v>21</v>
@@ -5524,7 +5524,7 @@
         <v>7.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
         <v>5.2</v>
@@ -5536,13 +5536,13 @@
         <v>5</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
         <v>4.9</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX26" t="n">
         <v>7.2</v>
@@ -5554,13 +5554,13 @@
         <v>4.9</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
         <v>5.3</v>
@@ -5572,11 +5572,11 @@
         <v>13.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G27" t="n">
         <v>2.28</v>
@@ -5637,7 +5637,7 @@
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
         <v>2.02</v>
@@ -5649,7 +5649,7 @@
         <v>3.65</v>
       </c>
       <c r="T27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U27" t="n">
         <v>2.04</v>
@@ -5685,7 +5685,7 @@
         <v>50</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG27" t="n">
         <v>970</v>
@@ -5715,62 +5715,62 @@
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX27" t="n">
         <v>4.7</v>
       </c>
       <c r="AY27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AZ27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC27" t="n">
         <v>5.1</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BD27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE27" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>6.6</v>
       </c>
       <c r="BF27" t="n">
         <v>14</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G31" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H31" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I31" t="n">
         <v>3.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K31" t="n">
         <v>4.4</v>
@@ -6413,13 +6413,13 @@
         <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q31" t="n">
         <v>1.51</v>
       </c>
       <c r="R31" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S31" t="n">
         <v>2.12</v>
@@ -6428,13 +6428,13 @@
         <v>1.45</v>
       </c>
       <c r="U31" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V31" t="n">
         <v>1.46</v>
       </c>
       <c r="W31" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X31" t="n">
         <v>34</v>
@@ -6467,10 +6467,10 @@
         <v>14.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ31" t="n">
         <v>38</v>
@@ -6482,28 +6482,28 @@
         <v>30</v>
       </c>
       <c r="AM31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>4.2</v>
       </c>
       <c r="AR31" t="n">
         <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AU31" t="n">
         <v>8.800000000000001</v>
@@ -6515,7 +6515,7 @@
         <v>20</v>
       </c>
       <c r="AX31" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY31" t="n">
         <v>9.6</v>
@@ -6524,10 +6524,10 @@
         <v>10.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC31" t="n">
         <v>16.5</v>
@@ -6536,17 +6536,17 @@
         <v>19.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG31" t="n">
         <v>11</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G32" t="n">
         <v>1.68</v>
@@ -6586,7 +6586,7 @@
         <v>5.5</v>
       </c>
       <c r="I32" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
         <v>4.3</v>
@@ -6622,7 +6622,7 @@
         <v>1.8</v>
       </c>
       <c r="U32" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V32" t="n">
         <v>1.2</v>
@@ -6634,16 +6634,16 @@
         <v>20</v>
       </c>
       <c r="Y32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA32" t="n">
         <v>150</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC32" t="n">
         <v>9.6</v>
@@ -6658,7 +6658,7 @@
         <v>10.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH32" t="n">
         <v>19.5</v>
@@ -6673,7 +6673,7 @@
         <v>16</v>
       </c>
       <c r="AL32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM32" t="n">
         <v>95</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
         <v>23</v>
       </c>
       <c r="AM34" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN34" t="n">
         <v>5.7</v>
@@ -7073,16 +7073,16 @@
         <v>42</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ34" t="n">
         <v>4.3</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT34" t="n">
         <v>13</v>
@@ -7094,7 +7094,7 @@
         <v>19</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX34" t="n">
         <v>10.5</v>
@@ -7106,7 +7106,7 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB34" t="n">
         <v>13.5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>3.95</v>
@@ -7192,13 +7192,13 @@
         <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="S35" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="O36" t="n">
         <v>1.35</v>
@@ -7395,10 +7395,10 @@
         <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
         <v>1.52</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -7550,13 +7550,13 @@
         <v>2.16</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H37" t="n">
         <v>3.4</v>
       </c>
       <c r="I37" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>3.55</v>
@@ -7595,7 +7595,7 @@
         <v>2.18</v>
       </c>
       <c r="V37" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
         <v>1.76</v>
@@ -7625,10 +7625,10 @@
         <v>40</v>
       </c>
       <c r="AF37" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH37" t="n">
         <v>970</v>
@@ -7637,13 +7637,13 @@
         <v>46</v>
       </c>
       <c r="AJ37" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM37" t="n">
         <v>110</v>
@@ -7664,7 +7664,7 @@
         <v>21</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT37" t="n">
         <v>9</v>
@@ -7676,7 +7676,7 @@
         <v>12.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX37" t="n">
         <v>13</v>
@@ -7688,19 +7688,19 @@
         <v>15</v>
       </c>
       <c r="BA37" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BB37" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC37" t="n">
         <v>18.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE37" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF37" t="n">
         <v>14</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -7747,13 +7747,13 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
         <v>4.4</v>
       </c>
       <c r="J38" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K38" t="n">
         <v>4.4</v>
@@ -7774,7 +7774,7 @@
         <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R38" t="n">
         <v>1.41</v>
@@ -7831,7 +7831,7 @@
         <v>65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK38" t="n">
         <v>25</v>
@@ -7840,7 +7840,7 @@
         <v>40</v>
       </c>
       <c r="AM38" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN38" t="n">
         <v>15.5</v>
@@ -7855,7 +7855,7 @@
         <v>13.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS38" t="n">
         <v>4.3</v>
@@ -7882,16 +7882,16 @@
         <v>14.5</v>
       </c>
       <c r="BA38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD38" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>4</v>
       </c>
       <c r="BE38" t="n">
         <v>4.3</v>
@@ -7900,11 +7900,11 @@
         <v>10.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G39" t="n">
         <v>1.85</v>
@@ -7944,7 +7944,7 @@
         <v>4.6</v>
       </c>
       <c r="I39" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>3.95</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G40" t="n">
         <v>2.5</v>
       </c>
       <c r="H40" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I40" t="n">
         <v>3.15</v>
@@ -8180,10 +8180,10 @@
         <v>1.46</v>
       </c>
       <c r="W40" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X40" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y40" t="n">
         <v>14</v>
@@ -8192,10 +8192,10 @@
         <v>22</v>
       </c>
       <c r="AA40" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB40" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC40" t="n">
         <v>8</v>
@@ -8204,7 +8204,7 @@
         <v>13.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF40" t="n">
         <v>16.5</v>
@@ -8234,7 +8234,7 @@
         <v>17</v>
       </c>
       <c r="AO40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP40" t="n">
         <v>14</v>
@@ -8252,7 +8252,7 @@
         <v>11</v>
       </c>
       <c r="AU40" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV40" t="n">
         <v>12</v>
@@ -8279,20 +8279,20 @@
         <v>22</v>
       </c>
       <c r="BD40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE40" t="n">
         <v>34</v>
       </c>
       <c r="BF40" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG40" t="n">
         <v>24</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G41" t="n">
         <v>2.38</v>
@@ -8332,7 +8332,7 @@
         <v>3.5</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J41" t="n">
         <v>3.25</v>
@@ -8344,13 +8344,13 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>1.79</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P41" t="n">
         <v>1.79</v>
@@ -8359,134 +8359,134 @@
         <v>2.06</v>
       </c>
       <c r="R41" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V41" t="n">
         <v>1.33</v>
       </c>
       <c r="W41" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY41" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AZ41" t="n">
-        <v>1.11</v>
+        <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.11</v>
+        <v>5.7</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.11</v>
+        <v>21</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.11</v>
+        <v>5.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.11</v>
+        <v>15.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.11</v>
+        <v>5.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8520,13 @@
         <v>2.56</v>
       </c>
       <c r="G42" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H42" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I42" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J42" t="n">
         <v>3.65</v>
@@ -8535,7 +8535,7 @@
         <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M42" t="n">
         <v>1.06</v>
@@ -8556,7 +8556,7 @@
         <v>1.42</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T42" t="n">
         <v>1.71</v>
@@ -8568,7 +8568,7 @@
         <v>1.51</v>
       </c>
       <c r="W42" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X42" t="n">
         <v>16.5</v>
@@ -8580,10 +8580,10 @@
         <v>21</v>
       </c>
       <c r="AA42" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC42" t="n">
         <v>8.4</v>
@@ -8592,37 +8592,37 @@
         <v>13</v>
       </c>
       <c r="AE42" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AF42" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ42" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK42" t="n">
         <v>38</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>40</v>
       </c>
       <c r="AL42" t="n">
         <v>38</v>
       </c>
       <c r="AM42" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN42" t="n">
         <v>21</v>
       </c>
       <c r="AO42" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AP42" t="n">
         <v>14.5</v>
@@ -8637,7 +8637,7 @@
         <v>38</v>
       </c>
       <c r="AT42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU42" t="n">
         <v>7.4</v>
@@ -8649,7 +8649,7 @@
         <v>19.5</v>
       </c>
       <c r="AX42" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY42" t="n">
         <v>10.5</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
         <v>3.65</v>
       </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
@@ -8744,7 +8744,7 @@
         <v>1.65</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
@@ -8756,10 +8756,10 @@
         <v>1.96</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V43" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W43" t="n">
         <v>1.64</v>
@@ -8780,7 +8780,7 @@
         <v>9.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
         <v>18</v>
@@ -8789,10 +8789,10 @@
         <v>60</v>
       </c>
       <c r="AF43" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH43" t="n">
         <v>23</v>
@@ -8804,7 +8804,7 @@
         <v>42</v>
       </c>
       <c r="AK43" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL43" t="n">
         <v>60</v>
@@ -8825,56 +8825,56 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR43" t="n">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE43" t="n">
         <v>5</v>
       </c>
-      <c r="AX43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB43" t="n">
+      <c r="BF43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG43" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>5</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K44" t="n">
         <v>4.9</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-10 18:08:02</t>
+          <t>2026-05-10 20:23:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -760,19 +760,19 @@
         <v>1.23</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
         <v>1.23</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -969,7 +969,7 @@
         <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -1002,7 +1002,7 @@
         <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>11</v>
@@ -1154,13 +1154,13 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1169,28 +1169,28 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
         <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
         <v>3.25</v>
@@ -1199,7 +1199,7 @@
         <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
         <v>8</v>
@@ -1235,7 +1235,7 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
         <v>220</v>
@@ -1250,22 +1250,22 @@
         <v>380</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP4" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU4" t="n">
         <v>11</v>
@@ -1274,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX4" t="n">
         <v>34</v>
@@ -1304,11 +1304,11 @@
         <v>95</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
         <v>2.32</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.05</v>
       </c>
       <c r="G6" t="n">
-        <v>440</v>
+        <v>990</v>
       </c>
       <c r="H6" t="n">
         <v>1.05</v>
       </c>
       <c r="I6" t="n">
-        <v>660</v>
+        <v>990</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1575,10 +1575,10 @@
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.56</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
@@ -1933,7 +1933,7 @@
         <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K8" t="n">
         <v>3.4</v>
@@ -1972,7 +1972,7 @@
         <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2118,52 +2118,52 @@
         <v>1.19</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="K9" t="n">
         <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
         <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
         <v>5.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.2</v>
@@ -2327,7 +2327,7 @@
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
         <v>110</v>
       </c>
       <c r="AP10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AY10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.87</v>
+        <v>2.68</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="BF10" t="n">
         <v>5.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -2897,13 +2897,13 @@
         <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
         <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
         <v>3.8</v>
@@ -2921,7 +2921,7 @@
         <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
         <v>1.9</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.72</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J15" t="n">
         <v>2.74</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         <v>3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3670,22 @@
         <v>1.81</v>
       </c>
       <c r="G17" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
         <v>4.9</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3718,7 +3718,7 @@
         <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
         <v>11.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
         <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q19" t="n">
         <v>1.58</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4315,10 +4315,10 @@
         <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
         <v>17.5</v>
@@ -4345,7 +4345,7 @@
         <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
         <v>170</v>
@@ -4363,10 +4363,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT20" t="n">
         <v>6.8</v>
@@ -4375,10 +4375,10 @@
         <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -4390,29 +4390,29 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4452,10 +4452,10 @@
         <v>3.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>3.95</v>
@@ -4473,7 +4473,7 @@
         <v>1.29</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>1.84</v>
@@ -4488,13 +4488,13 @@
         <v>1.72</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
         <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -4524,7 +4524,7 @@
         <v>16.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
         <v>19.5</v>
@@ -4557,10 +4557,10 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT21" t="n">
         <v>9.199999999999999</v>
@@ -4572,10 +4572,10 @@
         <v>13.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
@@ -4584,29 +4584,29 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF21" t="n">
         <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.97</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H22" t="n">
         <v>3.7</v>
@@ -4661,16 +4661,16 @@
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
@@ -4688,7 +4688,7 @@
         <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X22" t="n">
         <v>25</v>
@@ -4727,7 +4727,7 @@
         <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK22" t="n">
         <v>30</v>
@@ -4757,22 +4757,22 @@
         <v>2.26</v>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AV22" t="n">
         <v>2.1</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AY22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AZ22" t="n">
         <v>2.12</v>
@@ -4790,17 +4790,17 @@
         <v>2.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G23" t="n">
         <v>1.86</v>
@@ -4879,7 +4879,7 @@
         <v>2.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
         <v>2.16</v>
@@ -4939,7 +4939,7 @@
         <v>65</v>
       </c>
       <c r="AP23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>16</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>910</v>
+        <v>990</v>
       </c>
       <c r="H24" t="n">
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>850</v>
+        <v>990</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
@@ -5058,19 +5058,19 @@
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5219,160 +5219,160 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M25" t="n">
         <v>1.04</v>
       </c>
-      <c r="G25" t="n">
-        <v>370</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I25" t="n">
-        <v>430</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K25" t="n">
-        <v>950</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X25" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
         <v>1.01</v>
       </c>
-      <c r="M25" t="n">
+      <c r="AQ25" t="n">
         <v>1.01</v>
       </c>
-      <c r="N25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="AR25" t="n">
         <v>1.01</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AS25" t="n">
         <v>1.01</v>
       </c>
-      <c r="V25" t="n">
+      <c r="AT25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU25" t="n">
         <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
         <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>6.6</v>
       </c>
       <c r="I26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5763,14 +5763,14 @@
         <v>6.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="BG27" t="n">
         <v>5.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>110</v>
+        <v>3.1</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I28" t="n">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M28" t="n">
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S28" t="n">
-        <v>1.17</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>5.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6300,10 +6300,10 @@
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="AS30" t="n">
         <v>4.7</v>
@@ -6312,22 +6312,22 @@
         <v>3.75</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="AV30" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="AW30" t="n">
         <v>4.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AZ30" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="BA30" t="n">
         <v>4.6</v>
@@ -6336,7 +6336,7 @@
         <v>4.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BD30" t="n">
         <v>4.6</v>
@@ -6345,14 +6345,14 @@
         <v>4.9</v>
       </c>
       <c r="BF30" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6386,10 +6386,10 @@
         <v>2.28</v>
       </c>
       <c r="G31" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H31" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I31" t="n">
         <v>3.2</v>
@@ -6434,7 +6434,7 @@
         <v>1.46</v>
       </c>
       <c r="W31" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X31" t="n">
         <v>34</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>1.68</v>
       </c>
       <c r="H32" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I32" t="n">
         <v>5.9</v>
@@ -6697,7 +6697,7 @@
         <v>42</v>
       </c>
       <c r="AT32" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU32" t="n">
         <v>8.800000000000001</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6774,13 +6774,13 @@
         <v>1.88</v>
       </c>
       <c r="G33" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>3.8</v>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J33" t="n">
         <v>4</v>
@@ -6807,22 +6807,22 @@
         <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="S33" t="n">
-        <v>1.53</v>
+        <v>2.24</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
         <v>1.31</v>
       </c>
       <c r="W33" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X33" t="n">
         <v>34</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -6989,22 +6989,22 @@
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P34" t="n">
         <v>3.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="R34" t="n">
         <v>1.8</v>
       </c>
       <c r="S34" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="T34" t="n">
         <v>1.45</v>
@@ -7019,10 +7019,10 @@
         <v>2.8</v>
       </c>
       <c r="X34" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y34" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z34" t="n">
         <v>70</v>
@@ -7031,22 +7031,22 @@
         <v>180</v>
       </c>
       <c r="AB34" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE34" t="n">
         <v>70</v>
       </c>
       <c r="AF34" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH34" t="n">
         <v>20</v>
@@ -7055,7 +7055,7 @@
         <v>55</v>
       </c>
       <c r="AJ34" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK34" t="n">
         <v>15.5</v>
@@ -7073,16 +7073,16 @@
         <v>42</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT34" t="n">
         <v>13</v>
@@ -7094,7 +7094,7 @@
         <v>19</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX34" t="n">
         <v>10.5</v>
@@ -7106,7 +7106,7 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB34" t="n">
         <v>13.5</v>
@@ -7118,17 +7118,17 @@
         <v>17</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BG34" t="n">
         <v>24</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>1.88</v>
       </c>
       <c r="G35" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H35" t="n">
         <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
         <v>3.95</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7195,22 +7195,22 @@
         <v>1.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="S35" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
         <v>1.28</v>
       </c>
       <c r="W35" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7222,7 +7222,7 @@
         <v>42</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB35" t="n">
         <v>1000</v>
@@ -7231,7 +7231,7 @@
         <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AS35" t="n">
         <v>1.32</v>
       </c>
       <c r="AT35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.32</v>
       </c>
-      <c r="AU35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.18</v>
+        <v>7</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7550,13 +7550,13 @@
         <v>2.16</v>
       </c>
       <c r="G37" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H37" t="n">
         <v>3.4</v>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J37" t="n">
         <v>3.55</v>
@@ -7589,7 +7589,7 @@
         <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U37" t="n">
         <v>2.18</v>
@@ -7598,7 +7598,7 @@
         <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X37" t="n">
         <v>17</v>
@@ -7607,7 +7607,7 @@
         <v>16</v>
       </c>
       <c r="Z37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA37" t="n">
         <v>75</v>
@@ -7616,13 +7616,13 @@
         <v>970</v>
       </c>
       <c r="AC37" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD37" t="n">
         <v>970</v>
       </c>
       <c r="AE37" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AF37" t="n">
         <v>15</v>
@@ -7664,7 +7664,7 @@
         <v>21</v>
       </c>
       <c r="AS37" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AT37" t="n">
         <v>9</v>
@@ -7676,7 +7676,7 @@
         <v>12.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX37" t="n">
         <v>13</v>
@@ -7691,16 +7691,16 @@
         <v>38</v>
       </c>
       <c r="BB37" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC37" t="n">
         <v>18.5</v>
       </c>
       <c r="BD37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE37" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>10.5</v>
       </c>
       <c r="BF37" t="n">
         <v>14</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
         <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="R38" t="n">
         <v>1.41</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
         <v>3.65</v>
       </c>
       <c r="L40" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M40" t="n">
         <v>1.06</v>
@@ -8159,7 +8159,7 @@
         <v>1.27</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q40" t="n">
         <v>1.82</v>
@@ -8186,7 +8186,7 @@
         <v>16</v>
       </c>
       <c r="Y40" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z40" t="n">
         <v>22</v>
@@ -8234,10 +8234,10 @@
         <v>17</v>
       </c>
       <c r="AO40" t="n">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="AP40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ40" t="n">
         <v>13</v>
@@ -8285,14 +8285,14 @@
         <v>34</v>
       </c>
       <c r="BF40" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG40" t="n">
         <v>24</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
         <v>70</v>
       </c>
       <c r="AJ41" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK41" t="n">
         <v>30</v>
@@ -8452,7 +8452,7 @@
         <v>13</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX41" t="n">
         <v>11.5</v>
@@ -8464,29 +8464,29 @@
         <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC41" t="n">
         <v>21</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF41" t="n">
         <v>15.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G42" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H42" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I42" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J42" t="n">
         <v>3.65</v>
@@ -8565,10 +8565,10 @@
         <v>2.3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X42" t="n">
         <v>16.5</v>
@@ -8610,19 +8610,19 @@
         <v>36</v>
       </c>
       <c r="AK42" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL42" t="n">
         <v>38</v>
       </c>
       <c r="AM42" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP42" t="n">
         <v>14.5</v>
@@ -8658,7 +8658,7 @@
         <v>14.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BB42" t="n">
         <v>22</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
         <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L43" t="n">
         <v>1.44</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>
@@ -8905,170 +8905,170 @@
         </is>
       </c>
       <c r="F44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G44" t="n">
         <v>1.5</v>
       </c>
-      <c r="G44" t="n">
-        <v>1.58</v>
-      </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="I44" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K44" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P44" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-10 20:23:32</t>
+          <t>2026-05-10 22:37:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH44"/>
+  <dimension ref="A1:BH46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
         <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
         <v>3.3</v>
@@ -966,7 +966,7 @@
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.51</v>
@@ -975,16 +975,16 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
         <v>1.25</v>
@@ -993,13 +993,13 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
         <v>1.56</v>
@@ -1008,7 +1008,7 @@
         <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
         <v>21</v>
@@ -1017,25 +1017,25 @@
         <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>44</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
@@ -1056,22 +1056,22 @@
         <v>36</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1080,41 +1080,41 @@
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB3" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB3" t="n">
-        <v>7</v>
-      </c>
       <c r="BC3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG3" t="n">
         <v>8</v>
       </c>
-      <c r="BF3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J4" t="n">
         <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1175,34 +1175,34 @@
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
         <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
         <v>3.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
         <v>7.2</v>
@@ -1211,10 +1211,10 @@
         <v>11</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1235,7 +1235,7 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AK4" t="n">
         <v>220</v>
@@ -1259,7 +1259,7 @@
         <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
         <v>9.6</v>
@@ -1268,7 +1268,7 @@
         <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
         <v>2.32</v>
@@ -1348,10 +1348,10 @@
         <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.45</v>
@@ -1363,43 +1363,43 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
         <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
         <v>1.75</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
         <v>85</v>
@@ -1417,7 +1417,7 @@
         <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>13.5</v>
@@ -1447,62 +1447,62 @@
         <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G6" t="n">
         <v>990</v>
       </c>
       <c r="H6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I6" t="n">
         <v>990</v>
@@ -1641,52 +1641,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
         <v>2.42</v>
       </c>
       <c r="I7" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
         <v>1.56</v>
@@ -1754,7 +1754,7 @@
         <v>2.36</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
         <v>1.45</v>
@@ -1763,13 +1763,13 @@
         <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
         <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
         <v>1.69</v>
@@ -1778,7 +1778,7 @@
         <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1802,7 +1802,7 @@
         <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
         <v>28</v>
@@ -1811,7 +1811,7 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
@@ -1841,19 +1841,19 @@
         <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS7" t="n">
         <v>7.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW7" t="n">
         <v>5.1</v>
@@ -1862,35 +1862,35 @@
         <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>7.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.36</v>
+        <v>5.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>2.42</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
         <v>4.5</v>
@@ -1936,7 +1936,7 @@
         <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.48</v>
@@ -2005,7 +2005,7 @@
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
@@ -2038,7 +2038,7 @@
         <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.06</v>
+        <v>2.86</v>
       </c>
       <c r="AT8" t="n">
         <v>6.4</v>
@@ -2050,19 +2050,19 @@
         <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AZ8" t="n">
         <v>7</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2071,7 +2071,7 @@
         <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="BE8" t="n">
         <v>5.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>1.19</v>
       </c>
       <c r="G9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
         <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>1.21</v>
@@ -2139,28 +2139,28 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
         <v>1.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
         <v>1.03</v>
@@ -2193,7 +2193,7 @@
         <v>440</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>15.5</v>
@@ -2202,7 +2202,7 @@
         <v>55</v>
       </c>
       <c r="AI9" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AJ9" t="n">
         <v>10.5</v>
@@ -2217,13 +2217,13 @@
         <v>280</v>
       </c>
       <c r="AN9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.4</v>
@@ -2232,13 +2232,13 @@
         <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
         <v>4.4</v>
@@ -2247,13 +2247,13 @@
         <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
         <v>4.6</v>
@@ -2271,14 +2271,14 @@
         <v>4.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BG9" t="n">
         <v>4.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -2321,19 +2321,19 @@
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
         <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O10" t="n">
         <v>1.44</v>
@@ -2351,7 +2351,7 @@
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
         <v>1.8</v>
@@ -2381,7 +2381,7 @@
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>80</v>
@@ -2393,7 +2393,7 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>95</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AX10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BF10" t="n">
         <v>5.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
         <v>600</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
         <v>870</v>
@@ -2712,7 +2712,7 @@
         <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
         <v>1.9</v>
@@ -2936,7 +2936,7 @@
         <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
         <v>1.62</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H14" t="n">
         <v>3.45</v>
@@ -3109,7 +3109,7 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>1.28</v>
@@ -3136,7 +3136,7 @@
         <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X14" t="n">
         <v>16.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.72</v>
       </c>
       <c r="I15" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J15" t="n">
         <v>2.74</v>
@@ -3303,7 +3303,7 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.47</v>
@@ -3363,7 +3363,7 @@
         <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
         <v>70</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.47</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
         <v>3.75</v>
@@ -3912,7 +3912,7 @@
         <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
@@ -3963,10 +3963,10 @@
         <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
         <v>9.800000000000001</v>
@@ -3978,7 +3978,7 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
         <v>7.8</v>
@@ -4002,29 +4002,29 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.4</v>
       </c>
       <c r="BD18" t="n">
         <v>4.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
         <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
         <v>2.28</v>
       </c>
       <c r="X19" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Y19" t="n">
         <v>26</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="G21" t="n">
         <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>2.06</v>
       </c>
       <c r="O21" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="T21" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="G22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.18</v>
       </c>
-      <c r="H22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.83</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X22" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Z22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO22" t="n">
         <v>44</v>
       </c>
-      <c r="AA22" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP22" t="n">
-        <v>2.12</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.26</v>
+        <v>5.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.02</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.96</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.1</v>
+        <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.24</v>
+        <v>5.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.08</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>2.02</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.12</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.24</v>
+        <v>5.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.14</v>
+        <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.32</v>
+        <v>5.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.32</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
         <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
         <v>1.43</v>
@@ -4876,7 +4876,7 @@
         <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
         <v>1.25</v>
@@ -4888,10 +4888,10 @@
         <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="n">
         <v>110</v>
@@ -4903,7 +4903,7 @@
         <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>65</v>
@@ -4921,19 +4921,19 @@
         <v>65</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO23" t="n">
         <v>65</v>
@@ -4945,7 +4945,7 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AS23" t="n">
         <v>38</v>
@@ -4960,48 +4960,48 @@
         <v>16.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AX23" t="n">
         <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
         <v>16.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="BB23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC23" t="n">
         <v>16.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BE23" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M24" t="n">
         <v>1.04</v>
       </c>
-      <c r="G24" t="n">
-        <v>990</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I24" t="n">
-        <v>990</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="N24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X24" t="n">
         <v>950</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC25" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AD25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK25" t="n">
         <v>28</v>
       </c>
-      <c r="Y25" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z25" t="n">
+      <c r="AL25" t="n">
         <v>75</v>
       </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>36</v>
-      </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN25" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>1.79</v>
+        <v>990</v>
       </c>
       <c r="H26" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>990</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.11</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>3.7</v>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5766,11 +5766,11 @@
         <v>5.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
         <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
@@ -5849,13 +5849,13 @@
         <v>2.46</v>
       </c>
       <c r="V28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X28" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y28" t="n">
         <v>970</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H29" t="n">
         <v>1.38</v>
       </c>
       <c r="I29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="J29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K29" t="n">
         <v>5.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -6028,13 +6028,13 @@
         <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R29" t="n">
         <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>1.05</v>
       </c>
       <c r="T29" t="n">
         <v>2.28</v>
@@ -6043,7 +6043,7 @@
         <v>1.63</v>
       </c>
       <c r="V29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="W29" t="n">
         <v>1.07</v>
@@ -6061,7 +6061,7 @@
         <v>970</v>
       </c>
       <c r="AB29" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AC29" t="n">
         <v>970</v>
@@ -6076,10 +6076,10 @@
         <v>130</v>
       </c>
       <c r="AG29" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="AH29" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6103,62 +6103,62 @@
         <v>970</v>
       </c>
       <c r="AP29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS29" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AT29" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
         <v>3.75</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="AV30" t="n">
         <v>3.85</v>
@@ -6348,11 +6348,11 @@
         <v>4.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -6437,10 +6437,10 @@
         <v>1.64</v>
       </c>
       <c r="X31" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Y31" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Z31" t="n">
         <v>30</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
         <v>1.57</v>
       </c>
       <c r="S33" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T33" t="n">
         <v>1.11</v>
@@ -6825,7 +6825,7 @@
         <v>2</v>
       </c>
       <c r="X33" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Y33" t="n">
         <v>1000</v>
@@ -6876,65 +6876,65 @@
         <v>11</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT33" t="n">
         <v>1.47</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR33" t="n">
+      <c r="AU33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX33" t="n">
         <v>1.48</v>
       </c>
-      <c r="AS33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AY33" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="BD33" t="n">
         <v>18</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
         <v>1.49</v>
       </c>
       <c r="S35" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T35" t="n">
         <v>1.11</v>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AR35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BD35" t="n">
         <v>1.3</v>
       </c>
-      <c r="AS35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BE35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF35" t="n">
         <v>7</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -7362,49 +7362,49 @@
         <v>2.56</v>
       </c>
       <c r="I36" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P36" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q36" t="n">
         <v>2.04</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>2.36</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V36" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W36" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7422,7 +7422,7 @@
         <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD36" t="n">
         <v>1000</v>
@@ -7461,62 +7461,62 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
         <v>3.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M37" t="n">
         <v>1.07</v>
@@ -7664,7 +7664,7 @@
         <v>21</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT37" t="n">
         <v>9</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -7855,10 +7855,10 @@
         <v>13.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT38" t="n">
         <v>8.6</v>
@@ -7870,7 +7870,7 @@
         <v>14</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX38" t="n">
         <v>11</v>
@@ -7882,19 +7882,19 @@
         <v>14.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC38" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF38" t="n">
         <v>10.5</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>1.73</v>
       </c>
       <c r="G39" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H39" t="n">
         <v>4.6</v>
@@ -7992,7 +7992,7 @@
         <v>23</v>
       </c>
       <c r="Y39" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z39" t="n">
         <v>40</v>
@@ -8019,7 +8019,7 @@
         <v>10.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI39" t="n">
         <v>60</v>
@@ -8049,7 +8049,7 @@
         <v>17.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS39" t="n">
         <v>9.6</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
         <v>3.65</v>
       </c>
       <c r="L40" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M40" t="n">
         <v>1.06</v>
@@ -8168,7 +8168,7 @@
         <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T40" t="n">
         <v>1.68</v>
@@ -8186,7 +8186,7 @@
         <v>16</v>
       </c>
       <c r="Y40" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z40" t="n">
         <v>22</v>
@@ -8234,7 +8234,7 @@
         <v>17</v>
       </c>
       <c r="AO40" t="n">
-        <v>300</v>
+        <v>27</v>
       </c>
       <c r="AP40" t="n">
         <v>15</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -8326,16 +8326,16 @@
         <v>2.16</v>
       </c>
       <c r="G41" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="H41" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I41" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J41" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>3.6</v>
@@ -8368,13 +8368,13 @@
         <v>1.8</v>
       </c>
       <c r="U41" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W41" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="X41" t="n">
         <v>14.5</v>
@@ -8389,31 +8389,31 @@
         <v>85</v>
       </c>
       <c r="AB41" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD41" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE41" t="n">
         <v>55</v>
       </c>
       <c r="AF41" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG41" t="n">
         <v>13</v>
       </c>
       <c r="AH41" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI41" t="n">
         <v>70</v>
       </c>
       <c r="AJ41" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK41" t="n">
         <v>30</v>
@@ -8440,7 +8440,7 @@
         <v>21</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="AT41" t="n">
         <v>7.8</v>
@@ -8452,10 +8452,10 @@
         <v>13</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AX41" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY41" t="n">
         <v>9.4</v>
@@ -8464,29 +8464,29 @@
         <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC41" t="n">
         <v>21</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BF41" t="n">
         <v>15.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G42" t="n">
         <v>2.58</v>
@@ -8529,7 +8529,7 @@
         <v>2.98</v>
       </c>
       <c r="J42" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K42" t="n">
         <v>3.7</v>
@@ -8544,7 +8544,7 @@
         <v>4.2</v>
       </c>
       <c r="O42" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P42" t="n">
         <v>2.08</v>
@@ -8553,13 +8553,13 @@
         <v>1.88</v>
       </c>
       <c r="R42" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S42" t="n">
         <v>3.25</v>
       </c>
       <c r="T42" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U42" t="n">
         <v>2.3</v>
@@ -8571,7 +8571,7 @@
         <v>1.63</v>
       </c>
       <c r="X42" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y42" t="n">
         <v>13</v>
@@ -8580,19 +8580,19 @@
         <v>21</v>
       </c>
       <c r="AA42" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB42" t="n">
         <v>12</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
         <v>13</v>
       </c>
       <c r="AE42" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AF42" t="n">
         <v>17.5</v>
@@ -8601,16 +8601,16 @@
         <v>12</v>
       </c>
       <c r="AH42" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI42" t="n">
         <v>42</v>
       </c>
       <c r="AJ42" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK42" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AL42" t="n">
         <v>38</v>
@@ -8619,10 +8619,10 @@
         <v>95</v>
       </c>
       <c r="AN42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP42" t="n">
         <v>14.5</v>
@@ -8631,16 +8631,16 @@
         <v>11.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS42" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AT42" t="n">
         <v>10.5</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV42" t="n">
         <v>11.5</v>
@@ -8655,10 +8655,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA42" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BB42" t="n">
         <v>22</v>
@@ -8676,11 +8676,11 @@
         <v>18</v>
       </c>
       <c r="BG42" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
         <v>9.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD43" t="n">
         <v>18</v>
@@ -8828,7 +8828,7 @@
         <v>4.4</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT43" t="n">
         <v>7.4</v>
@@ -8849,13 +8849,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ43" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA43" t="n">
         <v>4.9</v>
       </c>
       <c r="BB43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC43" t="n">
         <v>4.6</v>
@@ -8864,17 +8864,17 @@
         <v>4.8</v>
       </c>
       <c r="BE43" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-10 22:37:37</t>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
         <v>4.3</v>
       </c>
       <c r="K44" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8929,7 +8929,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O44" t="n">
         <v>1.26</v>
@@ -8938,7 +8938,7 @@
         <v>2.02</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R44" t="n">
         <v>1.39</v>
@@ -8947,7 +8947,7 @@
         <v>2.96</v>
       </c>
       <c r="T44" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U44" t="n">
         <v>1.67</v>
@@ -8977,13 +8977,13 @@
         <v>1000</v>
       </c>
       <c r="AD44" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG44" t="n">
         <v>1000</v>
@@ -9013,62 +9013,450 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AX44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:52:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Olancho</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
         <v>1.02</v>
       </c>
-      <c r="AY44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BH44" t="inlineStr">
-        <is>
-          <t>2026-05-10 22:37:37</t>
+      <c r="G45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I45" t="n">
+        <v>990</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K45" t="n">
+        <v>950</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:52:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-05-11 00:52:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH48"/>
+  <dimension ref="A1:BH50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
         <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1145,43 +1145,43 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="n">
         <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
         <v>3.5</v>
@@ -1190,16 +1190,16 @@
         <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
         <v>7.4</v>
@@ -1208,19 +1208,19 @@
         <v>7.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AB4" t="n">
         <v>26</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
@@ -1250,10 +1250,10 @@
         <v>370</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.8</v>
@@ -1262,13 +1262,13 @@
         <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
         <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1286,16 +1286,16 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB4" t="n">
         <v>95</v>
       </c>
       <c r="BC4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BD4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE4" t="n">
         <v>95</v>
@@ -1304,11 +1304,11 @@
         <v>95</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1348,16 +1348,16 @@
         <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1372,7 +1372,7 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1408,7 +1408,7 @@
         <v>8.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
         <v>17</v>
@@ -1453,10 +1453,10 @@
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1468,41 +1468,41 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
         <v>18.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>990</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
         <v>4.2</v>
@@ -1751,13 +1751,13 @@
         <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
         <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
         <v>2.8</v>
@@ -1766,7 +1766,7 @@
         <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
         <v>2.24</v>
@@ -1775,7 +1775,7 @@
         <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.32</v>
@@ -1787,46 +1787,46 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
         <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
         <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL7" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
         <v>120</v>
@@ -1838,59 +1838,59 @@
         <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA7" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BB7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
         <v>1.23</v>
@@ -2130,7 +2130,7 @@
         <v>7.4</v>
       </c>
       <c r="K9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>1.21</v>
@@ -2151,7 +2151,7 @@
         <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
         <v>2.18</v>
@@ -2223,7 +2223,7 @@
         <v>580</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>4.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC10" t="n">
         <v>970</v>
@@ -2417,40 +2417,40 @@
         <v>110</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
         <v>5.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
         <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AX10" t="n">
         <v>4.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ10" t="n">
         <v>4</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.14</v>
+        <v>2.96</v>
       </c>
       <c r="BB10" t="n">
         <v>2.74</v>
@@ -2459,20 +2459,20 @@
         <v>3.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.12</v>
+        <v>2.92</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="BF10" t="n">
         <v>6</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
         <v>1.2</v>
@@ -2736,7 +2736,7 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.45</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,34 +2915,34 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
         <v>1.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
         <v>1.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="n">
         <v>2.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
@@ -3109,7 +3109,7 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
@@ -3136,7 +3136,7 @@
         <v>1.62</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
         <v>1.32</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>2.72</v>
       </c>
       <c r="I16" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
@@ -3497,7 +3497,7 @@
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>1.47</v>
@@ -3524,7 +3524,7 @@
         <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3682,10 +3682,10 @@
         <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
         <v>5.7</v>
@@ -3876,10 +3876,10 @@
         <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -3909,10 +3909,10 @@
         <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X18" t="n">
         <v>11.5</v>
@@ -3927,10 +3927,10 @@
         <v>180</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
         <v>22</v>
@@ -3942,7 +3942,7 @@
         <v>11</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>24</v>
@@ -3963,7 +3963,7 @@
         <v>190</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>150</v>
@@ -3975,10 +3975,10 @@
         <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
@@ -3990,7 +3990,7 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>9</v>
@@ -4002,7 +4002,7 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>18</v>
@@ -4011,20 +4011,20 @@
         <v>19.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
         <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
         <v>18</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT19" t="n">
         <v>7.8</v>
@@ -4184,7 +4184,7 @@
         <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
@@ -4196,29 +4196,29 @@
         <v>16.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD19" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF19" t="n">
         <v>20</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4249,52 +4249,52 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="Q20" t="n">
         <v>1.17</v>
       </c>
       <c r="R20" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
         <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4599,14 +4599,14 @@
         <v>4.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="BG21" t="n">
         <v>4.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
         <v>3.85</v>
@@ -4649,7 +4649,7 @@
         <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
         <v>3.3</v>
@@ -4676,7 +4676,7 @@
         <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
         <v>1.92</v>
@@ -4688,7 +4688,7 @@
         <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>12.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4822,109 +4822,109 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="G23" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
         <v>16.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL23" t="n">
         <v>40</v>
@@ -4933,25 +4933,25 @@
         <v>100</v>
       </c>
       <c r="AN23" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
         <v>7.4</v>
@@ -4960,41 +4960,41 @@
         <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5016,109 +5016,109 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="G24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U24" t="n">
         <v>2.18</v>
       </c>
-      <c r="H24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.22</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="X24" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="Z24" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF24" t="n">
         <v>16.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -5127,25 +5127,25 @@
         <v>100</v>
       </c>
       <c r="AN24" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO24" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
@@ -5154,41 +5154,41 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AX24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG24" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I25" t="n">
         <v>4.7</v>
       </c>
-      <c r="I25" t="n">
-        <v>4.9</v>
-      </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -5249,7 +5249,7 @@
         <v>1.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
         <v>1.85</v>
@@ -5261,16 +5261,16 @@
         <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U25" t="n">
         <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X25" t="n">
         <v>16.5</v>
@@ -5285,7 +5285,7 @@
         <v>110</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC25" t="n">
         <v>9</v>
@@ -5345,22 +5345,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
@@ -5378,18 +5378,18 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M26" t="n">
         <v>1.04</v>
       </c>
-      <c r="G26" t="n">
-        <v>990</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I26" t="n">
-        <v>990</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="N26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X26" t="n">
         <v>950</v>
       </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="G27" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="H27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>360</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS27" t="n">
         <v>6</v>
       </c>
-      <c r="I27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="AT27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE27" t="n">
         <v>6</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="X27" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BF27" t="n">
-        <v>3.25</v>
+        <v>13.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.62</v>
+        <v>6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,179 +5792,179 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>1.76</v>
+        <v>990</v>
       </c>
       <c r="H28" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>8.199999999999999</v>
+        <v>990</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.58</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S28" t="n">
-        <v>5.1</v>
+        <v>1.44</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>2.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H29" t="n">
         <v>3.75</v>
@@ -6007,13 +6007,13 @@
         <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -6025,7 +6025,7 @@
         <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q29" t="n">
         <v>2.02</v>
@@ -6046,7 +6046,7 @@
         <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X29" t="n">
         <v>15.5</v>
@@ -6061,7 +6061,7 @@
         <v>95</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
         <v>9.4</v>
@@ -6073,7 +6073,7 @@
         <v>50</v>
       </c>
       <c r="AF29" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
         <v>11.5</v>
@@ -6106,59 +6106,59 @@
         <v>11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU29" t="n">
         <v>6.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD29" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE29" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>3.05</v>
       </c>
       <c r="H30" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I30" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J30" t="n">
         <v>3.45</v>
@@ -6210,7 +6210,7 @@
         <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
         <v>4.9</v>
@@ -6222,13 +6222,13 @@
         <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R30" t="n">
         <v>1.54</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
         <v>1.54</v>
@@ -6240,7 +6240,7 @@
         <v>1.51</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X30" t="n">
         <v>950</v>
@@ -6249,10 +6249,10 @@
         <v>18</v>
       </c>
       <c r="Z30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB30" t="n">
         <v>970</v>
@@ -6270,7 +6270,7 @@
         <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
         <v>970</v>
@@ -6303,7 +6303,7 @@
         <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS30" t="n">
         <v>4.6</v>
@@ -6315,31 +6315,31 @@
         <v>8</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX30" t="n">
         <v>15.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA30" t="n">
         <v>4.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE30" t="n">
         <v>4.7</v>
@@ -6348,11 +6348,11 @@
         <v>12</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6392,10 +6392,10 @@
         <v>1.38</v>
       </c>
       <c r="I31" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="J31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K31" t="n">
         <v>5.2</v>
@@ -6416,7 +6416,7 @@
         <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R31" t="n">
         <v>1.32</v>
@@ -6431,7 +6431,7 @@
         <v>1.63</v>
       </c>
       <c r="V31" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="W31" t="n">
         <v>1.07</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6580,22 +6580,22 @@
         <v>2.42</v>
       </c>
       <c r="G32" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H32" t="n">
         <v>2.88</v>
       </c>
       <c r="I32" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -6607,7 +6607,7 @@
         <v>1.29</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
         <v>1.86</v>
@@ -6625,10 +6625,10 @@
         <v>2.24</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X32" t="n">
         <v>18</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6771,170 +6771,170 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="G33" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K33" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>2.48</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="Q33" t="n">
         <v>1.51</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="S33" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="V33" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X33" t="n">
         <v>950</v>
       </c>
       <c r="Y33" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Z33" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA33" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB33" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AC33" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD33" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN33" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.22</v>
+        <v>4.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.23</v>
+        <v>4.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.21</v>
+        <v>4.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.29</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.29</v>
+        <v>12</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.29</v>
+        <v>4.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.29</v>
+        <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.29</v>
+        <v>4.3</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.29</v>
+        <v>4.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.29</v>
+        <v>4.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.22</v>
+        <v>4.4</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.29</v>
+        <v>4.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.29</v>
+        <v>11</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>5.9</v>
       </c>
       <c r="J34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K34" t="n">
         <v>4.5</v>
@@ -7094,7 +7094,7 @@
         <v>19.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AX34" t="n">
         <v>9.6</v>
@@ -7115,7 +7115,7 @@
         <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE34" t="n">
         <v>38</v>
@@ -7124,11 +7124,11 @@
         <v>7.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7150,179 +7150,179 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.54</v>
+        <v>1.88</v>
       </c>
       <c r="G35" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="I35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2</v>
+      </c>
+      <c r="X35" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS35" t="n">
         <v>6</v>
       </c>
-      <c r="J35" t="n">
+      <c r="AT35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB35" t="n">
         <v>5.3</v>
       </c>
-      <c r="K35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P35" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X35" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS35" t="n">
+      <c r="BC35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD35" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>17</v>
-      </c>
       <c r="BE35" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BF35" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>24</v>
+        <v>5.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7344,179 +7344,179 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>1.88</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="H36" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K36" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>2.32</v>
       </c>
       <c r="O36" t="n">
         <v>1.19</v>
       </c>
       <c r="P36" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="R36" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="T36" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>2.48</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR36" t="n">
         <v>1.31</v>
       </c>
-      <c r="W36" t="n">
-        <v>2</v>
-      </c>
-      <c r="X36" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AS36" t="n">
-        <v>1.89</v>
+        <v>1.33</v>
       </c>
       <c r="AT36" t="n">
-        <v>11.5</v>
+        <v>1.35</v>
       </c>
       <c r="AU36" t="n">
-        <v>9</v>
+        <v>1.35</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.71</v>
+        <v>1.35</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.6</v>
+        <v>1.35</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="BB36" t="n">
-        <v>5</v>
+        <v>1.35</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="BF36" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.82</v>
+        <v>1.35</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="G37" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="K37" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N37" t="n">
-        <v>2.32</v>
+        <v>7.8</v>
       </c>
       <c r="O37" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="S37" t="n">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V37" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W37" t="n">
-        <v>2.02</v>
+        <v>2.8</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z37" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AA37" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV37" t="n">
         <v>21</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AW37" t="n">
-        <v>1.35</v>
+        <v>12</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.35</v>
+        <v>12.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.35</v>
+        <v>10</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.35</v>
+        <v>15.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.35</v>
+        <v>13</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.35</v>
+        <v>15.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.27</v>
+        <v>12.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.3</v>
+        <v>18</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.33</v>
+        <v>12</v>
       </c>
       <c r="BF37" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.35</v>
+        <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,179 +7732,179 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Dundee Utd</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.84</v>
+        <v>1.74</v>
       </c>
       <c r="G38" t="n">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="H38" t="n">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S38" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="T38" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="U38" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V38" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="W38" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="X38" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="BA38" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC38" t="n">
         <v>15</v>
       </c>
-      <c r="AE38" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP38" t="n">
+      <c r="BD38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE38" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF38" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="BG38" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7926,186 +7926,186 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>St Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="G39" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M39" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N39" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P39" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="R39" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S39" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="U39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W39" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP39" t="n">
         <v>14</v>
       </c>
-      <c r="Z39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG39" t="n">
+      <c r="AQ39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX39" t="n">
         <v>11</v>
       </c>
-      <c r="AH39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS39" t="n">
+      <c r="AY39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF39" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>14</v>
-      </c>
       <c r="BG39" t="n">
-        <v>27</v>
+        <v>4.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8120,179 +8120,179 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.93</v>
+        <v>2.84</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="I40" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K40" t="n">
         <v>3.7</v>
       </c>
-      <c r="K40" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.3</v>
       </c>
-      <c r="M40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N40" t="n">
-        <v>4</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.41</v>
-      </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T40" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="U40" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V40" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="X40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z40" t="n">
         <v>21</v>
       </c>
-      <c r="Y40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>38</v>
-      </c>
       <c r="AA40" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC40" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE40" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>60</v>
       </c>
-      <c r="AF40" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG40" t="n">
+      <c r="AK40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>13</v>
       </c>
-      <c r="AH40" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA40" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BC40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE40" t="n">
         <v>4.2</v>
       </c>
-      <c r="BD40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF40" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -8314,179 +8314,179 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Dundee Utd</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>St Mirren</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="G41" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="H41" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K41" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M41" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="O41" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="P41" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V41" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="W41" t="n">
-        <v>2.16</v>
+        <v>1.78</v>
       </c>
       <c r="X41" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Y41" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="Z41" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AA41" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AB41" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD41" t="n">
         <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AF41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS41" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH41" t="n">
+      <c r="AT41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC41" t="n">
         <v>18.5</v>
       </c>
-      <c r="AI41" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN41" t="n">
+      <c r="BD41" t="n">
         <v>9.4</v>
       </c>
-      <c r="AO41" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE41" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BG41" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
         <v>2.5</v>
       </c>
       <c r="H42" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I42" t="n">
         <v>3.15</v>
@@ -8571,10 +8571,10 @@
         <v>1.66</v>
       </c>
       <c r="X42" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y42" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z42" t="n">
         <v>22</v>
@@ -8622,10 +8622,10 @@
         <v>17.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP42" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ42" t="n">
         <v>13</v>
@@ -8670,17 +8670,17 @@
         <v>30</v>
       </c>
       <c r="BE42" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BF42" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG42" t="n">
         <v>25</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G43" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H43" t="n">
         <v>3.4</v>
       </c>
       <c r="I43" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
@@ -8729,13 +8729,13 @@
         <v>3.6</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M43" t="n">
         <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
         <v>1.35</v>
@@ -8756,13 +8756,13 @@
         <v>1.81</v>
       </c>
       <c r="U43" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V43" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W43" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X43" t="n">
         <v>14.5</v>
@@ -8798,7 +8798,7 @@
         <v>22</v>
       </c>
       <c r="AI43" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ43" t="n">
         <v>36</v>
@@ -8825,7 +8825,7 @@
         <v>10.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AS43" t="n">
         <v>4.8</v>
@@ -8843,7 +8843,7 @@
         <v>4.8</v>
       </c>
       <c r="AX43" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AY43" t="n">
         <v>9.4</v>
@@ -8855,13 +8855,13 @@
         <v>4.8</v>
       </c>
       <c r="BB43" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE43" t="n">
         <v>4.9</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -8911,10 +8911,10 @@
         <v>2.6</v>
       </c>
       <c r="H44" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I44" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J44" t="n">
         <v>3.6</v>
@@ -8992,7 +8992,7 @@
         <v>16.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ44" t="n">
         <v>38</v>
@@ -9004,7 +9004,7 @@
         <v>38</v>
       </c>
       <c r="AM44" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN44" t="n">
         <v>21</v>
@@ -9028,7 +9028,7 @@
         <v>10.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV44" t="n">
         <v>11.5</v>
@@ -9061,21 +9061,21 @@
         <v>50</v>
       </c>
       <c r="BF44" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG44" t="n">
         <v>23</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9085,191 +9085,191 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G45" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="H45" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="I45" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K45" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AT45" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9279,191 +9279,191 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medel</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Internacional de Bogot</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="G46" t="n">
-        <v>1.5</v>
+        <v>2.54</v>
       </c>
       <c r="H46" t="n">
-        <v>8.4</v>
+        <v>3.65</v>
       </c>
       <c r="I46" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M46" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="O46" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="P46" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.79</v>
+        <v>2.34</v>
       </c>
       <c r="R46" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="U46" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="V46" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="W46" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="X46" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="Z46" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="AA46" t="n">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="AB46" t="n">
         <v>9.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD46" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AE46" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AF46" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>10</v>
       </c>
-      <c r="AG46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>260</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AR46" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AS46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC46" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT46" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BD46" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG46" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9473,378 +9473,766 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Atletico Nacional Medel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Internacional de Bogot</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="G47" t="n">
-        <v>1000</v>
+        <v>1.53</v>
       </c>
       <c r="H47" t="n">
-        <v>1.02</v>
+        <v>8</v>
       </c>
       <c r="I47" t="n">
-        <v>990</v>
+        <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="K47" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N47" t="n">
-        <v>1.24</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P47" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="R47" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V47" t="n">
         <v>1.11</v>
       </c>
-      <c r="U47" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Olancho</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I48" t="n">
+        <v>990</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K48" t="n">
+        <v>950</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>2026-05-11 05:23:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G49" t="n">
+        <v>990</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I49" t="n">
+        <v>990</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K49" t="n">
+        <v>950</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH49" t="inlineStr">
+        <is>
+          <t>2026-05-11 05:23:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>America de Cali S.A</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F50" t="n">
         <v>2.12</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G50" t="n">
         <v>2.4</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H50" t="n">
         <v>3.55</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I50" t="n">
         <v>4.3</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J50" t="n">
         <v>3.15</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K50" t="n">
         <v>3.65</v>
       </c>
-      <c r="L48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="L50" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M50" t="n">
         <v>1.09</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N50" t="n">
         <v>3</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O50" t="n">
         <v>1.41</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P50" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q50" t="n">
         <v>2.18</v>
       </c>
-      <c r="R48" t="n">
+      <c r="R50" t="n">
         <v>1.25</v>
       </c>
-      <c r="S48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T48" t="n">
+      <c r="S50" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T50" t="n">
         <v>1.91</v>
       </c>
-      <c r="U48" t="n">
+      <c r="U50" t="n">
         <v>1.91</v>
       </c>
-      <c r="V48" t="n">
+      <c r="V50" t="n">
         <v>1.31</v>
       </c>
-      <c r="W48" t="n">
+      <c r="W50" t="n">
         <v>1.71</v>
       </c>
-      <c r="X48" t="n">
+      <c r="X50" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y50" t="n">
         <v>15</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="Z50" t="n">
         <v>34</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AA50" t="n">
         <v>85</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AB50" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AC50" t="n">
         <v>8</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AD50" t="n">
         <v>20</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AE50" t="n">
         <v>70</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AF50" t="n">
         <v>16</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AG50" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AH50" t="n">
         <v>25</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AI50" t="n">
         <v>85</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AJ50" t="n">
         <v>32</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AK50" t="n">
         <v>34</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AL50" t="n">
         <v>55</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AM50" t="n">
         <v>160</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AN50" t="n">
         <v>29</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AO50" t="n">
         <v>80</v>
       </c>
-      <c r="AP48" t="n">
+      <c r="AP50" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ48" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR48" t="n">
+      <c r="AQ50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR50" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AS50" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AT50" t="n">
         <v>7</v>
       </c>
-      <c r="AU48" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW48" t="n">
+      <c r="AU50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA50" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX48" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ48" t="n">
+      <c r="BB50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF50" t="n">
         <v>17</v>
       </c>
-      <c r="BA48" t="n">
+      <c r="BG50" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH48" t="inlineStr">
-        <is>
-          <t>2026-05-11 03:07:42</t>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.23</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>870</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
         <v>2.78</v>
@@ -960,7 +960,7 @@
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
@@ -981,22 +981,22 @@
         <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V3" t="n">
         <v>1.43</v>
@@ -1014,19 +1014,19 @@
         <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
         <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>17</v>
@@ -1035,31 +1035,31 @@
         <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.800000000000001</v>
@@ -1068,22 +1068,22 @@
         <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1092,29 +1092,29 @@
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE3" t="n">
         <v>9.6</v>
       </c>
-      <c r="BD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BF3" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
         <v>1.43</v>
@@ -1157,34 +1157,34 @@
         <v>1.45</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
         <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
         <v>1.97</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
         <v>2.32</v>
@@ -1199,73 +1199,73 @@
         <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z4" t="n">
         <v>7.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7.2</v>
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
         <v>16.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AH4" t="n">
         <v>34</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="AK4" t="n">
         <v>210</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM4" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP4" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU4" t="n">
         <v>10</v>
@@ -1274,22 +1274,22 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
         <v>34</v>
       </c>
       <c r="AY4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
         <v>27</v>
       </c>
       <c r="BB4" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BC4" t="n">
         <v>44</v>
@@ -1304,11 +1304,11 @@
         <v>95</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H5" t="n">
         <v>3.7</v>
@@ -1357,7 +1357,7 @@
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1366,10 +1366,10 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
         <v>2.32</v>
@@ -1381,16 +1381,16 @@
         <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X5" t="n">
         <v>11</v>
@@ -1402,10 +1402,10 @@
         <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
@@ -1414,7 +1414,7 @@
         <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
         <v>13.5</v>
@@ -1426,25 +1426,25 @@
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN5" t="n">
         <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
         <v>9.4</v>
@@ -1453,13 +1453,13 @@
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1468,41 +1468,41 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
         <v>9.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
         <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG5" t="n">
         <v>9.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>990</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J7" t="n">
         <v>2.88</v>
@@ -1748,19 +1748,19 @@
         <v>1.56</v>
       </c>
       <c r="M7" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R7" t="n">
         <v>1.16</v>
@@ -1775,10 +1775,10 @@
         <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
         <v>8.6</v>
@@ -1790,16 +1790,16 @@
         <v>17</v>
       </c>
       <c r="AA7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
         <v>48</v>
@@ -1808,10 +1808,10 @@
         <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
         <v>90</v>
@@ -1826,16 +1826,16 @@
         <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN7" t="n">
         <v>120</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
@@ -1844,7 +1844,7 @@
         <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
         <v>8.199999999999999</v>
@@ -1853,44 +1853,44 @@
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -1942,149 +1942,149 @@
         <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
         <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
         <v>210</v>
       </c>
       <c r="AN8" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
         <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.28</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2136,31 +2136,31 @@
         <v>1.21</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="T9" t="n">
         <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
         <v>1.04</v>
@@ -2169,13 +2169,13 @@
         <v>5.3</v>
       </c>
       <c r="X9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Z9" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2184,19 +2184,19 @@
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
         <v>55</v>
@@ -2217,7 +2217,7 @@
         <v>270</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO9" t="n">
         <v>580</v>
@@ -2226,28 +2226,28 @@
         <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV9" t="n">
         <v>4.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY9" t="n">
         <v>9.4</v>
@@ -2256,29 +2256,29 @@
         <v>4.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD9" t="n">
         <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.44</v>
@@ -2333,58 +2333,58 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC10" t="n">
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2396,10 +2396,10 @@
         <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="AQ10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.92</v>
-      </c>
       <c r="BE10" t="n">
-        <v>1.97</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.34</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G11" t="n">
         <v>600</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="I11" t="n">
         <v>870</v>
@@ -2518,7 +2518,7 @@
         <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
         <v>1.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G13" t="n">
         <v>1.45</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
         <v>990</v>
@@ -2906,7 +2906,7 @@
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,16 +2915,16 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -2942,13 +2942,13 @@
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,10 +2957,10 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -2969,10 +2969,10 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
@@ -2981,10 +2981,10 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
@@ -2993,68 +2993,68 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G14" t="n">
         <v>3.2</v>
@@ -3097,37 +3097,37 @@
         <v>2.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
         <v>2.14</v>
@@ -3139,10 +3139,10 @@
         <v>1.45</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
         <v>21</v>
@@ -3151,25 +3151,25 @@
         <v>46</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>14.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AF14" t="n">
         <v>25</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>48</v>
@@ -3178,10 +3178,10 @@
         <v>60</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
@@ -3193,62 +3193,62 @@
         <v>27</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="AY14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
         <v>4</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BB14" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3306,143 +3306,143 @@
         <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15</v>
-      </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
       </c>
       <c r="AN15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV15" t="n">
         <v>12</v>
       </c>
-      <c r="AR15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>13</v>
-      </c>
       <c r="AW15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>3.25</v>
       </c>
       <c r="H16" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L16" t="n">
         <v>1.46</v>
@@ -3497,52 +3497,52 @@
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O16" t="n">
         <v>1.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U16" t="n">
         <v>1.86</v>
       </c>
       <c r="V16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
         <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>15</v>
@@ -3551,28 +3551,28 @@
         <v>46</v>
       </c>
       <c r="AF16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="n">
         <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN16" t="n">
         <v>55</v>
@@ -3581,16 +3581,16 @@
         <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
         <v>8</v>
@@ -3602,41 +3602,41 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
         <v>3.65</v>
@@ -3685,28 +3685,28 @@
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
         <v>1.44</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q17" t="n">
         <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
         <v>1.94</v>
@@ -3715,10 +3715,10 @@
         <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -3727,19 +3727,19 @@
         <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
         <v>60</v>
@@ -3754,13 +3754,13 @@
         <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
         <v>44</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AL17" t="n">
         <v>65</v>
@@ -3769,22 +3769,22 @@
         <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO17" t="n">
         <v>70</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3793,10 +3793,10 @@
         <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="AX17" t="n">
         <v>10.5</v>
@@ -3808,29 +3808,29 @@
         <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
         <v>21</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G18" t="n">
         <v>1.93</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.4</v>
@@ -3903,49 +3903,49 @@
         <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
         <v>2.06</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
         <v>180</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
         <v>110</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
         <v>120</v>
@@ -3957,28 +3957,28 @@
         <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
@@ -3990,7 +3990,7 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AX18" t="n">
         <v>9</v>
@@ -4002,29 +4002,29 @@
         <v>19.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BB18" t="n">
         <v>18</v>
       </c>
       <c r="BC18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G19" t="n">
         <v>2.46</v>
@@ -4067,7 +4067,7 @@
         <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
         <v>3.45</v>
@@ -4088,10 +4088,10 @@
         <v>1.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -4106,31 +4106,31 @@
         <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -4139,10 +4139,10 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
         <v>38</v>
@@ -4151,74 +4151,74 @@
         <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="AR19" t="n">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.8</v>
+        <v>3.75</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AZ19" t="n">
         <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5.5</v>
       </c>
-      <c r="BE19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -4273,13 +4273,13 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
         <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
         <v>1.17</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
         <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,7 +4467,7 @@
         <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.23</v>
@@ -4476,7 +4476,7 @@
         <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="R21" t="n">
         <v>1.5</v>
@@ -4533,7 +4533,7 @@
         <v>70</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AK21" t="n">
         <v>970</v>
@@ -4551,62 +4551,62 @@
         <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AQ21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT21" t="n">
         <v>4</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AU21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BA21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD21" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4</v>
-      </c>
       <c r="BE21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
         <v>7.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
         <v>4.2</v>
@@ -4652,49 +4652,49 @@
         <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
         <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y22" t="n">
         <v>12.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>14</v>
       </c>
       <c r="Z22" t="n">
         <v>34</v>
@@ -4703,10 +4703,10 @@
         <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
         <v>17.5</v>
@@ -4721,7 +4721,7 @@
         <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
         <v>90</v>
@@ -4739,68 +4739,68 @@
         <v>170</v>
       </c>
       <c r="AN22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO22" t="n">
         <v>80</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW22" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY22" t="n">
         <v>5.1</v>
       </c>
-      <c r="AX22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>17.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>2.16</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I23" t="n">
         <v>4.2</v>
@@ -4864,19 +4864,19 @@
         <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V23" t="n">
         <v>1.31</v>
@@ -4909,7 +4909,7 @@
         <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
@@ -4921,10 +4921,10 @@
         <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL23" t="n">
         <v>40</v>
@@ -4933,22 +4933,22 @@
         <v>100</v>
       </c>
       <c r="AN23" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO23" t="n">
         <v>50</v>
       </c>
       <c r="AP23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ23" t="n">
         <v>13.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
         <v>9</v>
@@ -4960,41 +4960,41 @@
         <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AX23" t="n">
         <v>11.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
         <v>2.24</v>
@@ -5040,10 +5040,10 @@
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -5079,10 +5079,10 @@
         <v>1.8</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z24" t="n">
         <v>32</v>
@@ -5094,25 +5094,25 @@
         <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF24" t="n">
         <v>16.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
         <v>32</v>
@@ -5127,22 +5127,22 @@
         <v>100</v>
       </c>
       <c r="AN24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
         <v>13</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT24" t="n">
         <v>9.199999999999999</v>
@@ -5154,41 +5154,41 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AX24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY24" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF24" t="n">
         <v>11.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -5237,7 +5237,7 @@
         <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -5267,7 +5267,7 @@
         <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W25" t="n">
         <v>2.16</v>
@@ -5279,7 +5279,7 @@
         <v>18.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA25" t="n">
         <v>110</v>
@@ -5327,10 +5327,10 @@
         <v>60</v>
       </c>
       <c r="AP25" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
         <v>32</v>
@@ -5351,7 +5351,7 @@
         <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
@@ -5360,7 +5360,7 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
@@ -5378,11 +5378,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5419,25 +5419,25 @@
         <v>1.54</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
         <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.2</v>
@@ -5446,7 +5446,7 @@
         <v>2.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="R26" t="n">
         <v>1.57</v>
@@ -5455,16 +5455,16 @@
         <v>2.48</v>
       </c>
       <c r="T26" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
         <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X26" t="n">
         <v>950</v>
@@ -5500,7 +5500,7 @@
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="n">
         <v>970</v>
@@ -5512,71 +5512,71 @@
         <v>36</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.64</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.62</v>
+        <v>4.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC26" t="n">
         <v>11</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>1.65</v>
       </c>
       <c r="G27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I27" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="J27" t="n">
         <v>3.4</v>
@@ -5631,25 +5631,25 @@
         <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>1.52</v>
       </c>
       <c r="P27" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
         <v>1.6</v>
@@ -5658,40 +5658,40 @@
         <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X27" t="n">
         <v>10.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
         <v>70</v>
       </c>
       <c r="AA27" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AB27" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE27" t="n">
         <v>190</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI27" t="n">
         <v>200</v>
@@ -5700,19 +5700,19 @@
         <v>21</v>
       </c>
       <c r="AK27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL27" t="n">
         <v>75</v>
       </c>
       <c r="AM27" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AP27" t="n">
         <v>7.8</v>
@@ -5721,22 +5721,22 @@
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AT27" t="n">
         <v>5.1</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AX27" t="n">
         <v>7.2</v>
@@ -5748,7 +5748,7 @@
         <v>5.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -5757,20 +5757,20 @@
         <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BF27" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5995,94 +5995,94 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H29" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="J29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
         <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="T29" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U29" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W29" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="X29" t="n">
         <v>15.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AA29" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="n">
         <v>29</v>
@@ -6094,71 +6094,71 @@
         <v>42</v>
       </c>
       <c r="AM29" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN29" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AP29" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS29" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AT29" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="AU29" t="n">
         <v>6.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA29" t="n">
         <v>5</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BB29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD29" t="n">
         <v>4.7</v>
       </c>
-      <c r="AZ29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE29" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G30" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H30" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I30" t="n">
         <v>3.05</v>
       </c>
       <c r="J30" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
         <v>4.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
         <v>1.03</v>
@@ -6222,13 +6222,13 @@
         <v>2.34</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="R30" t="n">
         <v>1.54</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T30" t="n">
         <v>1.54</v>
@@ -6237,10 +6237,10 @@
         <v>2.48</v>
       </c>
       <c r="V30" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W30" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="X30" t="n">
         <v>950</v>
@@ -6255,7 +6255,7 @@
         <v>44</v>
       </c>
       <c r="AB30" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC30" t="n">
         <v>11</v>
@@ -6264,22 +6264,22 @@
         <v>15</v>
       </c>
       <c r="AE30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
         <v>970</v>
       </c>
       <c r="AI30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK30" t="n">
         <v>30</v>
@@ -6297,62 +6297,62 @@
         <v>970</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="AU30" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX30" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY30" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB30" t="n">
         <v>4.6</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE30" t="n">
         <v>4.7</v>
       </c>
       <c r="BF30" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BG30" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>5.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
@@ -6410,7 +6410,7 @@
         <v>3.45</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P31" t="n">
         <v>1.83</v>
@@ -6419,19 +6419,19 @@
         <v>1.97</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="T31" t="n">
         <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="W31" t="n">
         <v>1.07</v>
@@ -6461,7 +6461,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG31" t="n">
         <v>950</v>
@@ -6470,7 +6470,7 @@
         <v>950</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ31" t="n">
         <v>1000</v>
@@ -6491,62 +6491,62 @@
         <v>970</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AT31" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AX31" t="n">
-        <v>5.8</v>
+        <v>3.15</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="BE31" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="BF31" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6577,25 +6577,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G32" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="H32" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J32" t="n">
         <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -6604,61 +6604,61 @@
         <v>3.95</v>
       </c>
       <c r="O32" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="T32" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="U32" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W32" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X32" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y32" t="n">
         <v>15</v>
       </c>
       <c r="Z32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA32" t="n">
         <v>55</v>
       </c>
       <c r="AB32" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE32" t="n">
         <v>38</v>
       </c>
       <c r="AF32" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH32" t="n">
         <v>19</v>
@@ -6667,7 +6667,7 @@
         <v>48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK32" t="n">
         <v>32</v>
@@ -6685,62 +6685,62 @@
         <v>32</v>
       </c>
       <c r="AP32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR32" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AS32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX32" t="n">
         <v>4</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AY32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB32" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW32" t="n">
+      <c r="BC32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE32" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="BF32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG32" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>20</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G33" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="H33" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J33" t="n">
         <v>3.75</v>
@@ -6789,13 +6789,13 @@
         <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>1.15</v>
@@ -6807,7 +6807,7 @@
         <v>1.51</v>
       </c>
       <c r="R33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S33" t="n">
         <v>2.12</v>
@@ -6819,10 +6819,10 @@
         <v>2.8</v>
       </c>
       <c r="V33" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W33" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="X33" t="n">
         <v>950</v>
@@ -6879,10 +6879,10 @@
         <v>17</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR33" t="n">
         <v>4.4</v>
@@ -6891,7 +6891,7 @@
         <v>4.7</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AU33" t="n">
         <v>8.800000000000001</v>
@@ -6903,13 +6903,13 @@
         <v>4.4</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY33" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BA33" t="n">
         <v>4.5</v>
@@ -6918,7 +6918,7 @@
         <v>4.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD33" t="n">
         <v>4.4</v>
@@ -6927,14 +6927,14 @@
         <v>4.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG33" t="n">
         <v>11</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>1.67</v>
       </c>
       <c r="G34" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H34" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I34" t="n">
         <v>5.9</v>
@@ -6989,49 +6989,49 @@
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S34" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="T34" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U34" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V34" t="n">
         <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X34" t="n">
         <v>20</v>
       </c>
       <c r="Y34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z34" t="n">
         <v>46</v>
       </c>
       <c r="AA34" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC34" t="n">
         <v>9.6</v>
@@ -7043,13 +7043,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG34" t="n">
         <v>9.6</v>
       </c>
       <c r="AH34" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI34" t="n">
         <v>70</v>
@@ -7067,13 +7067,13 @@
         <v>95</v>
       </c>
       <c r="AN34" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO34" t="n">
         <v>75</v>
       </c>
       <c r="AP34" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>20</v>
@@ -7094,10 +7094,10 @@
         <v>19.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY34" t="n">
         <v>9.199999999999999</v>
@@ -7115,20 +7115,20 @@
         <v>14.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF34" t="n">
         <v>7.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>4</v>
@@ -7183,7 +7183,7 @@
         <v>1.03</v>
       </c>
       <c r="N35" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O35" t="n">
         <v>1.19</v>
@@ -7198,7 +7198,7 @@
         <v>1.61</v>
       </c>
       <c r="S35" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="T35" t="n">
         <v>1.57</v>
@@ -7210,34 +7210,34 @@
         <v>1.31</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X35" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Y35" t="n">
         <v>26</v>
       </c>
       <c r="Z35" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA35" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB35" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC35" t="n">
         <v>12.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE35" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF35" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AG35" t="n">
         <v>13.5</v>
@@ -7249,80 +7249,80 @@
         <v>50</v>
       </c>
       <c r="AJ35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK35" t="n">
         <v>22</v>
       </c>
       <c r="AL35" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AM35" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN35" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT35" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU35" t="n">
         <v>9</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AY35" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BC35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.88</v>
       </c>
       <c r="G36" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H36" t="n">
         <v>4</v>
@@ -7368,88 +7368,88 @@
         <v>3.95</v>
       </c>
       <c r="K36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M36" t="n">
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>2.32</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P36" t="n">
         <v>2.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V36" t="n">
         <v>1.29</v>
       </c>
       <c r="W36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z36" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA36" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK36" t="n">
         <v>21</v>
       </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>22</v>
-      </c>
       <c r="AL36" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM36" t="n">
         <v>85</v>
@@ -7458,65 +7458,65 @@
         <v>11</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.35</v>
+        <v>16.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.35</v>
+        <v>16</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.31</v>
+        <v>4.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.33</v>
+        <v>4.7</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.35</v>
+        <v>7.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.27</v>
+        <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.35</v>
+        <v>10.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.35</v>
+        <v>9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.35</v>
+        <v>12.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.35</v>
+        <v>4.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.27</v>
+        <v>13.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.3</v>
+        <v>21</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.33</v>
+        <v>4.7</v>
       </c>
       <c r="BF36" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.35</v>
+        <v>4.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7550,16 +7550,16 @@
         <v>1.54</v>
       </c>
       <c r="G37" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H37" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I37" t="n">
         <v>6</v>
       </c>
       <c r="J37" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K37" t="n">
         <v>5.6</v>
@@ -7577,49 +7577,49 @@
         <v>1.13</v>
       </c>
       <c r="P37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R37" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S37" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="T37" t="n">
         <v>1.54</v>
       </c>
       <c r="U37" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V37" t="n">
         <v>1.2</v>
       </c>
       <c r="W37" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X37" t="n">
         <v>40</v>
       </c>
       <c r="Y37" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Z37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA37" t="n">
         <v>180</v>
       </c>
       <c r="AB37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE37" t="n">
         <v>60</v>
@@ -7637,7 +7637,7 @@
         <v>55</v>
       </c>
       <c r="AJ37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK37" t="n">
         <v>14</v>
@@ -7652,7 +7652,7 @@
         <v>4.7</v>
       </c>
       <c r="AO37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP37" t="n">
         <v>30</v>
@@ -7661,13 +7661,13 @@
         <v>30</v>
       </c>
       <c r="AR37" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU37" t="n">
         <v>12</v>
@@ -7676,22 +7676,22 @@
         <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX37" t="n">
         <v>12.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ37" t="n">
         <v>15.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB37" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC37" t="n">
         <v>12.5</v>
@@ -7700,17 +7700,17 @@
         <v>18</v>
       </c>
       <c r="BE37" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG37" t="n">
         <v>25</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7744,13 +7744,13 @@
         <v>1.74</v>
       </c>
       <c r="G38" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H38" t="n">
         <v>4.5</v>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -7759,13 +7759,13 @@
         <v>4.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.24</v>
@@ -7777,10 +7777,10 @@
         <v>1.69</v>
       </c>
       <c r="R38" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S38" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T38" t="n">
         <v>1.71</v>
@@ -7789,7 +7789,7 @@
         <v>2.22</v>
       </c>
       <c r="V38" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W38" t="n">
         <v>2.16</v>
@@ -7831,7 +7831,7 @@
         <v>60</v>
       </c>
       <c r="AJ38" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="n">
         <v>18</v>
@@ -7855,7 +7855,7 @@
         <v>17.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="AS38" t="n">
         <v>9.6</v>
@@ -7870,7 +7870,7 @@
         <v>16.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX38" t="n">
         <v>10.5</v>
@@ -7882,7 +7882,7 @@
         <v>15.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB38" t="n">
         <v>16.5</v>
@@ -7891,20 +7891,20 @@
         <v>15</v>
       </c>
       <c r="BD38" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE38" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF38" t="n">
         <v>7</v>
       </c>
       <c r="BG38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -7947,13 +7947,13 @@
         <v>4.4</v>
       </c>
       <c r="J39" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K39" t="n">
         <v>4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M39" t="n">
         <v>1.06</v>
@@ -7965,22 +7965,22 @@
         <v>1.28</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T39" t="n">
         <v>1.72</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.7</v>
-      </c>
       <c r="U39" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V39" t="n">
         <v>1.29</v>
@@ -7989,19 +7989,19 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA39" t="n">
         <v>100</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC39" t="n">
         <v>9</v>
@@ -8019,10 +8019,10 @@
         <v>13</v>
       </c>
       <c r="AH39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI39" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ39" t="n">
         <v>28</v>
@@ -8031,7 +8031,7 @@
         <v>25</v>
       </c>
       <c r="AL39" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM39" t="n">
         <v>100</v>
@@ -8040,7 +8040,7 @@
         <v>13</v>
       </c>
       <c r="AO39" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP39" t="n">
         <v>14</v>
@@ -8049,10 +8049,10 @@
         <v>13.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT39" t="n">
         <v>8.6</v>
@@ -8064,7 +8064,7 @@
         <v>14</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX39" t="n">
         <v>11</v>
@@ -8076,29 +8076,29 @@
         <v>14.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB39" t="n">
         <v>19.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -8129,25 +8129,25 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G40" t="n">
         <v>3.35</v>
       </c>
       <c r="H40" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J40" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K40" t="n">
         <v>3.7</v>
       </c>
       <c r="L40" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M40" t="n">
         <v>1.08</v>
@@ -8159,10 +8159,10 @@
         <v>1.35</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R40" t="n">
         <v>1.3</v>
@@ -8171,16 +8171,16 @@
         <v>3.25</v>
       </c>
       <c r="T40" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U40" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V40" t="n">
         <v>1.53</v>
       </c>
       <c r="W40" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X40" t="n">
         <v>15.5</v>
@@ -8219,7 +8219,7 @@
         <v>55</v>
       </c>
       <c r="AJ40" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK40" t="n">
         <v>44</v>
@@ -8237,37 +8237,37 @@
         <v>34</v>
       </c>
       <c r="AP40" t="n">
-        <v>9.4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ40" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="AR40" t="n">
-        <v>12.5</v>
+        <v>3.55</v>
       </c>
       <c r="AS40" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT40" t="n">
-        <v>9.4</v>
+        <v>3.25</v>
       </c>
       <c r="AU40" t="n">
-        <v>5.8</v>
+        <v>2.94</v>
       </c>
       <c r="AV40" t="n">
-        <v>9</v>
+        <v>3.35</v>
       </c>
       <c r="AW40" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AX40" t="n">
-        <v>14.5</v>
+        <v>3.65</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="AZ40" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="BA40" t="n">
         <v>4</v>
@@ -8276,7 +8276,7 @@
         <v>4</v>
       </c>
       <c r="BC40" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BD40" t="n">
         <v>4</v>
@@ -8285,14 +8285,14 @@
         <v>4.2</v>
       </c>
       <c r="BF40" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BG40" t="n">
-        <v>20</v>
+        <v>3.85</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -8323,64 +8323,64 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G41" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H41" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K41" t="n">
         <v>3.75</v>
       </c>
-      <c r="J41" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L41" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M41" t="n">
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q41" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U41" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V41" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W41" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z41" t="n">
         <v>26</v>
@@ -8389,13 +8389,13 @@
         <v>65</v>
       </c>
       <c r="AB41" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE41" t="n">
         <v>42</v>
@@ -8404,34 +8404,34 @@
         <v>15</v>
       </c>
       <c r="AG41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI41" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ41" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK41" t="n">
         <v>29</v>
       </c>
-      <c r="AK41" t="n">
-        <v>24</v>
-      </c>
       <c r="AL41" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM41" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN41" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AO41" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AP41" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ41" t="n">
         <v>12</v>
@@ -8440,22 +8440,22 @@
         <v>21</v>
       </c>
       <c r="AS41" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AT41" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU41" t="n">
         <v>7.2</v>
       </c>
       <c r="AV41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX41" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>13</v>
       </c>
       <c r="AY41" t="n">
         <v>9.800000000000001</v>
@@ -8464,29 +8464,29 @@
         <v>15</v>
       </c>
       <c r="BA41" t="n">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC41" t="n">
         <v>18.5</v>
       </c>
       <c r="BD41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG41" t="n">
         <v>9.4</v>
       </c>
-      <c r="BE41" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>27</v>
-      </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -8541,28 +8541,28 @@
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S42" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T42" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U42" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V42" t="n">
         <v>1.46</v>
@@ -8574,7 +8574,7 @@
         <v>16</v>
       </c>
       <c r="Y42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z42" t="n">
         <v>22</v>
@@ -8583,13 +8583,13 @@
         <v>65</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC42" t="n">
         <v>8</v>
       </c>
       <c r="AD42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE42" t="n">
         <v>32</v>
@@ -8601,7 +8601,7 @@
         <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI42" t="n">
         <v>44</v>
@@ -8613,28 +8613,28 @@
         <v>24</v>
       </c>
       <c r="AL42" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM42" t="n">
         <v>75</v>
       </c>
       <c r="AN42" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ42" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR42" t="n">
         <v>20</v>
       </c>
       <c r="AS42" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT42" t="n">
         <v>11.5</v>
@@ -8646,19 +8646,19 @@
         <v>12</v>
       </c>
       <c r="AW42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX42" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY42" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB42" t="n">
         <v>30</v>
@@ -8667,20 +8667,20 @@
         <v>22</v>
       </c>
       <c r="BD42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE42" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BF42" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -8714,16 +8714,16 @@
         <v>2.18</v>
       </c>
       <c r="G43" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H43" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K43" t="n">
         <v>3.6</v>
@@ -8738,7 +8738,7 @@
         <v>3.35</v>
       </c>
       <c r="O43" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P43" t="n">
         <v>1.79</v>
@@ -8753,16 +8753,16 @@
         <v>3.7</v>
       </c>
       <c r="T43" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U43" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W43" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X43" t="n">
         <v>14.5</v>
@@ -8777,13 +8777,13 @@
         <v>85</v>
       </c>
       <c r="AB43" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE43" t="n">
         <v>55</v>
@@ -8819,62 +8819,62 @@
         <v>60</v>
       </c>
       <c r="AP43" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR43" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="AS43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF43" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT43" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BG43" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -8905,25 +8905,25 @@
         </is>
       </c>
       <c r="F44" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G44" t="n">
         <v>2.56</v>
       </c>
-      <c r="G44" t="n">
-        <v>2.6</v>
-      </c>
       <c r="H44" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I44" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K44" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L44" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M44" t="n">
         <v>1.06</v>
@@ -8935,7 +8935,7 @@
         <v>1.29</v>
       </c>
       <c r="P44" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q44" t="n">
         <v>1.88</v>
@@ -8953,13 +8953,13 @@
         <v>2.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X44" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y44" t="n">
         <v>13</v>
@@ -8968,7 +8968,7 @@
         <v>21</v>
       </c>
       <c r="AA44" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB44" t="n">
         <v>12</v>
@@ -8983,58 +8983,58 @@
         <v>32</v>
       </c>
       <c r="AF44" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI44" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ44" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK44" t="n">
         <v>27</v>
       </c>
       <c r="AL44" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM44" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN44" t="n">
         <v>21</v>
       </c>
       <c r="AO44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT44" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR44" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV44" t="n">
         <v>11.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AX44" t="n">
         <v>16</v>
@@ -9043,32 +9043,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA44" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB44" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BC44" t="n">
         <v>24</v>
       </c>
       <c r="BD44" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE44" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BF44" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG44" t="n">
         <v>23</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -9111,10 +9111,10 @@
         <v>3.7</v>
       </c>
       <c r="J45" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K45" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q45" t="n">
         <v>2.32</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -9293,19 +9293,19 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G46" t="n">
         <v>2.54</v>
       </c>
       <c r="H46" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K46" t="n">
         <v>3.15</v>
@@ -9317,7 +9317,7 @@
         <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O46" t="n">
         <v>1.45</v>
@@ -9341,10 +9341,10 @@
         <v>1.92</v>
       </c>
       <c r="V46" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W46" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X46" t="n">
         <v>11.5</v>
@@ -9356,22 +9356,22 @@
         <v>28</v>
       </c>
       <c r="AA46" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB46" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC46" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD46" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE46" t="n">
         <v>60</v>
       </c>
       <c r="AF46" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG46" t="n">
         <v>14</v>
@@ -9398,19 +9398,19 @@
         <v>36</v>
       </c>
       <c r="AO46" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP46" t="n">
         <v>9</v>
       </c>
       <c r="AQ46" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR46" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT46" t="n">
         <v>7.4</v>
@@ -9419,44 +9419,44 @@
         <v>6.2</v>
       </c>
       <c r="AV46" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC46" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX46" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF46" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE46" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG46" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -9490,19 +9490,19 @@
         <v>1.43</v>
       </c>
       <c r="G47" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="J47" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="K47" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,34 +9511,34 @@
         <v>1.05</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O47" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P47" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T47" t="n">
         <v>2.04</v>
       </c>
       <c r="U47" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V47" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W47" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="X47" t="n">
         <v>18.5</v>
@@ -9595,10 +9595,10 @@
         <v>250</v>
       </c>
       <c r="AP47" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AQ47" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AR47" t="n">
         <v>5.1</v>
@@ -9607,13 +9607,13 @@
         <v>5.3</v>
       </c>
       <c r="AT47" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AU47" t="n">
-        <v>9.4</v>
+        <v>3.85</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AW47" t="n">
         <v>5.3</v>
@@ -9622,10 +9622,10 @@
         <v>7.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AZ47" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BA47" t="n">
         <v>5.2</v>
@@ -9634,23 +9634,23 @@
         <v>3.95</v>
       </c>
       <c r="BC47" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD47" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE47" t="n">
         <v>5.2</v>
       </c>
       <c r="BF47" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="BG47" t="n">
         <v>5.3</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
         <v>1.18</v>
       </c>
       <c r="S48" t="n">
-        <v>1.05</v>
+        <v>1.9</v>
       </c>
       <c r="T48" t="n">
         <v>1.11</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -9875,28 +9875,28 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="G49" t="n">
-        <v>990</v>
+        <v>1.89</v>
       </c>
       <c r="H49" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="I49" t="n">
-        <v>990</v>
+        <v>7.2</v>
       </c>
       <c r="J49" t="n">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K49" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -9905,10 +9905,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -9917,10 +9917,10 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -9929,116 +9929,116 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y49" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z49" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA49" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB49" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF49" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH49" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI49" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK49" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL49" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM49" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN49" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO49" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -10069,16 +10069,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="H50" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>3.15</v>
@@ -10102,7 +10102,7 @@
         <v>1.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R50" t="n">
         <v>1.25</v>
@@ -10111,16 +10111,16 @@
         <v>4.1</v>
       </c>
       <c r="T50" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U50" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V50" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W50" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="X50" t="n">
         <v>13.5</v>
@@ -10132,13 +10132,13 @@
         <v>34</v>
       </c>
       <c r="AA50" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB50" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC50" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD50" t="n">
         <v>20</v>
@@ -10147,7 +10147,7 @@
         <v>70</v>
       </c>
       <c r="AF50" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG50" t="n">
         <v>13.5</v>
@@ -10159,7 +10159,7 @@
         <v>85</v>
       </c>
       <c r="AJ50" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK50" t="n">
         <v>34</v>
@@ -10177,62 +10177,62 @@
         <v>80</v>
       </c>
       <c r="AP50" t="n">
-        <v>9.4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ50" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AT50" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="AU50" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="AV50" t="n">
-        <v>14</v>
+        <v>3.6</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AX50" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AY50" t="n">
-        <v>9.4</v>
+        <v>3.35</v>
       </c>
       <c r="AZ50" t="n">
-        <v>17</v>
+        <v>3.65</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BB50" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BE50" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BF50" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="BG50" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH50"/>
+  <dimension ref="A1:BH51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
         <v>2.78</v>
@@ -960,7 +960,7 @@
         <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
@@ -999,7 +999,7 @@
         <v>1.91</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
         <v>1.56</v>
@@ -1020,19 +1020,19 @@
         <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>21</v>
@@ -1044,7 +1044,7 @@
         <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
         <v>70</v>
@@ -1068,19 +1068,19 @@
         <v>17.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
         <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>14.5</v>
@@ -1095,26 +1095,26 @@
         <v>9</v>
       </c>
       <c r="BB3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC3" t="n">
         <v>9</v>
       </c>
-      <c r="BC3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF3" t="n">
         <v>9</v>
       </c>
-      <c r="BE3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
         <v>1.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1172,28 +1172,28 @@
         <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
         <v>1.97</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
         <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="W4" t="n">
         <v>1.11</v>
@@ -1205,13 +1205,13 @@
         <v>7.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
@@ -1226,31 +1226,31 @@
         <v>90</v>
       </c>
       <c r="AG4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="AK4" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AL4" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN4" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
         <v>13.5</v>
@@ -1259,19 +1259,19 @@
         <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
         <v>10.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU4" t="n">
         <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
         <v>15</v>
@@ -1280,35 +1280,35 @@
         <v>34</v>
       </c>
       <c r="AY4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ4" t="n">
         <v>27</v>
       </c>
       <c r="BA4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
         <v>55</v>
       </c>
       <c r="BC4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD4" t="n">
         <v>44</v>
       </c>
       <c r="BE4" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BG4" t="n">
         <v>7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>2.3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
         <v>3.95</v>
@@ -1381,7 +1381,7 @@
         <v>4.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
         <v>1.93</v>
@@ -1429,7 +1429,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1441,7 +1441,7 @@
         <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
         <v>75</v>
@@ -1459,7 +1459,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
         <v>1.24</v>
@@ -1569,10 +1569,10 @@
         <v>1.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1587,58 +1587,58 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
         <v>2.88</v>
@@ -1745,22 +1745,22 @@
         <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
         <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.16</v>
@@ -1769,16 +1769,16 @@
         <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>8.6</v>
@@ -1787,22 +1787,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB7" t="n">
         <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
         <v>28</v>
@@ -1811,58 +1811,58 @@
         <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
         <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM7" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AN7" t="n">
         <v>120</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
         <v>5.3</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
         <v>20</v>
@@ -1871,26 +1871,26 @@
         <v>5.6</v>
       </c>
       <c r="BB7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -1942,7 +1942,7 @@
         <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
         <v>2.7</v>
@@ -1954,7 +1954,7 @@
         <v>1.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
@@ -1963,13 +1963,13 @@
         <v>4.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
         <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
         <v>1.7</v>
@@ -1993,10 +1993,10 @@
         <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>15.5</v>
@@ -2005,13 +2005,13 @@
         <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
         <v>38</v>
@@ -2020,7 +2020,7 @@
         <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
         <v>38</v>
@@ -2029,62 +2029,62 @@
         <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BE8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2133,10 +2133,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
         <v>6.4</v>
@@ -2145,22 +2145,22 @@
         <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
         <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
         <v>1.04</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
         <v>23</v>
@@ -2199,7 +2199,7 @@
         <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI9" t="n">
         <v>280</v>
@@ -2229,7 +2229,7 @@
         <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
         <v>4.7</v>
@@ -2241,10 +2241,10 @@
         <v>16.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX9" t="n">
         <v>7.4</v>
@@ -2256,7 +2256,7 @@
         <v>4.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
         <v>7.8</v>
@@ -2265,10 +2265,10 @@
         <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF9" t="n">
         <v>2.76</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2339,16 +2339,16 @@
         <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
         <v>1.98</v>
@@ -2363,19 +2363,19 @@
         <v>1.92</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>140</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
         <v>970</v>
@@ -2399,7 +2399,7 @@
         <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
         <v>27</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="BF10" t="n">
-        <v>16</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>600</v>
       </c>
       <c r="H11" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
         <v>870</v>
@@ -2518,7 +2518,7 @@
         <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="G13" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="I13" t="n">
         <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>70</v>
@@ -2924,13 +2924,13 @@
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -2939,19 +2939,19 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="X13" t="n">
         <v>95</v>
       </c>
       <c r="Y13" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -2960,101 +2960,101 @@
         <v>36</v>
       </c>
       <c r="AC13" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD13" t="n">
         <v>14.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3085,52 +3085,52 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I14" t="n">
         <v>2.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
         <v>1.62</v>
@@ -3139,28 +3139,28 @@
         <v>1.45</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
         <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
         <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
         <v>25</v>
@@ -3172,7 +3172,7 @@
         <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
         <v>60</v>
@@ -3187,68 +3187,68 @@
         <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
         <v>12.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
         <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY14" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
       </c>
       <c r="BC14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD14" t="n">
         <v>3.95</v>
       </c>
-      <c r="BD14" t="n">
-        <v>4</v>
-      </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
         <v>21</v>
       </c>
       <c r="BG14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3279,49 +3279,49 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
@@ -3336,13 +3336,13 @@
         <v>19.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
         <v>12</v>
@@ -3351,10 +3351,10 @@
         <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
         <v>16.5</v>
@@ -3363,19 +3363,19 @@
         <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
         <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
         <v>110</v>
@@ -3384,10 +3384,10 @@
         <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP15" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>11.5</v>
@@ -3396,53 +3396,53 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4</v>
-      </c>
       <c r="AX15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD15" t="n">
         <v>4</v>
       </c>
-      <c r="BB15" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG15" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2.88</v>
       </c>
       <c r="G16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H16" t="n">
         <v>2.7</v>
@@ -3485,10 +3485,10 @@
         <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.46</v>
@@ -3497,34 +3497,34 @@
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U16" t="n">
         <v>1.86</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W16" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
         <v>11.5</v>
@@ -3548,7 +3548,7 @@
         <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF16" t="n">
         <v>23</v>
@@ -3575,7 +3575,7 @@
         <v>170</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO16" t="n">
         <v>48</v>
@@ -3584,28 +3584,28 @@
         <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX16" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>10.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3679,13 +3679,13 @@
         <v>3.65</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
         <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
@@ -3700,19 +3700,19 @@
         <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
         <v>3.85</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
@@ -3769,19 +3769,19 @@
         <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO17" t="n">
         <v>70</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
         <v>4</v>
@@ -3790,16 +3790,16 @@
         <v>7.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
@@ -3814,13 +3814,13 @@
         <v>4.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF17" t="n">
         <v>21</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G18" t="n">
         <v>1.93</v>
@@ -3870,13 +3870,13 @@
         <v>4.9</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
         <v>1.4</v>
@@ -3885,7 +3885,7 @@
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
         <v>1.41</v>
@@ -3894,7 +3894,7 @@
         <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
@@ -3903,10 +3903,10 @@
         <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
         <v>1.2</v>
@@ -3930,10 +3930,10 @@
         <v>8.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>110</v>
@@ -3942,7 +3942,7 @@
         <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>28</v>
@@ -3954,7 +3954,7 @@
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
@@ -3963,22 +3963,22 @@
         <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>160</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT18" t="n">
         <v>6.2</v>
@@ -3990,41 +3990,41 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC18" t="n">
         <v>19</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>2.46</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
         <v>3.45</v>
@@ -4091,7 +4091,7 @@
         <v>2.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -4103,7 +4103,7 @@
         <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
         <v>1.69</v>
@@ -4124,13 +4124,13 @@
         <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>17.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -4163,62 +4163,62 @@
         <v>60</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>6.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
         <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE19" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="G21" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4485,16 +4485,16 @@
         <v>2.68</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X21" t="n">
         <v>25</v>
@@ -4521,13 +4521,13 @@
         <v>75</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
         <v>70</v>
@@ -4545,68 +4545,68 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AO21" t="n">
         <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU21" t="n">
         <v>4</v>
       </c>
-      <c r="AU21" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AV21" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BA21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD21" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
         <v>3.75</v>
@@ -4652,7 +4652,7 @@
         <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.42</v>
@@ -4682,13 +4682,13 @@
         <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
         <v>10.5</v>
@@ -4745,16 +4745,16 @@
         <v>80</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
         <v>7</v>
@@ -4763,44 +4763,44 @@
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE22" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD22" t="n">
+      <c r="BF22" t="n">
         <v>6</v>
       </c>
-      <c r="BE22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H23" t="n">
         <v>3.65</v>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.3</v>
@@ -4864,25 +4864,25 @@
         <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
@@ -4975,7 +4975,7 @@
         <v>3.95</v>
       </c>
       <c r="BB23" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>17.5</v>
@@ -4987,14 +4987,14 @@
         <v>4</v>
       </c>
       <c r="BF23" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG23" t="n">
         <v>3.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
         <v>1.06</v>
@@ -5133,7 +5133,7 @@
         <v>46</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
         <v>13</v>
@@ -5154,7 +5154,7 @@
         <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>32</v>
+        <v>5.3</v>
       </c>
       <c r="AX24" t="n">
         <v>12.5</v>
@@ -5166,13 +5166,13 @@
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>5.3</v>
       </c>
       <c r="BB24" t="n">
         <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>17</v>
+        <v>5.7</v>
       </c>
       <c r="BD24" t="n">
         <v>5.9</v>
@@ -5181,14 +5181,14 @@
         <v>5.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG24" t="n">
         <v>5.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G25" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H25" t="n">
         <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -5267,10 +5267,10 @@
         <v>2.18</v>
       </c>
       <c r="V25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X25" t="n">
         <v>16.5</v>
@@ -5288,7 +5288,7 @@
         <v>9.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
         <v>18.5</v>
@@ -5327,10 +5327,10 @@
         <v>60</v>
       </c>
       <c r="AP25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>32</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
         <v>1.2</v>
@@ -5446,7 +5446,7 @@
         <v>2.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
         <v>1.57</v>
@@ -5458,7 +5458,7 @@
         <v>1.8</v>
       </c>
       <c r="U26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V26" t="n">
         <v>1.13</v>
@@ -5515,68 +5515,68 @@
         <v>120</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AO26" t="n">
         <v>120</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV26" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AW26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC26" t="n">
         <v>11</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BG26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>6.8</v>
       </c>
       <c r="I27" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>3.4</v>
@@ -5655,7 +5655,7 @@
         <v>1.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W27" t="n">
         <v>2.28</v>
@@ -5676,7 +5676,7 @@
         <v>6.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
         <v>36</v>
@@ -5685,7 +5685,7 @@
         <v>190</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG27" t="n">
         <v>13</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT27" t="n">
         <v>5.1</v>
@@ -5733,10 +5733,10 @@
         <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX27" t="n">
         <v>7.2</v>
@@ -5745,10 +5745,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -5757,20 +5757,20 @@
         <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF27" t="n">
         <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
         <v>1.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P28" t="n">
         <v>1.24</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H29" t="n">
         <v>4.2</v>
       </c>
       <c r="I29" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>3.35</v>
@@ -6016,7 +6016,7 @@
         <v>1.34</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
         <v>3.6</v>
@@ -6028,16 +6028,16 @@
         <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R29" t="n">
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U29" t="n">
         <v>2.1</v>
@@ -6070,7 +6070,7 @@
         <v>20</v>
       </c>
       <c r="AE29" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF29" t="n">
         <v>15.5</v>
@@ -6106,7 +6106,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR29" t="n">
         <v>4.7</v>
@@ -6145,20 +6145,20 @@
         <v>4.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG29" t="n">
         <v>5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H30" t="n">
         <v>2.48</v>
@@ -6201,7 +6201,7 @@
         <v>3.05</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K30" t="n">
         <v>4.3</v>
@@ -6213,7 +6213,7 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
         <v>1.2</v>
@@ -6228,13 +6228,13 @@
         <v>1.54</v>
       </c>
       <c r="S30" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="U30" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="V30" t="n">
         <v>1.49</v>
@@ -6246,49 +6246,49 @@
         <v>950</v>
       </c>
       <c r="Y30" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA30" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB30" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AC30" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF30" t="n">
         <v>29</v>
       </c>
-      <c r="AF30" t="n">
-        <v>25</v>
-      </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>970</v>
       </c>
       <c r="AI30" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL30" t="n">
         <v>46</v>
       </c>
-      <c r="AK30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>38</v>
-      </c>
       <c r="AM30" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
         <v>970</v>
@@ -6297,62 +6297,62 @@
         <v>970</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.2</v>
+        <v>1.87</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.95</v>
+        <v>2.12</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.95</v>
+        <v>2.06</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.75</v>
+        <v>1.82</v>
       </c>
       <c r="AV30" t="n">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.3</v>
+        <v>1.99</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.2</v>
+        <v>1.76</v>
       </c>
       <c r="AY30" t="n">
-        <v>3.95</v>
+        <v>2.18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.6</v>
+        <v>2.04</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.7</v>
+        <v>1.87</v>
       </c>
       <c r="BF30" t="n">
-        <v>4</v>
+        <v>1.88</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.95</v>
+        <v>1.88</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6386,13 +6386,13 @@
         <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="H31" t="n">
         <v>1.38</v>
       </c>
       <c r="I31" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="J31" t="n">
         <v>4.4</v>
@@ -6401,7 +6401,7 @@
         <v>5.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
@@ -6422,16 +6422,16 @@
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
         <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="W31" t="n">
         <v>1.07</v>
@@ -6440,10 +6440,10 @@
         <v>970</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AA31" t="n">
         <v>970</v>
@@ -6491,62 +6491,62 @@
         <v>970</v>
       </c>
       <c r="AP31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX31" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AY31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>4.9</v>
       </c>
-      <c r="AZ31" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB31" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6580,10 +6580,10 @@
         <v>2.44</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="H32" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="I32" t="n">
         <v>3.15</v>
@@ -6592,10 +6592,10 @@
         <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -6604,7 +6604,7 @@
         <v>3.95</v>
       </c>
       <c r="O32" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P32" t="n">
         <v>2</v>
@@ -6616,19 +6616,19 @@
         <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U32" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V32" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W32" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X32" t="n">
         <v>18.5</v>
@@ -6652,10 +6652,10 @@
         <v>15.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG32" t="n">
         <v>14</v>
@@ -6676,7 +6676,7 @@
         <v>44</v>
       </c>
       <c r="AM32" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN32" t="n">
         <v>23</v>
@@ -6685,62 +6685,62 @@
         <v>32</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB32" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB32" t="n">
+      <c r="BC32" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC32" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G33" t="n">
         <v>2.58</v>
       </c>
       <c r="H33" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I33" t="n">
         <v>3.15</v>
@@ -6789,7 +6789,7 @@
         <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
@@ -6801,13 +6801,13 @@
         <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q33" t="n">
         <v>1.51</v>
       </c>
       <c r="R33" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S33" t="n">
         <v>2.12</v>
@@ -6819,7 +6819,7 @@
         <v>2.8</v>
       </c>
       <c r="V33" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W33" t="n">
         <v>1.63</v>
@@ -6834,7 +6834,7 @@
         <v>32</v>
       </c>
       <c r="AA33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB33" t="n">
         <v>21</v>
@@ -6882,16 +6882,16 @@
         <v>4.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS33" t="n">
         <v>4.7</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU33" t="n">
         <v>8.800000000000001</v>
@@ -6909,7 +6909,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA33" t="n">
         <v>4.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.67</v>
       </c>
-      <c r="G34" t="n">
-        <v>1.69</v>
-      </c>
       <c r="H34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I34" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
         <v>4.3</v>
@@ -6983,7 +6983,7 @@
         <v>4.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M34" t="n">
         <v>1.05</v>
@@ -6998,7 +6998,7 @@
         <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R34" t="n">
         <v>1.51</v>
@@ -7016,7 +7016,7 @@
         <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X34" t="n">
         <v>20</v>
@@ -7025,16 +7025,16 @@
         <v>23</v>
       </c>
       <c r="Z34" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA34" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB34" t="n">
         <v>10.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD34" t="n">
         <v>22</v>
@@ -7043,19 +7043,19 @@
         <v>75</v>
       </c>
       <c r="AF34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH34" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI34" t="n">
         <v>70</v>
       </c>
       <c r="AJ34" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK34" t="n">
         <v>16</v>
@@ -7067,7 +7067,7 @@
         <v>95</v>
       </c>
       <c r="AN34" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO34" t="n">
         <v>75</v>
@@ -7097,7 +7097,7 @@
         <v>32</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY34" t="n">
         <v>9.199999999999999</v>
@@ -7121,14 +7121,14 @@
         <v>36</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG34" t="n">
         <v>34</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7162,10 +7162,10 @@
         <v>1.89</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I35" t="n">
         <v>4.2</v>
@@ -7198,10 +7198,10 @@
         <v>1.61</v>
       </c>
       <c r="S35" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="T35" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U35" t="n">
         <v>2.48</v>
@@ -7210,7 +7210,7 @@
         <v>1.31</v>
       </c>
       <c r="W35" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>32</v>
@@ -7219,7 +7219,7 @@
         <v>26</v>
       </c>
       <c r="Z35" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA35" t="n">
         <v>90</v>
@@ -7234,7 +7234,7 @@
         <v>21</v>
       </c>
       <c r="AE35" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF35" t="n">
         <v>18</v>
@@ -7249,7 +7249,7 @@
         <v>50</v>
       </c>
       <c r="AJ35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK35" t="n">
         <v>22</v>
@@ -7267,10 +7267,10 @@
         <v>36</v>
       </c>
       <c r="AP35" t="n">
-        <v>18</v>
+        <v>3.7</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.65</v>
+        <v>15</v>
       </c>
       <c r="AR35" t="n">
         <v>3.8</v>
@@ -7279,10 +7279,10 @@
         <v>4</v>
       </c>
       <c r="AT35" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AV35" t="n">
         <v>12</v>
@@ -7291,10 +7291,10 @@
         <v>3.9</v>
       </c>
       <c r="AX35" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ35" t="n">
         <v>11.5</v>
@@ -7315,14 +7315,14 @@
         <v>4</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG35" t="n">
         <v>21</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7377,13 +7377,13 @@
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O36" t="n">
         <v>1.22</v>
       </c>
       <c r="P36" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q36" t="n">
         <v>1.56</v>
@@ -7392,7 +7392,7 @@
         <v>1.53</v>
       </c>
       <c r="S36" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
         <v>1.64</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
         <v>1.39</v>
       </c>
       <c r="R37" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S37" t="n">
         <v>1.96</v>
@@ -7592,7 +7592,7 @@
         <v>1.54</v>
       </c>
       <c r="U37" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V37" t="n">
         <v>1.2</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7744,16 +7744,16 @@
         <v>1.74</v>
       </c>
       <c r="G38" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H38" t="n">
         <v>4.5</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K38" t="n">
         <v>4.5</v>
@@ -7780,10 +7780,10 @@
         <v>1.49</v>
       </c>
       <c r="S38" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T38" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U38" t="n">
         <v>2.22</v>
@@ -7897,14 +7897,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG38" t="n">
         <v>8.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
         <v>3.65</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L39" t="n">
         <v>1.31</v>
@@ -7968,10 +7968,10 @@
         <v>2.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S39" t="n">
         <v>3.05</v>
@@ -8094,11 +8094,11 @@
         <v>11</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -8132,61 +8132,61 @@
         <v>2.86</v>
       </c>
       <c r="G40" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H40" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J40" t="n">
         <v>2.86</v>
       </c>
-      <c r="J40" t="n">
-        <v>2.84</v>
-      </c>
       <c r="K40" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M40" t="n">
         <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>1.35</v>
       </c>
       <c r="P40" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>2.02</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="T40" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U40" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V40" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W40" t="n">
         <v>1.42</v>
       </c>
       <c r="X40" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y40" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z40" t="n">
         <v>21</v>
@@ -8195,7 +8195,7 @@
         <v>50</v>
       </c>
       <c r="AB40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC40" t="n">
         <v>9.199999999999999</v>
@@ -8219,7 +8219,7 @@
         <v>55</v>
       </c>
       <c r="AJ40" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK40" t="n">
         <v>44</v>
@@ -8228,71 +8228,71 @@
         <v>60</v>
       </c>
       <c r="AM40" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN40" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO40" t="n">
         <v>34</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AQ40" t="n">
         <v>3.2</v>
       </c>
       <c r="AR40" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AS40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW40" t="n">
         <v>3.95</v>
       </c>
-      <c r="AT40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AX40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>3.65</v>
       </c>
-      <c r="AY40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BA40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC40" t="n">
         <v>4</v>
       </c>
-      <c r="BB40" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE40" t="n">
         <v>4.2</v>
       </c>
       <c r="BF40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG40" t="n">
         <v>3.9</v>
       </c>
-      <c r="BG40" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -8335,10 +8335,10 @@
         <v>3.7</v>
       </c>
       <c r="J41" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K41" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.36</v>
@@ -8353,19 +8353,19 @@
         <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R41" t="n">
         <v>1.36</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U41" t="n">
         <v>2.12</v>
@@ -8380,7 +8380,7 @@
         <v>16</v>
       </c>
       <c r="Y41" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z41" t="n">
         <v>26</v>
@@ -8389,7 +8389,7 @@
         <v>65</v>
       </c>
       <c r="AB41" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC41" t="n">
         <v>8.199999999999999</v>
@@ -8443,7 +8443,7 @@
         <v>7</v>
       </c>
       <c r="AT41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU41" t="n">
         <v>7.2</v>
@@ -8452,7 +8452,7 @@
         <v>13</v>
       </c>
       <c r="AW41" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX41" t="n">
         <v>12.5</v>
@@ -8467,33 +8467,33 @@
         <v>6.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC41" t="n">
         <v>18.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE41" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF41" t="n">
         <v>15</v>
       </c>
       <c r="BG41" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>English Sky Bet Championship</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8508,186 +8508,186 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G42" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H42" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I42" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K42" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L42" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="O42" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R42" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="S42" t="n">
-        <v>2.98</v>
+        <v>1.05</v>
       </c>
       <c r="T42" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>2.4</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>English Sky Bet Championship</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8702,186 +8702,186 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="G43" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="H43" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="I43" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="J43" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K43" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L43" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="M43" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="O43" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="P43" t="n">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="S43" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="T43" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="V43" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W43" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="X43" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AA43" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB43" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AC43" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP43" t="n">
         <v>16</v>
       </c>
-      <c r="AE43" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH43" t="n">
+      <c r="AQ43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG43" t="n">
         <v>22</v>
       </c>
-      <c r="AI43" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,191 +8891,191 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.54</v>
+        <v>2.18</v>
       </c>
       <c r="G44" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="H44" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="J44" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K44" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L44" t="n">
         <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="P44" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="R44" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S44" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T44" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="U44" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V44" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="W44" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="X44" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD44" t="n">
         <v>16</v>
       </c>
-      <c r="Y44" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA44" t="n">
+      <c r="AE44" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL44" t="n">
         <v>48</v>
       </c>
-      <c r="AB44" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>36</v>
-      </c>
       <c r="AM44" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AN44" t="n">
         <v>21</v>
       </c>
       <c r="AO44" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AP44" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS44" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT44" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AU44" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV44" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW44" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="AX44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ44" t="n">
         <v>16</v>
       </c>
-      <c r="AY44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>15</v>
-      </c>
       <c r="BA44" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BB44" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="BC44" t="n">
-        <v>24</v>
+        <v>6.8</v>
       </c>
       <c r="BD44" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="BF44" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BG44" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9085,191 +9085,191 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H45" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="I45" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J45" t="n">
         <v>3.7</v>
       </c>
-      <c r="J45" t="n">
-        <v>2.96</v>
-      </c>
       <c r="K45" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P45" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9279,191 +9279,191 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sao Bernardo</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G46" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="H46" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J46" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="K46" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="R46" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9473,191 +9473,191 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medel</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Internacional de Bogot</t>
+          <t>Sao Bernardo</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.43</v>
+        <v>2.42</v>
       </c>
       <c r="G47" t="n">
-        <v>1.56</v>
+        <v>2.56</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="I47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S47" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X47" t="n">
         <v>11.5</v>
       </c>
-      <c r="J47" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K47" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W47" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="X47" t="n">
-        <v>18.5</v>
-      </c>
       <c r="Y47" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="Z47" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="AA47" t="n">
-        <v>380</v>
+        <v>85</v>
       </c>
       <c r="AB47" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC47" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD47" t="n">
-        <v>38</v>
+        <v>17.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="AF47" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP47" t="n">
         <v>9</v>
       </c>
-      <c r="AG47" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AQ47" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR47" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS47" t="n">
         <v>5.3</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AW47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA47" t="n">
         <v>5.3</v>
       </c>
-      <c r="AX47" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA47" t="n">
+      <c r="BB47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD47" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE47" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG47" t="n">
         <v>5.3</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9667,191 +9667,191 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Atletico Nacional Medel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Internacional de Bogot</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="G48" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="I48" t="n">
-        <v>990</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K48" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N48" t="n">
-        <v>1.25</v>
+        <v>3.95</v>
       </c>
       <c r="O48" t="n">
         <v>1.27</v>
       </c>
       <c r="P48" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S48" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="T48" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
         <v>1.11</v>
       </c>
       <c r="V48" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W48" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y48" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z48" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA48" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD48" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE48" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF48" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI48" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK48" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL48" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM48" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN48" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO48" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9861,191 +9861,191 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
-        <v>1.89</v>
+        <v>1000</v>
       </c>
       <c r="H49" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="I49" t="n">
-        <v>7.2</v>
+        <v>990</v>
       </c>
       <c r="J49" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="K49" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P49" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.44</v>
+        <v>1.27</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T49" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U49" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z49" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD49" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE49" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF49" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG49" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH49" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI49" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ49" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK49" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL49" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN49" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR49" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT49" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AV49" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX49" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AY49" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10055,184 +10055,378 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="G50" t="n">
-        <v>2.58</v>
+        <v>1.92</v>
       </c>
       <c r="H50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I50" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J50" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I50" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.15</v>
       </c>
       <c r="K50" t="n">
         <v>3.65</v>
       </c>
       <c r="L50" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="U50" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="V50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="Y50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z50" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AA50" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="AB50" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AC50" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AE50" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL50" t="n">
         <v>70</v>
       </c>
-      <c r="AF50" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>55</v>
-      </c>
       <c r="AM50" t="n">
-        <v>160</v>
+        <v>310</v>
       </c>
       <c r="AN50" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AO50" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR50" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT50" t="n">
         <v>3.1</v>
       </c>
       <c r="AU50" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AV50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>2026-05-11 09:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X51" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV51" t="n">
         <v>3.6</v>
       </c>
-      <c r="AW50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB50" t="n">
+      <c r="AW51" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF51" t="n">
         <v>3.85</v>
       </c>
-      <c r="BC50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH50" t="inlineStr">
-        <is>
-          <t>2026-05-11 07:38:53</t>
+      <c r="BG51" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G2" t="n">
         <v>4.3</v>
@@ -766,7 +766,7 @@
         <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -775,13 +775,13 @@
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
         <v>1.36</v>
@@ -790,7 +790,7 @@
         <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>1.29</v>
@@ -805,64 +805,64 @@
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
         <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
         <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
@@ -898,29 +898,29 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
@@ -975,43 +975,43 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.46</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA3" t="n">
         <v>70</v>
@@ -1020,25 +1020,25 @@
         <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="AJ3" t="n">
         <v>55</v>
@@ -1047,10 +1047,10 @@
         <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>44</v>
@@ -1062,13 +1062,13 @@
         <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1077,44 +1077,44 @@
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
         <v>14.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="G4" t="n">
         <v>10.5</v>
@@ -1166,31 +1166,31 @@
         <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
         <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
         <v>3.3</v>
@@ -1199,25 +1199,25 @@
         <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
         <v>16.5</v>
@@ -1226,7 +1226,7 @@
         <v>90</v>
       </c>
       <c r="AG4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AH4" t="n">
         <v>32</v>
@@ -1235,25 +1235,25 @@
         <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AO4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>6.8</v>
@@ -1271,13 +1271,13 @@
         <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
         <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1286,29 +1286,29 @@
         <v>27</v>
       </c>
       <c r="BA4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB4" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BC4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BD4" t="n">
         <v>44</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF4" t="n">
         <v>55</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>2.3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -1357,7 +1357,7 @@
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1372,7 +1372,7 @@
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1384,16 +1384,16 @@
         <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
         <v>11.5</v>
@@ -1408,25 +1408,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
         <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>280</v>
+        <v>130</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="AJ5" t="n">
         <v>32</v>
@@ -1438,13 +1438,13 @@
         <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
         <v>9.4</v>
@@ -1453,10 +1453,10 @@
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AT5" t="n">
         <v>7.2</v>
@@ -1468,31 +1468,31 @@
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
         <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC5" t="n">
         <v>19</v>
       </c>
-      <c r="BC5" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD5" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BF5" t="n">
         <v>21</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
         <v>12.5</v>
@@ -1542,7 +1542,7 @@
         <v>1.39</v>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
@@ -1557,7 +1557,7 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.34</v>
@@ -1581,7 +1581,7 @@
         <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
@@ -1599,7 +1599,7 @@
         <v>14</v>
       </c>
       <c r="AB6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AC6" t="n">
         <v>13</v>
@@ -1641,37 +1641,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
         <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
         <v>7.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY6" t="n">
         <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.3</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
         <v>5.1</v>
@@ -1680,23 +1680,23 @@
         <v>5.6</v>
       </c>
       <c r="BC6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD6" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
         <v>3.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G7" t="n">
         <v>3.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K7" t="n">
         <v>3.1</v>
@@ -1748,16 +1748,16 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
         <v>2.88</v>
@@ -1775,7 +1775,7 @@
         <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.34</v>
@@ -1790,7 +1790,7 @@
         <v>15.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AB7" t="n">
         <v>10.5</v>
@@ -1802,7 +1802,7 @@
         <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
         <v>28</v>
@@ -1814,28 +1814,28 @@
         <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
@@ -1850,22 +1850,22 @@
         <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
         <v>20</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA7" t="n">
         <v>5.7</v>
@@ -1880,7 +1880,7 @@
         <v>5.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
         <v>5.8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
         <v>3.8</v>
@@ -1945,7 +1945,7 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
         <v>1.52</v>
@@ -1969,22 +1969,22 @@
         <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>8.6</v>
@@ -1996,7 +1996,7 @@
         <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
         <v>15.5</v>
@@ -2008,25 +2008,25 @@
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
         <v>8</v>
@@ -2035,10 +2035,10 @@
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2047,44 +2047,44 @@
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB8" t="n">
         <v>30</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="BE8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF8" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF8" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>1.23</v>
       </c>
       <c r="H9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
         <v>25</v>
@@ -2130,10 +2130,10 @@
         <v>7.4</v>
       </c>
       <c r="K9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
@@ -2148,16 +2148,16 @@
         <v>2.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
         <v>1.68</v>
@@ -2190,10 +2190,10 @@
         <v>85</v>
       </c>
       <c r="AE9" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9" t="n">
         <v>15</v>
@@ -2202,7 +2202,7 @@
         <v>55</v>
       </c>
       <c r="AI9" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AJ9" t="n">
         <v>10.5</v>
@@ -2214,25 +2214,25 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AO9" t="n">
         <v>630</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AT9" t="n">
         <v>7.8</v>
@@ -2241,10 +2241,10 @@
         <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AX9" t="n">
         <v>7.2</v>
@@ -2253,10 +2253,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB9" t="n">
         <v>7.8</v>
@@ -2265,20 +2265,20 @@
         <v>10.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
         <v>3.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
         <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.44</v>
@@ -2333,16 +2333,16 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
         <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
@@ -2351,128 +2351,128 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AI10" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB10" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB10" t="n">
-        <v>6</v>
-      </c>
       <c r="BC10" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.25</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I11" t="n">
         <v>2.86</v>
@@ -2518,7 +2518,7 @@
         <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>1.29</v>
@@ -2536,7 +2536,7 @@
         <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.43</v>
@@ -2545,19 +2545,19 @@
         <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
         <v>2.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W11" t="n">
         <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
         <v>15.5</v>
@@ -2566,19 +2566,19 @@
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AB11" t="n">
         <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
         <v>24</v>
@@ -2590,19 +2590,19 @@
         <v>19.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AM11" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>27</v>
@@ -2620,7 +2620,7 @@
         <v>13</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="AT11" t="n">
         <v>10</v>
@@ -2644,19 +2644,19 @@
         <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BC11" t="n">
         <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BF11" t="n">
         <v>16</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
         <v>5.6</v>
@@ -2712,7 +2712,7 @@
         <v>2.94</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,16 +2721,16 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="O12" t="n">
         <v>1.07</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -2748,119 +2748,119 @@
         <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>2.04</v>
       </c>
       <c r="G13" t="n">
-        <v>990</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I13" t="n">
-        <v>990</v>
+        <v>13.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2924,7 +2924,7 @@
         <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
@@ -2939,122 +2939,122 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="G14" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
@@ -3109,124 +3109,124 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="X14" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y14" t="n">
         <v>950</v>
       </c>
-      <c r="Y14" t="n">
-        <v>95</v>
-      </c>
       <c r="Z14" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AA14" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD14" t="n">
         <v>40</v>
       </c>
-      <c r="AC14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>32</v>
-      </c>
       <c r="AE14" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="AF14" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AK14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL14" t="n">
         <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AP14" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BB14" t="n">
         <v>7</v>
@@ -3235,20 +3235,20 @@
         <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G15" t="n">
         <v>2.84</v>
@@ -3291,10 +3291,10 @@
         <v>2.96</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.26</v>
@@ -3306,7 +3306,7 @@
         <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
         <v>2.24</v>
@@ -3324,7 +3324,7 @@
         <v>1.51</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V15" t="n">
         <v>1.51</v>
@@ -3339,110 +3339,110 @@
         <v>18.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AN15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO15" t="n">
         <v>17</v>
       </c>
-      <c r="AO15" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AP15" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU15" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AV15" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="G16" t="n">
         <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3503,7 +3503,7 @@
         <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q16" t="n">
         <v>1.01</v>
@@ -3521,13 +3521,13 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
         <v>1000</v>
@@ -3536,7 +3536,7 @@
         <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>1000</v>
@@ -3629,14 +3629,14 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3670,22 @@
         <v>2.82</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I17" t="n">
         <v>2.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3700,10 +3700,10 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
         <v>3.1</v>
@@ -3715,7 +3715,7 @@
         <v>2.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W17" t="n">
         <v>1.46</v>
@@ -3724,16 +3724,16 @@
         <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
         <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC17" t="n">
         <v>9.6</v>
@@ -3742,31 +3742,31 @@
         <v>14.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
         <v>26</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
         <v>40</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AM17" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>32</v>
@@ -3781,16 +3781,16 @@
         <v>9.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
         <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
         <v>9.800000000000001</v>
@@ -3808,19 +3808,19 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF17" t="n">
         <v>21</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
         <v>2.16</v>
@@ -3894,16 +3894,16 @@
         <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
         <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
         <v>2.22</v>
@@ -3915,22 +3915,22 @@
         <v>1.86</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
         <v>29</v>
       </c>
       <c r="AA18" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>17</v>
@@ -3948,7 +3948,7 @@
         <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
@@ -3960,7 +3960,7 @@
         <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN18" t="n">
         <v>13</v>
@@ -4011,7 +4011,7 @@
         <v>17</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BE18" t="n">
         <v>7.2</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="I19" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4085,10 +4085,10 @@
         <v>1.47</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
         <v>1.24</v>
@@ -4100,70 +4100,70 @@
         <v>1.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AA19" t="n">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC19" t="n">
         <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="AK19" t="n">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO19" t="n">
         <v>46</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AQ19" t="n">
         <v>7</v>
@@ -4172,10 +4172,10 @@
         <v>13.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
@@ -4184,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="AX19" t="n">
         <v>14.5</v>
@@ -4193,32 +4193,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
         <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
@@ -4282,7 +4282,7 @@
         <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
@@ -4291,22 +4291,22 @@
         <v>4.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y20" t="n">
         <v>13</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>13.5</v>
       </c>
       <c r="Z20" t="n">
         <v>28</v>
@@ -4315,13 +4315,13 @@
         <v>85</v>
       </c>
       <c r="AB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC20" t="n">
-        <v>9</v>
-      </c>
       <c r="AD20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>60</v>
@@ -4336,7 +4336,7 @@
         <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ20" t="n">
         <v>44</v>
@@ -4348,7 +4348,7 @@
         <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>36</v>
@@ -4366,7 +4366,7 @@
         <v>16.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -4378,7 +4378,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
@@ -4390,29 +4390,29 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB20" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB20" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD20" t="n">
         <v>4.2</v>
       </c>
-      <c r="BD20" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BE20" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
         <v>21</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.81</v>
       </c>
       <c r="G21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H21" t="n">
         <v>5</v>
@@ -4455,10 +4455,10 @@
         <v>5.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L21" t="n">
         <v>1.4</v>
@@ -4482,7 +4482,7 @@
         <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
         <v>2.02</v>
@@ -4497,7 +4497,7 @@
         <v>2.12</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
         <v>18</v>
@@ -4506,7 +4506,7 @@
         <v>50</v>
       </c>
       <c r="AA21" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB21" t="n">
         <v>8.4</v>
@@ -4515,22 +4515,22 @@
         <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AE21" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AJ21" t="n">
         <v>25</v>
@@ -4542,13 +4542,13 @@
         <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP21" t="n">
         <v>9.800000000000001</v>
@@ -4557,10 +4557,10 @@
         <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT21" t="n">
         <v>6.2</v>
@@ -4569,44 +4569,44 @@
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
         <v>19.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB21" t="n">
         <v>18</v>
       </c>
       <c r="BC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD21" t="n">
         <v>5.3</v>
       </c>
-      <c r="BD21" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF21" t="n">
         <v>14.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
         <v>2.42</v>
@@ -4652,7 +4652,7 @@
         <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
         <v>1.4</v>
@@ -4667,16 +4667,16 @@
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
         <v>1.85</v>
@@ -4685,13 +4685,13 @@
         <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
         <v>1.7</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y22" t="n">
         <v>14</v>
@@ -4736,7 +4736,7 @@
         <v>50</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>27</v>
@@ -4754,7 +4754,7 @@
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -4766,7 +4766,7 @@
         <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX22" t="n">
         <v>13</v>
@@ -4778,29 +4778,29 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF22" t="n">
         <v>18</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="G23" t="n">
         <v>1.56</v>
@@ -4840,13 +4840,13 @@
         <v>6.6</v>
       </c>
       <c r="I23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.25</v>
@@ -4855,10 +4855,10 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P23" t="n">
         <v>2.34</v>
@@ -4873,16 +4873,16 @@
         <v>2.48</v>
       </c>
       <c r="T23" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X23" t="n">
         <v>950</v>
@@ -4891,16 +4891,16 @@
         <v>950</v>
       </c>
       <c r="Z23" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD23" t="n">
         <v>950</v>
@@ -4912,55 +4912,55 @@
         <v>10.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH23" t="n">
         <v>970</v>
       </c>
       <c r="AI23" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK23" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL23" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AM23" t="n">
         <v>85</v>
       </c>
       <c r="AN23" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AO23" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AW23" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AX23" t="n">
         <v>6.8</v>
@@ -4969,32 +4969,32 @@
         <v>4.1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC23" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H24" t="n">
         <v>5.8</v>
@@ -5037,10 +5037,10 @@
         <v>6.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5070,28 +5070,28 @@
         <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X24" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="Y24" t="n">
         <v>26</v>
       </c>
       <c r="Z24" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AA24" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
         <v>12</v>
@@ -5100,7 +5100,7 @@
         <v>25</v>
       </c>
       <c r="AE24" t="n">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="AF24" t="n">
         <v>13</v>
@@ -5112,83 +5112,83 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AJ24" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AK24" t="n">
         <v>19</v>
       </c>
       <c r="AL24" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
         <v>8.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>75</v>
+        <v>700</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX24" t="n">
         <v>9.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H25" t="n">
         <v>3.9</v>
@@ -5231,7 +5231,7 @@
         <v>4.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K25" t="n">
         <v>3.25</v>
@@ -5249,10 +5249,10 @@
         <v>1.46</v>
       </c>
       <c r="P25" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
@@ -5270,10 +5270,10 @@
         <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y25" t="n">
         <v>12.5</v>
@@ -5282,7 +5282,7 @@
         <v>34</v>
       </c>
       <c r="AA25" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB25" t="n">
         <v>8</v>
@@ -5294,7 +5294,7 @@
         <v>17.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AF25" t="n">
         <v>13.5</v>
@@ -5303,31 +5303,31 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ25" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO25" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
         <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
@@ -5348,7 +5348,7 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -5360,29 +5360,29 @@
         <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
         <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
         <v>19</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="I26" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.32</v>
@@ -5437,34 +5437,34 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="X26" t="n">
         <v>19</v>
@@ -5476,10 +5476,10 @@
         <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC26" t="n">
         <v>9.6</v>
@@ -5488,37 +5488,37 @@
         <v>18</v>
       </c>
       <c r="AE26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ26" t="n">
         <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AM26" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AN26" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AP26" t="n">
         <v>14</v>
@@ -5530,10 +5530,10 @@
         <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26" t="n">
         <v>7.4</v>
@@ -5542,19 +5542,19 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BB26" t="n">
         <v>20</v>
@@ -5563,20 +5563,20 @@
         <v>17</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.4</v>
+        <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BF26" t="n">
         <v>11.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.86</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H27" t="n">
         <v>4.6</v>
@@ -5649,13 +5649,13 @@
         <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U27" t="n">
         <v>2.18</v>
       </c>
       <c r="V27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W27" t="n">
         <v>2.14</v>
@@ -5679,7 +5679,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
         <v>60</v>
@@ -5688,10 +5688,10 @@
         <v>11.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>60</v>
@@ -5712,7 +5712,7 @@
         <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
         <v>15.5</v>
@@ -5730,7 +5730,7 @@
         <v>9</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV27" t="n">
         <v>16.5</v>
@@ -5739,7 +5739,7 @@
         <v>50</v>
       </c>
       <c r="AX27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
@@ -5754,13 +5754,13 @@
         <v>18.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD27" t="n">
         <v>29</v>
       </c>
       <c r="BE27" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF27" t="n">
         <v>10</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>2.16</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I28" t="n">
         <v>4.1</v>
@@ -5831,7 +5831,7 @@
         <v>1.26</v>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
         <v>1.79</v>
@@ -5876,7 +5876,7 @@
         <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF28" t="n">
         <v>17</v>
@@ -5888,7 +5888,7 @@
         <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ28" t="n">
         <v>32</v>
@@ -5897,7 +5897,7 @@
         <v>26</v>
       </c>
       <c r="AL28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM28" t="n">
         <v>100</v>
@@ -5906,7 +5906,7 @@
         <v>16</v>
       </c>
       <c r="AO28" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP28" t="n">
         <v>14.5</v>
@@ -5918,7 +5918,7 @@
         <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT28" t="n">
         <v>9</v>
@@ -5930,7 +5930,7 @@
         <v>13.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
@@ -5942,7 +5942,7 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
@@ -5951,20 +5951,20 @@
         <v>17.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>6.8</v>
       </c>
       <c r="I29" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>4.7</v>
@@ -6013,13 +6013,13 @@
         <v>5.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>1.2</v>
@@ -6034,7 +6034,7 @@
         <v>1.58</v>
       </c>
       <c r="S29" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T29" t="n">
         <v>1.82</v>
@@ -6046,52 +6046,52 @@
         <v>1.13</v>
       </c>
       <c r="W29" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="X29" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="Y29" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="Z29" t="n">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC29" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AD29" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>390</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>26</v>
       </c>
-      <c r="AI29" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>970</v>
-      </c>
       <c r="AK29" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM29" t="n">
         <v>120</v>
@@ -6103,62 +6103,62 @@
         <v>130</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AS29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU29" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AV29" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY29" t="n">
         <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BC29" t="n">
         <v>11</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BG29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="G30" t="n">
         <v>1.78</v>
       </c>
       <c r="H30" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.49</v>
@@ -6213,7 +6213,7 @@
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>1.52</v>
@@ -6234,7 +6234,7 @@
         <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V30" t="n">
         <v>1.15</v>
@@ -6246,10 +6246,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y30" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AA30" t="n">
         <v>320</v>
@@ -6261,7 +6261,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AE30" t="n">
         <v>190</v>
@@ -6273,25 +6273,25 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AI30" t="n">
         <v>200</v>
       </c>
       <c r="AJ30" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AM30" t="n">
         <v>330</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
         <v>370</v>
@@ -6303,10 +6303,10 @@
         <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT30" t="n">
         <v>5.2</v>
@@ -6315,10 +6315,10 @@
         <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AX30" t="n">
         <v>7.2</v>
@@ -6327,10 +6327,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB30" t="n">
         <v>15</v>
@@ -6339,20 +6339,20 @@
         <v>20</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BF30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG30" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="G31" t="n">
         <v>990</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="I31" t="n">
         <v>990</v>
@@ -6398,7 +6398,7 @@
         <v>1.09</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6407,22 +6407,22 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O31" t="n">
         <v>1.08</v>
       </c>
       <c r="P31" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R31" t="n">
         <v>1.15</v>
       </c>
       <c r="S31" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -6437,7 +6437,7 @@
         <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I32" t="n">
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.17</v>
@@ -6601,7 +6601,7 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>1.35</v>
@@ -6628,10 +6628,10 @@
         <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y32" t="n">
         <v>15.5</v>
@@ -6640,7 +6640,7 @@
         <v>38</v>
       </c>
       <c r="AA32" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AB32" t="n">
         <v>10</v>
@@ -6652,7 +6652,7 @@
         <v>17.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF32" t="n">
         <v>15.5</v>
@@ -6664,34 +6664,34 @@
         <v>20</v>
       </c>
       <c r="AI32" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ32" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AK32" t="n">
         <v>25</v>
       </c>
       <c r="AL32" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM32" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO32" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP32" t="n">
         <v>11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR32" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="AS32" t="n">
         <v>5.8</v>
@@ -6703,44 +6703,44 @@
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA32" t="n">
         <v>5.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="BC32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD32" t="n">
         <v>28</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF32" t="n">
         <v>4.7</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         <v>3.05</v>
       </c>
       <c r="H33" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I33" t="n">
         <v>2.82</v>
@@ -6786,7 +6786,7 @@
         <v>3.4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.27</v>
@@ -6825,7 +6825,7 @@
         <v>1.49</v>
       </c>
       <c r="X33" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="Y33" t="n">
         <v>17</v>
@@ -6834,19 +6834,19 @@
         <v>23</v>
       </c>
       <c r="AA33" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AB33" t="n">
         <v>18</v>
       </c>
       <c r="AC33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AE33" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AF33" t="n">
         <v>25</v>
@@ -6855,22 +6855,22 @@
         <v>15.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AI33" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AK33" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="n">
-        <v>70</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
         <v>21</v>
@@ -6879,62 +6879,62 @@
         <v>18</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ33" t="n">
         <v>11</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="AT33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU33" t="n">
         <v>8</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AW33" t="n">
         <v>19</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY33" t="n">
         <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC33" t="n">
         <v>20</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF33" t="n">
         <v>13.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
         <v>14.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="I34" t="n">
         <v>1.42</v>
@@ -6983,7 +6983,7 @@
         <v>5.4</v>
       </c>
       <c r="L34" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M34" t="n">
         <v>1.07</v>
@@ -6992,16 +6992,16 @@
         <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P34" t="n">
         <v>1.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
         <v>3.45</v>
@@ -7010,10 +7010,10 @@
         <v>2.32</v>
       </c>
       <c r="U34" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="W34" t="n">
         <v>1.07</v>
@@ -7022,28 +7022,28 @@
         <v>970</v>
       </c>
       <c r="Y34" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z34" t="n">
         <v>970</v>
       </c>
-      <c r="Z34" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AA34" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AB34" t="n">
         <v>950</v>
       </c>
       <c r="AC34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="n">
         <v>970</v>
       </c>
-      <c r="AD34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>21</v>
-      </c>
       <c r="AF34" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AG34" t="n">
         <v>950</v>
@@ -7052,7 +7052,7 @@
         <v>950</v>
       </c>
       <c r="AI34" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ34" t="n">
         <v>1000</v>
@@ -7070,65 +7070,65 @@
         <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AQ34" t="n">
         <v>5.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.35</v>
+        <v>13</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB34" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="BG34" t="n">
         <v>6.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G35" t="n">
         <v>2.58</v>
@@ -7174,7 +7174,7 @@
         <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L35" t="n">
         <v>1.33</v>
@@ -7192,7 +7192,7 @@
         <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="R35" t="n">
         <v>1.39</v>
@@ -7219,13 +7219,13 @@
         <v>15</v>
       </c>
       <c r="Z35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AA35" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB35" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC35" t="n">
         <v>9.6</v>
@@ -7234,7 +7234,7 @@
         <v>15.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF35" t="n">
         <v>20</v>
@@ -7243,52 +7243,52 @@
         <v>14</v>
       </c>
       <c r="AH35" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AI35" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ35" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AK35" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL35" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM35" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AN35" t="n">
         <v>24</v>
       </c>
       <c r="AO35" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP35" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR35" t="n">
         <v>16</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT35" t="n">
         <v>10</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV35" t="n">
         <v>10</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX35" t="n">
         <v>13</v>
@@ -7297,32 +7297,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BC35" t="n">
         <v>20</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF35" t="n">
         <v>15</v>
       </c>
       <c r="BG35" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7353,31 +7353,31 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="G36" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H36" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I36" t="n">
         <v>3.2</v>
       </c>
       <c r="J36" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M36" t="n">
         <v>1.03</v>
       </c>
       <c r="N36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O36" t="n">
         <v>1.15</v>
@@ -7386,10 +7386,10 @@
         <v>2.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R36" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S36" t="n">
         <v>2.12</v>
@@ -7398,125 +7398,125 @@
         <v>1.44</v>
       </c>
       <c r="U36" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V36" t="n">
         <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X36" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Y36" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AA36" t="n">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="AB36" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC36" t="n">
         <v>10.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF36" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="AG36" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AK36" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AL36" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM36" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AN36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO36" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AQ36" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AU36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV36" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AW36" t="n">
         <v>20</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.2</v>
+        <v>19.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ36" t="n">
         <v>11</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BD36" t="n">
         <v>19.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BF36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG36" t="n">
         <v>12.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G37" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="H37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I37" t="n">
         <v>5.8</v>
-      </c>
-      <c r="I37" t="n">
-        <v>6</v>
       </c>
       <c r="J37" t="n">
         <v>4.4</v>
@@ -7565,7 +7565,7 @@
         <v>4.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M37" t="n">
         <v>1.05</v>
@@ -7577,7 +7577,7 @@
         <v>1.24</v>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
         <v>1.73</v>
@@ -7586,7 +7586,7 @@
         <v>1.51</v>
       </c>
       <c r="S37" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T37" t="n">
         <v>1.79</v>
@@ -7598,7 +7598,7 @@
         <v>1.2</v>
       </c>
       <c r="W37" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X37" t="n">
         <v>20</v>
@@ -7613,7 +7613,7 @@
         <v>140</v>
       </c>
       <c r="AB37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC37" t="n">
         <v>9.800000000000001</v>
@@ -7628,7 +7628,7 @@
         <v>10.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH37" t="n">
         <v>19.5</v>
@@ -7637,7 +7637,7 @@
         <v>70</v>
       </c>
       <c r="AJ37" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK37" t="n">
         <v>16</v>
@@ -7670,7 +7670,7 @@
         <v>9.4</v>
       </c>
       <c r="AU37" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV37" t="n">
         <v>19.5</v>
@@ -7700,17 +7700,17 @@
         <v>27</v>
       </c>
       <c r="BE37" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG37" t="n">
         <v>55</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7744,58 +7744,58 @@
         <v>1.93</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K38" t="n">
         <v>4</v>
-      </c>
-      <c r="I38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4.3</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O38" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="R38" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S38" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="T38" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U38" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V38" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X38" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y38" t="n">
         <v>19.5</v>
@@ -7804,107 +7804,107 @@
         <v>34</v>
       </c>
       <c r="AA38" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC38" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD38" t="n">
         <v>16.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AF38" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG38" t="n">
         <v>10.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW38" t="n">
         <v>23</v>
       </c>
-      <c r="AK38" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN38" t="n">
+      <c r="AX38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE38" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO38" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF38" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BG38" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
         <v>1.53</v>
       </c>
       <c r="S39" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
         <v>1.64</v>
@@ -7998,7 +7998,7 @@
         <v>40</v>
       </c>
       <c r="AA39" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AB39" t="n">
         <v>14</v>
@@ -8016,7 +8016,7 @@
         <v>16</v>
       </c>
       <c r="AG39" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH39" t="n">
         <v>19</v>
@@ -8034,7 +8034,7 @@
         <v>34</v>
       </c>
       <c r="AM39" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN39" t="n">
         <v>11</v>
@@ -8043,19 +8043,19 @@
         <v>42</v>
       </c>
       <c r="AP39" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>17</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT39" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU39" t="n">
         <v>8.6</v>
@@ -8064,7 +8064,7 @@
         <v>13</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX39" t="n">
         <v>10.5</v>
@@ -8076,10 +8076,10 @@
         <v>12.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB39" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BC39" t="n">
         <v>13.5</v>
@@ -8088,17 +8088,17 @@
         <v>21</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="BF39" t="n">
         <v>7.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8132,13 +8132,13 @@
         <v>1.55</v>
       </c>
       <c r="G40" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H40" t="n">
         <v>5.6</v>
       </c>
       <c r="I40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>5.3</v>
@@ -8153,13 +8153,13 @@
         <v>1.02</v>
       </c>
       <c r="N40" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q40" t="n">
         <v>1.38</v>
@@ -8168,16 +8168,16 @@
         <v>1.95</v>
       </c>
       <c r="S40" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T40" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U40" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V40" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
         <v>2.74</v>
@@ -8186,16 +8186,16 @@
         <v>38</v>
       </c>
       <c r="Y40" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Z40" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AA40" t="n">
         <v>180</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC40" t="n">
         <v>13.5</v>
@@ -8216,7 +8216,7 @@
         <v>17</v>
       </c>
       <c r="AI40" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ40" t="n">
         <v>19.5</v>
@@ -8225,28 +8225,28 @@
         <v>14</v>
       </c>
       <c r="AL40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM40" t="n">
         <v>60</v>
       </c>
       <c r="AN40" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO40" t="n">
         <v>36</v>
       </c>
       <c r="AP40" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="AQ40" t="n">
         <v>30</v>
       </c>
       <c r="AR40" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AS40" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT40" t="n">
         <v>14.5</v>
@@ -8258,7 +8258,7 @@
         <v>21</v>
       </c>
       <c r="AW40" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AX40" t="n">
         <v>12.5</v>
@@ -8270,10 +8270,10 @@
         <v>15.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BB40" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC40" t="n">
         <v>12.5</v>
@@ -8282,17 +8282,17 @@
         <v>19.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG40" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
         <v>1.99</v>
       </c>
       <c r="H41" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I41" t="n">
         <v>4.2</v>
@@ -8362,7 +8362,7 @@
         <v>1.62</v>
       </c>
       <c r="S41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T41" t="n">
         <v>1.58</v>
@@ -8380,13 +8380,13 @@
         <v>32</v>
       </c>
       <c r="Y41" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="Z41" t="n">
         <v>42</v>
       </c>
       <c r="AA41" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB41" t="n">
         <v>16.5</v>
@@ -8410,7 +8410,7 @@
         <v>19.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AJ41" t="n">
         <v>27</v>
@@ -8422,7 +8422,7 @@
         <v>32</v>
       </c>
       <c r="AM41" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN41" t="n">
         <v>10.5</v>
@@ -8431,28 +8431,28 @@
         <v>36</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.75</v>
+        <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.65</v>
+        <v>11.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>3.85</v>
+        <v>16</v>
       </c>
       <c r="AS41" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT41" t="n">
         <v>10</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.15</v>
+        <v>5.1</v>
       </c>
       <c r="AV41" t="n">
         <v>12</v>
       </c>
       <c r="AW41" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="AX41" t="n">
         <v>11</v>
@@ -8464,10 +8464,10 @@
         <v>11.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BB41" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="BC41" t="n">
         <v>13</v>
@@ -8476,7 +8476,7 @@
         <v>19</v>
       </c>
       <c r="BE41" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BF41" t="n">
         <v>6.4</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8526,13 +8526,13 @@
         <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>3.7</v>
       </c>
       <c r="K42" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
         <v>1.3</v>
@@ -8547,16 +8547,16 @@
         <v>1.27</v>
       </c>
       <c r="P42" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R42" t="n">
         <v>1.41</v>
       </c>
       <c r="S42" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T42" t="n">
         <v>1.71</v>
@@ -8571,19 +8571,19 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y42" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AA42" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC42" t="n">
         <v>10.5</v>
@@ -8592,37 +8592,37 @@
         <v>21</v>
       </c>
       <c r="AE42" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG42" t="n">
         <v>13</v>
       </c>
       <c r="AH42" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK42" t="n">
         <v>21</v>
       </c>
-      <c r="AI42" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>24</v>
-      </c>
       <c r="AL42" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AM42" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN42" t="n">
         <v>13</v>
       </c>
       <c r="AO42" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP42" t="n">
         <v>14.5</v>
@@ -8631,10 +8631,10 @@
         <v>14</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT42" t="n">
         <v>8.800000000000001</v>
@@ -8646,41 +8646,41 @@
         <v>14.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="AX42" t="n">
         <v>11.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.5</v>
+        <v>19</v>
       </c>
       <c r="BF42" t="n">
         <v>10.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>1.73</v>
       </c>
       <c r="G43" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H43" t="n">
         <v>4.8</v>
@@ -8723,7 +8723,7 @@
         <v>5.4</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K43" t="n">
         <v>4.4</v>
@@ -8762,25 +8762,25 @@
         <v>1.23</v>
       </c>
       <c r="W43" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X43" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z43" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AA43" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AB43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD43" t="n">
         <v>23</v>
@@ -8789,19 +8789,19 @@
         <v>70</v>
       </c>
       <c r="AF43" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH43" t="n">
         <v>21</v>
       </c>
       <c r="AI43" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AJ43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="n">
         <v>20</v>
@@ -8810,13 +8810,13 @@
         <v>32</v>
       </c>
       <c r="AM43" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO43" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AP43" t="n">
         <v>17</v>
@@ -8825,22 +8825,22 @@
         <v>18</v>
       </c>
       <c r="AR43" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT43" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU43" t="n">
         <v>8.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AX43" t="n">
         <v>10.5</v>
@@ -8852,29 +8852,29 @@
         <v>15.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BB43" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC43" t="n">
         <v>15</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BF43" t="n">
         <v>8</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
         <v>3.6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
         <v>1.08</v>
@@ -8935,10 +8935,10 @@
         <v>1.36</v>
       </c>
       <c r="P44" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R44" t="n">
         <v>1.3</v>
@@ -8947,7 +8947,7 @@
         <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U44" t="n">
         <v>2.08</v>
@@ -8959,13 +8959,13 @@
         <v>1.46</v>
       </c>
       <c r="X44" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z44" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA44" t="n">
         <v>50</v>
@@ -8977,25 +8977,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE44" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF44" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH44" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ44" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AK44" t="n">
         <v>44</v>
@@ -9004,7 +9004,7 @@
         <v>60</v>
       </c>
       <c r="AM44" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN44" t="n">
         <v>42</v>
@@ -9022,7 +9022,7 @@
         <v>12.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AT44" t="n">
         <v>8.199999999999999</v>
@@ -9034,7 +9034,7 @@
         <v>9</v>
       </c>
       <c r="AW44" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="AX44" t="n">
         <v>14.5</v>
@@ -9046,29 +9046,29 @@
         <v>13</v>
       </c>
       <c r="BA44" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="BB44" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BC44" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="BD44" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="BF44" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BG44" t="n">
         <v>20</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="G45" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I45" t="n">
         <v>3.45</v>
       </c>
-      <c r="I45" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J45" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K45" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L45" t="n">
         <v>1.35</v>
@@ -9126,85 +9126,85 @@
         <v>3.75</v>
       </c>
       <c r="O45" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P45" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R45" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T45" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U45" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V45" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W45" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="X45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y45" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z45" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA45" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB45" t="n">
         <v>11</v>
       </c>
       <c r="AC45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD45" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE45" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF45" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH45" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI45" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ45" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK45" t="n">
         <v>29</v>
       </c>
       <c r="AL45" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM45" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN45" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO45" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AP45" t="n">
         <v>12.5</v>
@@ -9213,13 +9213,13 @@
         <v>12</v>
       </c>
       <c r="AR45" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS45" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AT45" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU45" t="n">
         <v>7.2</v>
@@ -9228,41 +9228,41 @@
         <v>13</v>
       </c>
       <c r="AW45" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AX45" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY45" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA45" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BB45" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BC45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD45" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF45" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9293,88 +9293,88 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="G46" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="H46" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="J46" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="K46" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L46" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M46" t="n">
         <v>1.12</v>
       </c>
       <c r="N46" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="O46" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P46" t="n">
         <v>1.48</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S46" t="n">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="U46" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="V46" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="X46" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y46" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z46" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC46" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD46" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE46" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG46" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH46" t="n">
         <v>950</v>
@@ -9383,80 +9383,80 @@
         <v>1000</v>
       </c>
       <c r="AJ46" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AK46" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL46" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM46" t="n">
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AO46" t="n">
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AQ46" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AX46" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AY46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA46" t="n">
         <v>1.43</v>
       </c>
-      <c r="AS46" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BB46" t="n">
-        <v>5.8</v>
+        <v>1.67</v>
       </c>
       <c r="BC46" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.8</v>
+        <v>1.68</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9487,19 +9487,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="G47" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="H47" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="I47" t="n">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="J47" t="n">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
         <v>950</v>
@@ -9511,22 +9511,22 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O47" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P47" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R47" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S47" t="n">
-        <v>1.69</v>
+        <v>1.14</v>
       </c>
       <c r="T47" t="n">
         <v>1.11</v>
@@ -9535,122 +9535,122 @@
         <v>1.11</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W47" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
         <v>2.58</v>
       </c>
       <c r="H48" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I48" t="n">
         <v>3</v>
@@ -9705,28 +9705,28 @@
         <v>1.06</v>
       </c>
       <c r="N48" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O48" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R48" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U48" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V48" t="n">
         <v>1.5</v>
@@ -9735,22 +9735,22 @@
         <v>1.63</v>
       </c>
       <c r="X48" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y48" t="n">
         <v>14</v>
       </c>
       <c r="Z48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="n">
         <v>46</v>
       </c>
       <c r="AB48" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD48" t="n">
         <v>12.5</v>
@@ -9768,13 +9768,13 @@
         <v>15.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ48" t="n">
         <v>36</v>
       </c>
       <c r="AK48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL48" t="n">
         <v>34</v>
@@ -9786,31 +9786,31 @@
         <v>18</v>
       </c>
       <c r="AO48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP48" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS48" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT48" t="n">
         <v>12</v>
       </c>
       <c r="AU48" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV48" t="n">
         <v>12</v>
       </c>
       <c r="AW48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX48" t="n">
         <v>16.5</v>
@@ -9828,23 +9828,23 @@
         <v>32</v>
       </c>
       <c r="BC48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD48" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE48" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF48" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9878,19 +9878,19 @@
         <v>2.18</v>
       </c>
       <c r="G49" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J49" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K49" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L49" t="n">
         <v>1.43</v>
@@ -9905,7 +9905,7 @@
         <v>1.37</v>
       </c>
       <c r="P49" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q49" t="n">
         <v>2.06</v>
@@ -9914,52 +9914,52 @@
         <v>1.31</v>
       </c>
       <c r="S49" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T49" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U49" t="n">
         <v>2.04</v>
       </c>
       <c r="V49" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W49" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X49" t="n">
         <v>12.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z49" t="n">
         <v>30</v>
       </c>
       <c r="AA49" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC49" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE49" t="n">
         <v>60</v>
       </c>
       <c r="AF49" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG49" t="n">
         <v>11.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI49" t="n">
         <v>70</v>
@@ -9968,16 +9968,16 @@
         <v>32</v>
       </c>
       <c r="AK49" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL49" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM49" t="n">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AN49" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO49" t="n">
         <v>65</v>
@@ -9986,59 +9986,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU49" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>6.8</v>
       </c>
       <c r="AV49" t="n">
         <v>13.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX49" t="n">
         <v>12</v>
       </c>
       <c r="AY49" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ49" t="n">
         <v>16</v>
       </c>
       <c r="BA49" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB49" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BC49" t="n">
         <v>21</v>
       </c>
       <c r="BD49" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE49" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF49" t="n">
         <v>17.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10069,19 +10069,19 @@
         </is>
       </c>
       <c r="F50" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G50" t="n">
         <v>2.58</v>
       </c>
-      <c r="G50" t="n">
-        <v>2.62</v>
-      </c>
       <c r="H50" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I50" t="n">
         <v>2.94</v>
       </c>
       <c r="J50" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K50" t="n">
         <v>3.75</v>
@@ -10099,10 +10099,10 @@
         <v>1.29</v>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R50" t="n">
         <v>1.42</v>
@@ -10120,7 +10120,7 @@
         <v>1.51</v>
       </c>
       <c r="W50" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X50" t="n">
         <v>16</v>
@@ -10147,7 +10147,7 @@
         <v>32</v>
       </c>
       <c r="AF50" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG50" t="n">
         <v>11.5</v>
@@ -10159,7 +10159,7 @@
         <v>40</v>
       </c>
       <c r="AJ50" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK50" t="n">
         <v>27</v>
@@ -10171,7 +10171,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO50" t="n">
         <v>25</v>
@@ -10180,10 +10180,10 @@
         <v>14.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS50" t="n">
         <v>40</v>
@@ -10192,13 +10192,13 @@
         <v>11</v>
       </c>
       <c r="AU50" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV50" t="n">
         <v>11.5</v>
       </c>
       <c r="AW50" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX50" t="n">
         <v>15.5</v>
@@ -10222,7 +10222,7 @@
         <v>32</v>
       </c>
       <c r="BE50" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BF50" t="n">
         <v>18.5</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="G51" t="n">
         <v>2.04</v>
       </c>
       <c r="H51" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J51" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K51" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10287,19 +10287,19 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O51" t="n">
         <v>1.33</v>
       </c>
       <c r="P51" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="R51" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -10311,122 +10311,122 @@
         <v>1.11</v>
       </c>
       <c r="V51" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
         <v>1.96</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG51" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10457,19 +10457,19 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G52" t="n">
         <v>1.92</v>
       </c>
       <c r="H52" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="K52" t="n">
         <v>4.1</v>
@@ -10481,7 +10481,7 @@
         <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O52" t="n">
         <v>1.38</v>
@@ -10496,131 +10496,131 @@
         <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T52" t="n">
         <v>1.96</v>
       </c>
       <c r="U52" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V52" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W52" t="n">
         <v>2.08</v>
       </c>
       <c r="X52" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y52" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z52" t="n">
         <v>55</v>
       </c>
       <c r="AA52" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AB52" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC52" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC52" t="n">
-        <v>10</v>
-      </c>
       <c r="AD52" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE52" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF52" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG52" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH52" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI52" t="n">
-        <v>120</v>
+        <v>370</v>
       </c>
       <c r="AJ52" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK52" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL52" t="n">
         <v>55</v>
       </c>
       <c r="AM52" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN52" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO52" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP52" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="AV52" t="n">
-        <v>3.75</v>
+        <v>5.9</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX52" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="AY52" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="AZ52" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB52" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC52" t="n">
-        <v>3.75</v>
+        <v>5.9</v>
       </c>
       <c r="BD52" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF52" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G53" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H53" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I53" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K53" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L53" t="n">
         <v>1.48</v>
@@ -10678,7 +10678,7 @@
         <v>2.62</v>
       </c>
       <c r="O53" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P53" t="n">
         <v>1.54</v>
@@ -10693,13 +10693,13 @@
         <v>5.3</v>
       </c>
       <c r="T53" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
         <v>1.78</v>
       </c>
       <c r="V53" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W53" t="n">
         <v>1.62</v>
@@ -10708,16 +10708,16 @@
         <v>9</v>
       </c>
       <c r="Y53" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z53" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA53" t="n">
         <v>90</v>
       </c>
       <c r="AB53" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC53" t="n">
         <v>8.800000000000001</v>
@@ -10738,7 +10738,7 @@
         <v>29</v>
       </c>
       <c r="AI53" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ53" t="n">
         <v>48</v>
@@ -10750,7 +10750,7 @@
         <v>80</v>
       </c>
       <c r="AM53" t="n">
-        <v>230</v>
+        <v>580</v>
       </c>
       <c r="AN53" t="n">
         <v>48</v>
@@ -10768,7 +10768,7 @@
         <v>16</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT53" t="n">
         <v>6.8</v>
@@ -10780,7 +10780,7 @@
         <v>11</v>
       </c>
       <c r="AW53" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX53" t="n">
         <v>10.5</v>
@@ -10792,29 +10792,29 @@
         <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB53" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC53" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE53" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF53" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF53" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG53" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10845,19 +10845,19 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="G54" t="n">
-        <v>600</v>
+        <v>1.76</v>
       </c>
       <c r="H54" t="n">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="I54" t="n">
         <v>990</v>
       </c>
       <c r="J54" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K54" t="n">
         <v>950</v>
@@ -10869,7 +10869,7 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="O54" t="n">
         <v>1.14</v>
@@ -10878,13 +10878,13 @@
         <v>1.27</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="R54" t="n">
         <v>1.27</v>
       </c>
       <c r="S54" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="T54" t="n">
         <v>1.11</v>
@@ -10893,122 +10893,122 @@
         <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z54" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA54" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC54" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE54" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF54" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH54" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI54" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK54" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL54" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM54" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN54" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO54" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         <v>2.36</v>
       </c>
       <c r="G55" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H55" t="n">
         <v>3.75</v>
@@ -11102,19 +11102,19 @@
         <v>28</v>
       </c>
       <c r="AA55" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AC55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD55" t="n">
         <v>17.5</v>
       </c>
       <c r="AE55" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AF55" t="n">
         <v>17</v>
@@ -11126,7 +11126,7 @@
         <v>22</v>
       </c>
       <c r="AI55" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ55" t="n">
         <v>40</v>
@@ -11135,16 +11135,16 @@
         <v>34</v>
       </c>
       <c r="AL55" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM55" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN55" t="n">
         <v>32</v>
       </c>
       <c r="AO55" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP55" t="n">
         <v>9</v>
@@ -11153,10 +11153,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR55" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT55" t="n">
         <v>7.4</v>
@@ -11168,7 +11168,7 @@
         <v>13.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX55" t="n">
         <v>13</v>
@@ -11177,32 +11177,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB55" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC55" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD55" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF55" t="n">
         <v>6</v>
       </c>
-      <c r="BF55" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG55" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11236,16 +11236,16 @@
         <v>1.43</v>
       </c>
       <c r="G56" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J56" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K56" t="n">
         <v>5.2</v>
@@ -11263,7 +11263,7 @@
         <v>1.27</v>
       </c>
       <c r="P56" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q56" t="n">
         <v>1.79</v>
@@ -11281,10 +11281,10 @@
         <v>1.81</v>
       </c>
       <c r="V56" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W56" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="X56" t="n">
         <v>19.5</v>
@@ -11299,7 +11299,7 @@
         <v>380</v>
       </c>
       <c r="AB56" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC56" t="n">
         <v>13</v>
@@ -11344,13 +11344,13 @@
         <v>15</v>
       </c>
       <c r="AQ56" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR56" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS56" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT56" t="n">
         <v>7</v>
@@ -11359,10 +11359,10 @@
         <v>9.4</v>
       </c>
       <c r="AV56" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW56" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX56" t="n">
         <v>7.4</v>
@@ -11371,10 +11371,10 @@
         <v>9</v>
       </c>
       <c r="AZ56" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB56" t="n">
         <v>10.5</v>
@@ -11383,20 +11383,20 @@
         <v>13.5</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE56" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF56" t="n">
         <v>6.2</v>
       </c>
       <c r="BG56" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11430,43 +11430,43 @@
         <v>2.48</v>
       </c>
       <c r="G57" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="H57" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="I57" t="n">
         <v>3.7</v>
       </c>
       <c r="J57" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K57" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L57" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="n">
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O57" t="n">
         <v>1.02</v>
       </c>
       <c r="P57" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R57" t="n">
         <v>1.18</v>
       </c>
       <c r="S57" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T57" t="n">
         <v>1.11</v>
@@ -11478,7 +11478,7 @@
         <v>1.37</v>
       </c>
       <c r="W57" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11624,10 +11624,10 @@
         <v>1.04</v>
       </c>
       <c r="G58" t="n">
-        <v>110</v>
+        <v>1.64</v>
       </c>
       <c r="H58" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I58" t="n">
         <v>990</v>
@@ -11651,7 +11651,7 @@
         <v>1.09</v>
       </c>
       <c r="P58" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q58" t="n">
         <v>1.08</v>
@@ -11660,7 +11660,7 @@
         <v>1.38</v>
       </c>
       <c r="S58" t="n">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="T58" t="n">
         <v>1.11</v>
@@ -11672,7 +11672,7 @@
         <v>1.01</v>
       </c>
       <c r="W58" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -11702,7 +11702,7 @@
         <v>1000</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AH58" t="n">
         <v>1000</v>
@@ -11729,62 +11729,62 @@
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY58" t="n">
         <v>1.01</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11839,22 +11839,22 @@
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="O59" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P59" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="R59" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S59" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="T59" t="n">
         <v>1.11</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G60" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H60" t="n">
         <v>5.5</v>
@@ -12021,7 +12021,7 @@
         <v>6.2</v>
       </c>
       <c r="J60" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K60" t="n">
         <v>3.5</v>
@@ -12033,7 +12033,7 @@
         <v>1.13</v>
       </c>
       <c r="N60" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="O60" t="n">
         <v>1.13</v>
@@ -12048,10 +12048,10 @@
         <v>1.15</v>
       </c>
       <c r="S60" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T60" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U60" t="n">
         <v>1.61</v>
@@ -12060,7 +12060,7 @@
         <v>1.19</v>
       </c>
       <c r="W60" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X60" t="n">
         <v>9.4</v>
@@ -12096,7 +12096,7 @@
         <v>36</v>
       </c>
       <c r="AI60" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ60" t="n">
         <v>26</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G61" t="n">
         <v>2.32</v>
@@ -12227,7 +12227,7 @@
         <v>1.09</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O61" t="n">
         <v>1.41</v>
@@ -12269,7 +12269,7 @@
         <v>100</v>
       </c>
       <c r="AB61" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC61" t="n">
         <v>9.199999999999999</v>
@@ -12320,7 +12320,7 @@
         <v>19</v>
       </c>
       <c r="AS61" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT61" t="n">
         <v>7</v>
@@ -12332,7 +12332,7 @@
         <v>13.5</v>
       </c>
       <c r="AW61" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX61" t="n">
         <v>11.5</v>
@@ -12344,29 +12344,29 @@
         <v>17</v>
       </c>
       <c r="BA61" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB61" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>4.8</v>
       </c>
       <c r="BC61" t="n">
         <v>19.5</v>
       </c>
       <c r="BD61" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE61" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BF61" t="n">
         <v>20</v>
       </c>
       <c r="BG61" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H2" t="n">
         <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -796,31 +796,31 @@
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>13.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
         <v>13.5</v>
@@ -832,7 +832,7 @@
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
         <v>65</v>
@@ -862,7 +862,7 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
         <v>10.5</v>
@@ -874,7 +874,7 @@
         <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
         <v>11</v>
@@ -898,29 +898,29 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BE2" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF2" t="n">
         <v>9</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.43</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.48</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>340</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
         <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
         <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AK3" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
         <v>32</v>
       </c>
       <c r="BC3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BG3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>10.5</v>
@@ -1157,40 +1157,40 @@
         <v>1.43</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
         <v>3.3</v>
@@ -1199,116 +1199,116 @@
         <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
         <v>11.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF4" t="n">
         <v>90</v>
       </c>
       <c r="AG4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ4" t="n">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="AK4" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AL4" t="n">
         <v>160</v>
       </c>
       <c r="AM4" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN4" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AO4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>7.4</v>
       </c>
-      <c r="AP4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
         <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
         <v>9.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AY4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
         <v>70</v>
       </c>
       <c r="BC4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BD4" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BE4" t="n">
         <v>70</v>
       </c>
       <c r="BF4" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
@@ -1369,7 +1369,7 @@
         <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
         <v>2.38</v>
@@ -1381,7 +1381,7 @@
         <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
         <v>1.92</v>
@@ -1390,7 +1390,7 @@
         <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
@@ -1411,10 +1411,10 @@
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="n">
         <v>13</v>
@@ -1426,13 +1426,13 @@
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ5" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
         <v>290</v>
@@ -1441,10 +1441,10 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>160</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
         <v>9.4</v>
@@ -1453,7 +1453,7 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS5" t="n">
         <v>34</v>
@@ -1477,7 +1477,7 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
         <v>50</v>
@@ -1486,7 +1486,7 @@
         <v>23</v>
       </c>
       <c r="BC5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>29</v>
@@ -1495,14 +1495,14 @@
         <v>44</v>
       </c>
       <c r="BF5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG5" t="n">
         <v>48</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H6" t="n">
         <v>1.39</v>
@@ -1563,13 +1563,13 @@
         <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.55</v>
@@ -1578,7 +1578,7 @@
         <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
         <v>3.15</v>
@@ -1599,7 +1599,7 @@
         <v>11.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
         <v>11.5</v>
@@ -1608,7 +1608,7 @@
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF6" t="n">
         <v>120</v>
@@ -1617,25 +1617,25 @@
         <v>100</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
         <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AK6" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AL6" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AM6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN6" t="n">
-        <v>510</v>
+        <v>460</v>
       </c>
       <c r="AO6" t="n">
         <v>8.199999999999999</v>
@@ -1665,7 +1665,7 @@
         <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY6" t="n">
         <v>18</v>
@@ -1674,29 +1674,29 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H7" t="n">
         <v>2.5</v>
@@ -1742,64 +1742,64 @@
         <v>2.82</v>
       </c>
       <c r="K7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
         <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -1829,68 +1829,68 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.22</v>
+        <v>6.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.68</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.98</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.68</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.68</v>
+        <v>11.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.72</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.96</v>
+        <v>7.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.98</v>
+        <v>13</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
         <v>3.65</v>
@@ -1954,25 +1954,25 @@
         <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
         <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
         <v>8.800000000000001</v>
@@ -1993,13 +1993,13 @@
         <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>80</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
         <v>27</v>
@@ -2011,7 +2011,7 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>110</v>
@@ -2023,22 +2023,22 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2059,32 +2059,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BD8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2118,25 +2118,25 @@
         <v>1.19</v>
       </c>
       <c r="G9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
         <v>22</v>
       </c>
       <c r="J9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="n">
         <v>8.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
         <v>6.2</v>
@@ -2145,13 +2145,13 @@
         <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
         <v>1.51</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S9" t="n">
         <v>2.26</v>
@@ -2160,13 +2160,13 @@
         <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V9" t="n">
         <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
@@ -2193,7 +2193,7 @@
         <v>450</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>9.199999999999999</v>
@@ -2241,10 +2241,10 @@
         <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX9" t="n">
         <v>7</v>
@@ -2253,32 +2253,32 @@
         <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
         <v>7.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
         <v>3.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2315,31 +2315,31 @@
         <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
         <v>1.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
         <v>2.34</v>
@@ -2348,19 +2348,19 @@
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2411,7 +2411,7 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
@@ -2426,10 +2426,10 @@
         <v>7.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2438,7 +2438,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -2453,16 +2453,16 @@
         <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD10" t="n">
         <v>7.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
         <v>6.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
         <v>3.05</v>
@@ -2515,37 +2515,37 @@
         <v>2.84</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P11" t="n">
         <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
         <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
         <v>2.26</v>
@@ -2560,7 +2560,7 @@
         <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
         <v>970</v>
@@ -2569,13 +2569,13 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -2611,7 +2611,7 @@
         <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
@@ -2620,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>11</v>
@@ -2641,32 +2641,32 @@
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG11" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="O12" t="n">
         <v>1.07</v>
@@ -2781,7 +2781,7 @@
         <v>950</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
         <v>500</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>2.06</v>
       </c>
       <c r="G13" t="n">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
         <v>2.56</v>
       </c>
       <c r="I13" t="n">
-        <v>990</v>
+        <v>220</v>
       </c>
       <c r="J13" t="n">
         <v>1.64</v>
@@ -2942,7 +2942,7 @@
         <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.33</v>
       </c>
       <c r="G14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H14" t="n">
         <v>10.5</v>
@@ -3097,13 +3097,13 @@
         <v>12.5</v>
       </c>
       <c r="J14" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3124,7 +3124,7 @@
         <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
         <v>1.91</v>
@@ -3133,10 +3133,10 @@
         <v>1.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
@@ -3148,22 +3148,22 @@
         <v>110</v>
       </c>
       <c r="AA14" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
         <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
@@ -3172,7 +3172,7 @@
         <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AJ14" t="n">
         <v>11</v>
@@ -3184,10 +3184,10 @@
         <v>32</v>
       </c>
       <c r="AM14" t="n">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AO14" t="n">
         <v>170</v>
@@ -3199,25 +3199,25 @@
         <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
         <v>9.800000000000001</v>
@@ -3226,7 +3226,7 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
         <v>9.800000000000001</v>
@@ -3235,10 +3235,10 @@
         <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BF14" t="n">
         <v>4.1</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>2.84</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
@@ -3303,7 +3303,7 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
@@ -3321,19 +3321,19 @@
         <v>1.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U15" t="n">
         <v>2.48</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
         <v>1.54</v>
       </c>
       <c r="X15" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="Y15" t="n">
         <v>17.5</v>
@@ -3390,59 +3390,59 @@
         <v>5.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT15" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>4.3</v>
       </c>
-      <c r="AU15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AV15" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF15" t="n">
         <v>5</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BG15" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>2.26</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
         <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>1.81</v>
@@ -3718,7 +3718,7 @@
         <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
         <v>17</v>
@@ -3748,10 +3748,10 @@
         <v>50</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>100</v>
@@ -3784,7 +3784,7 @@
         <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT17" t="n">
         <v>11</v>
@@ -3811,26 +3811,26 @@
         <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC17" t="n">
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>2.16</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
@@ -3882,31 +3882,31 @@
         <v>1.29</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
         <v>1.34</v>
@@ -3915,10 +3915,10 @@
         <v>1.86</v>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z18" t="n">
         <v>29</v>
@@ -3927,28 +3927,28 @@
         <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
         <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AJ18" t="n">
         <v>27</v>
@@ -3960,13 +3960,13 @@
         <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN18" t="n">
         <v>14</v>
       </c>
       <c r="AO18" t="n">
-        <v>220</v>
+        <v>38</v>
       </c>
       <c r="AP18" t="n">
         <v>15</v>
@@ -3975,10 +3975,10 @@
         <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AT18" t="n">
         <v>9.199999999999999</v>
@@ -4011,20 +4011,20 @@
         <v>17.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE18" t="n">
         <v>36</v>
       </c>
       <c r="BF18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>16.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H19" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="K19" t="n">
         <v>3.35</v>
@@ -4079,13 +4079,13 @@
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O19" t="n">
         <v>1.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
         <v>2.4</v>
@@ -4100,10 +4100,10 @@
         <v>1.96</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.47</v>
@@ -4172,7 +4172,7 @@
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
         <v>7.8</v>
@@ -4199,7 +4199,7 @@
         <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC19" t="n">
         <v>7.6</v>
@@ -4208,17 +4208,17 @@
         <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG19" t="n">
         <v>7.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G20" t="n">
         <v>2.42</v>
@@ -4324,7 +4324,7 @@
         <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
         <v>30</v>
@@ -4336,7 +4336,7 @@
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
         <v>100</v>
@@ -4351,10 +4351,10 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
         <v>9.199999999999999</v>
@@ -4363,10 +4363,10 @@
         <v>9.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
         <v>7.6</v>
@@ -4378,7 +4378,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AX20" t="n">
         <v>13</v>
@@ -4390,29 +4390,29 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD20" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H21" t="n">
         <v>5.2</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.4</v>
@@ -4476,7 +4476,7 @@
         <v>1.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -4485,7 +4485,7 @@
         <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U21" t="n">
         <v>1.81</v>
@@ -4521,13 +4521,13 @@
         <v>700</v>
       </c>
       <c r="AF21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI21" t="n">
         <v>700</v>
@@ -4557,10 +4557,10 @@
         <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
         <v>6</v>
@@ -4572,41 +4572,41 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>8.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF21" t="n">
         <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.42</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
         <v>3.65</v>
@@ -4670,7 +4670,7 @@
         <v>1.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
@@ -4685,7 +4685,7 @@
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
         <v>1.7</v>
@@ -4712,7 +4712,7 @@
         <v>14.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
@@ -4730,7 +4730,7 @@
         <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AL22" t="n">
         <v>120</v>
@@ -4766,7 +4766,7 @@
         <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX22" t="n">
         <v>13</v>
@@ -4790,7 +4790,7 @@
         <v>10</v>
       </c>
       <c r="BE22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF22" t="n">
         <v>20</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.49</v>
       </c>
       <c r="G23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H23" t="n">
         <v>6.6</v>
@@ -4843,10 +4843,10 @@
         <v>11.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.27</v>
@@ -4855,25 +4855,25 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O23" t="n">
         <v>1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
         <v>1.61</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
         <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
         <v>2.2</v>
@@ -4882,7 +4882,7 @@
         <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X23" t="n">
         <v>950</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG23" t="n">
         <v>36</v>
@@ -4918,7 +4918,7 @@
         <v>970</v>
       </c>
       <c r="AI23" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AJ23" t="n">
         <v>500</v>
@@ -4930,7 +4930,7 @@
         <v>500</v>
       </c>
       <c r="AM23" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
         <v>15</v>
@@ -4939,10 +4939,10 @@
         <v>110</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR23" t="n">
         <v>4.2</v>
@@ -4954,13 +4954,13 @@
         <v>9</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
@@ -4969,22 +4969,22 @@
         <v>4.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF23" t="n">
         <v>5.6</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G24" t="n">
         <v>1.65</v>
@@ -5055,19 +5055,19 @@
         <v>1.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="R24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
         <v>2.64</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U24" t="n">
         <v>2.16</v>
@@ -5115,13 +5115,13 @@
         <v>700</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AK24" t="n">
         <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
         <v>580</v>
@@ -5133,62 +5133,62 @@
         <v>700</v>
       </c>
       <c r="AP24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>10</v>
-      </c>
       <c r="AX24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY24" t="n">
         <v>9</v>
       </c>
       <c r="AZ24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA24" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA24" t="n">
-        <v>10</v>
-      </c>
       <c r="BB24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC24" t="n">
         <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF24" t="n">
         <v>6.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G25" t="n">
         <v>2.32</v>
@@ -5231,13 +5231,13 @@
         <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
         <v>3.25</v>
       </c>
       <c r="L25" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
@@ -5375,14 +5375,14 @@
         <v>10</v>
       </c>
       <c r="BF25" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
         <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G26" t="n">
         <v>2.1</v>
@@ -5425,13 +5425,13 @@
         <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
         <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
@@ -5452,13 +5452,13 @@
         <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V26" t="n">
         <v>1.33</v>
@@ -5470,10 +5470,10 @@
         <v>26</v>
       </c>
       <c r="Y26" t="n">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="Z26" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AA26" t="n">
         <v>900</v>
@@ -5485,7 +5485,7 @@
         <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
         <v>500</v>
@@ -5503,7 +5503,7 @@
         <v>250</v>
       </c>
       <c r="AJ26" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AK26" t="n">
         <v>46</v>
@@ -5542,7 +5542,7 @@
         <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
         <v>11.5</v>
@@ -5554,7 +5554,7 @@
         <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
@@ -5566,7 +5566,7 @@
         <v>10</v>
       </c>
       <c r="BE26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF26" t="n">
         <v>11.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
         <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P27" t="n">
         <v>2.12</v>
@@ -5646,13 +5646,13 @@
         <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
         <v>1.79</v>
       </c>
       <c r="U27" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
         <v>1.26</v>
@@ -5661,7 +5661,7 @@
         <v>2.12</v>
       </c>
       <c r="X27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y27" t="n">
         <v>18</v>
@@ -5712,7 +5712,7 @@
         <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP27" t="n">
         <v>15.5</v>
@@ -5739,7 +5739,7 @@
         <v>50</v>
       </c>
       <c r="AX27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY27" t="n">
         <v>9.4</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5801,25 +5801,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H28" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I28" t="n">
         <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
         <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -5852,7 +5852,7 @@
         <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X28" t="n">
         <v>15.5</v>
@@ -5870,7 +5870,7 @@
         <v>10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>17</v>
@@ -5879,10 +5879,10 @@
         <v>50</v>
       </c>
       <c r="AF28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
         <v>18</v>
@@ -5891,7 +5891,7 @@
         <v>60</v>
       </c>
       <c r="AJ28" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
         <v>23</v>
@@ -5915,16 +5915,16 @@
         <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
         <v>14.5</v>
@@ -5954,17 +5954,17 @@
         <v>22</v>
       </c>
       <c r="BE28" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BF28" t="n">
         <v>13</v>
       </c>
       <c r="BG28" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G29" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H29" t="n">
         <v>7</v>
@@ -6007,10 +6007,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K29" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L29" t="n">
         <v>1.26</v>
@@ -6019,7 +6019,7 @@
         <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>1.2</v>
@@ -6043,10 +6043,10 @@
         <v>1.99</v>
       </c>
       <c r="V29" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W29" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X29" t="n">
         <v>50</v>
@@ -6064,7 +6064,7 @@
         <v>11</v>
       </c>
       <c r="AC29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AD29" t="n">
         <v>950</v>
@@ -6097,7 +6097,7 @@
         <v>120</v>
       </c>
       <c r="AN29" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO29" t="n">
         <v>130</v>
@@ -6106,13 +6106,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
         <v>8.6</v>
@@ -6121,10 +6121,10 @@
         <v>6.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29" t="n">
         <v>5.7</v>
@@ -6136,7 +6136,7 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB29" t="n">
         <v>7</v>
@@ -6145,20 +6145,20 @@
         <v>7.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
         <v>5</v>
       </c>
       <c r="BG29" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="G30" t="n">
         <v>1.76</v>
@@ -6201,22 +6201,22 @@
         <v>7.8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
         <v>1.49</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P30" t="n">
         <v>1.53</v>
@@ -6231,7 +6231,7 @@
         <v>5.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
         <v>1.6</v>
@@ -6246,19 +6246,19 @@
         <v>9.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z30" t="n">
         <v>250</v>
       </c>
       <c r="AA30" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AB30" t="n">
         <v>5.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
         <v>85</v>
@@ -6267,7 +6267,7 @@
         <v>200</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
@@ -6276,10 +6276,10 @@
         <v>110</v>
       </c>
       <c r="AI30" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK30" t="n">
         <v>26</v>
@@ -6288,28 +6288,28 @@
         <v>460</v>
       </c>
       <c r="AM30" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN30" t="n">
         <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU30" t="n">
         <v>7.4</v>
@@ -6318,7 +6318,7 @@
         <v>14.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="AX30" t="n">
         <v>7.4</v>
@@ -6330,7 +6330,7 @@
         <v>16</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BB30" t="n">
         <v>15</v>
@@ -6339,20 +6339,20 @@
         <v>20</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF30" t="n">
         <v>15.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G32" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H32" t="n">
         <v>3.75</v>
@@ -6589,19 +6589,19 @@
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
         <v>1.35</v>
@@ -6610,16 +6610,16 @@
         <v>1.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="T32" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="U32" t="n">
         <v>2.1</v>
@@ -6628,16 +6628,16 @@
         <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X32" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y32" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Z32" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AA32" t="n">
         <v>500</v>
@@ -6655,10 +6655,10 @@
         <v>500</v>
       </c>
       <c r="AF32" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AG32" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AH32" t="n">
         <v>970</v>
@@ -6679,7 +6679,7 @@
         <v>580</v>
       </c>
       <c r="AN32" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AO32" t="n">
         <v>500</v>
@@ -6688,13 +6688,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT32" t="n">
         <v>8</v>
@@ -6703,44 +6703,44 @@
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AW32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX32" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX32" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AY32" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ32" t="n">
         <v>11</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BF32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G33" t="n">
         <v>2.96</v>
@@ -6825,13 +6825,13 @@
         <v>1.51</v>
       </c>
       <c r="X33" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Y33" t="n">
         <v>500</v>
       </c>
       <c r="Z33" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA33" t="n">
         <v>900</v>
@@ -6849,7 +6849,7 @@
         <v>500</v>
       </c>
       <c r="AF33" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AG33" t="n">
         <v>26</v>
@@ -6858,13 +6858,13 @@
         <v>25</v>
       </c>
       <c r="AI33" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ33" t="n">
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL33" t="n">
         <v>500</v>
@@ -6876,7 +6876,7 @@
         <v>55</v>
       </c>
       <c r="AO33" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP33" t="n">
         <v>16.5</v>
@@ -6888,13 +6888,13 @@
         <v>15</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT33" t="n">
         <v>8.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AV33" t="n">
         <v>10.5</v>
@@ -6903,22 +6903,22 @@
         <v>18.5</v>
       </c>
       <c r="AX33" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY33" t="n">
         <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB33" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD33" t="n">
         <v>25</v>
@@ -6927,14 +6927,14 @@
         <v>9.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6965,64 +6965,64 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="H34" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I34" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="J34" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="K34" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U34" t="n">
         <v>1.6</v>
       </c>
       <c r="V34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W34" t="n">
         <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
         <v>14</v>
@@ -7034,7 +7034,7 @@
         <v>950</v>
       </c>
       <c r="AC34" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AD34" t="n">
         <v>21</v>
@@ -7043,7 +7043,7 @@
         <v>970</v>
       </c>
       <c r="AF34" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AG34" t="n">
         <v>950</v>
@@ -7070,65 +7070,65 @@
         <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP34" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AS34" t="n">
         <v>5.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV34" t="n">
         <v>6.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY34" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BB34" t="n">
         <v>4.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BF34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>2.58</v>
       </c>
       <c r="H35" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J35" t="n">
         <v>3.45</v>
@@ -7195,7 +7195,7 @@
         <v>1.8</v>
       </c>
       <c r="R35" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S35" t="n">
         <v>3.2</v>
@@ -7237,7 +7237,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AG35" t="n">
         <v>17.5</v>
@@ -7261,7 +7261,7 @@
         <v>580</v>
       </c>
       <c r="AN35" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO35" t="n">
         <v>500</v>
@@ -7294,7 +7294,7 @@
         <v>8.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ35" t="n">
         <v>11</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7359,13 +7359,13 @@
         <v>2.48</v>
       </c>
       <c r="H36" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="I36" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J36" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K36" t="n">
         <v>4.2</v>
@@ -7386,13 +7386,13 @@
         <v>2.78</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R36" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S36" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T36" t="n">
         <v>1.42</v>
@@ -7401,25 +7401,25 @@
         <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W36" t="n">
         <v>1.67</v>
       </c>
       <c r="X36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA36" t="n">
         <v>55</v>
       </c>
       <c r="AB36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC36" t="n">
         <v>10.5</v>
@@ -7434,19 +7434,19 @@
         <v>22</v>
       </c>
       <c r="AG36" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
         <v>13.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AJ36" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AK36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="n">
         <v>26</v>
@@ -7458,7 +7458,7 @@
         <v>11</v>
       </c>
       <c r="AO36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP36" t="n">
         <v>23</v>
@@ -7473,16 +7473,16 @@
         <v>20</v>
       </c>
       <c r="AT36" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV36" t="n">
         <v>12</v>
       </c>
       <c r="AW36" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="AX36" t="n">
         <v>19.5</v>
@@ -7494,16 +7494,16 @@
         <v>10.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BB36" t="n">
         <v>28</v>
       </c>
       <c r="BC36" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BE36" t="n">
         <v>20</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="F37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G37" t="n">
         <v>1.66</v>
       </c>
-      <c r="G37" t="n">
-        <v>1.67</v>
-      </c>
       <c r="H37" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I37" t="n">
         <v>5.9</v>
@@ -7598,7 +7598,7 @@
         <v>1.2</v>
       </c>
       <c r="W37" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X37" t="n">
         <v>19</v>
@@ -7607,19 +7607,19 @@
         <v>23</v>
       </c>
       <c r="Z37" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA37" t="n">
         <v>140</v>
       </c>
       <c r="AB37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC37" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE37" t="n">
         <v>70</v>
@@ -7628,7 +7628,7 @@
         <v>10.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH37" t="n">
         <v>19</v>
@@ -7637,7 +7637,7 @@
         <v>65</v>
       </c>
       <c r="AJ37" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK37" t="n">
         <v>16</v>
@@ -7652,7 +7652,7 @@
         <v>8</v>
       </c>
       <c r="AO37" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP37" t="n">
         <v>18</v>
@@ -7661,7 +7661,7 @@
         <v>20</v>
       </c>
       <c r="AR37" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AS37" t="n">
         <v>42</v>
@@ -7673,22 +7673,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV37" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW37" t="n">
         <v>60</v>
       </c>
       <c r="AX37" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB37" t="n">
         <v>15</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G38" t="n">
         <v>1.99</v>
       </c>
       <c r="H38" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7765,28 +7765,28 @@
         <v>1.06</v>
       </c>
       <c r="N38" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P38" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="T38" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="U38" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V38" t="n">
         <v>1.27</v>
@@ -7795,79 +7795,79 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y38" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z38" t="n">
         <v>34</v>
       </c>
       <c r="AA38" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG38" t="n">
         <v>10.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI38" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AJ38" t="n">
         <v>65</v>
       </c>
       <c r="AK38" t="n">
-        <v>19.5</v>
+        <v>65</v>
       </c>
       <c r="AL38" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM38" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN38" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV38" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>9</v>
       </c>
       <c r="AW38" t="n">
         <v>23</v>
@@ -7882,29 +7882,29 @@
         <v>15.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BB38" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC38" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BE38" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG38" t="n">
         <v>15</v>
       </c>
-      <c r="BF38" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>34</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L39" t="n">
         <v>1.27</v>
@@ -7968,13 +7968,13 @@
         <v>2.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="R39" t="n">
         <v>1.53</v>
       </c>
       <c r="S39" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
         <v>1.63</v>
@@ -8007,7 +8007,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD39" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="AE39" t="n">
         <v>190</v>
@@ -8085,7 +8085,7 @@
         <v>9</v>
       </c>
       <c r="BD39" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE39" t="n">
         <v>17.5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
         <v>1.57</v>
       </c>
       <c r="H40" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I40" t="n">
         <v>6.2</v>
@@ -8147,7 +8147,7 @@
         <v>5.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
         <v>1.02</v>
@@ -8159,22 +8159,22 @@
         <v>1.12</v>
       </c>
       <c r="P40" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q40" t="n">
         <v>1.38</v>
       </c>
       <c r="R40" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S40" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T40" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U40" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V40" t="n">
         <v>1.2</v>
@@ -8189,7 +8189,7 @@
         <v>40</v>
       </c>
       <c r="Z40" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AA40" t="n">
         <v>170</v>
@@ -8207,7 +8207,7 @@
         <v>60</v>
       </c>
       <c r="AF40" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG40" t="n">
         <v>10.5</v>
@@ -8216,7 +8216,7 @@
         <v>17</v>
       </c>
       <c r="AI40" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AJ40" t="n">
         <v>17</v>
@@ -8234,10 +8234,10 @@
         <v>4.7</v>
       </c>
       <c r="AO40" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ40" t="n">
         <v>32</v>
@@ -8246,10 +8246,10 @@
         <v>23</v>
       </c>
       <c r="AS40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU40" t="n">
         <v>12</v>
@@ -8261,16 +8261,16 @@
         <v>23</v>
       </c>
       <c r="AX40" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ40" t="n">
         <v>15.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BB40" t="n">
         <v>15.5</v>
@@ -8282,17 +8282,17 @@
         <v>19.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BF40" t="n">
         <v>4.3</v>
       </c>
       <c r="BG40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>1.89</v>
       </c>
       <c r="G41" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H41" t="n">
         <v>3.8</v>
@@ -8338,10 +8338,10 @@
         <v>4.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="M41" t="n">
         <v>1.03</v>
@@ -8374,7 +8374,7 @@
         <v>1.31</v>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X41" t="n">
         <v>75</v>
@@ -8428,7 +8428,7 @@
         <v>8.6</v>
       </c>
       <c r="AO41" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AP41" t="n">
         <v>16</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -8526,13 +8526,13 @@
         <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J42" t="n">
         <v>3.8</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
         <v>1.3</v>
@@ -8571,100 +8571,100 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y42" t="n">
         <v>17.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AA42" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AB42" t="n">
         <v>11</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE42" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="AF42" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG42" t="n">
         <v>11</v>
       </c>
       <c r="AH42" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ42" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL42" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AM42" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AN42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO42" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AP42" t="n">
         <v>15</v>
       </c>
       <c r="AQ42" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AT42" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AW42" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AX42" t="n">
         <v>11.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BC42" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD42" t="n">
         <v>16</v>
@@ -8676,11 +8676,11 @@
         <v>11</v>
       </c>
       <c r="BG42" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8714,13 +8714,13 @@
         <v>1.74</v>
       </c>
       <c r="G43" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I43" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J43" t="n">
         <v>4.1</v>
@@ -8738,13 +8738,13 @@
         <v>4.6</v>
       </c>
       <c r="O43" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P43" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R43" t="n">
         <v>1.49</v>
@@ -8756,13 +8756,13 @@
         <v>1.71</v>
       </c>
       <c r="U43" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V43" t="n">
         <v>1.22</v>
       </c>
       <c r="W43" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X43" t="n">
         <v>20</v>
@@ -8780,10 +8780,10 @@
         <v>11</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AE43" t="n">
         <v>320</v>
@@ -8801,7 +8801,7 @@
         <v>250</v>
       </c>
       <c r="AJ43" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK43" t="n">
         <v>17.5</v>
@@ -8813,7 +8813,7 @@
         <v>320</v>
       </c>
       <c r="AN43" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO43" t="n">
         <v>300</v>
@@ -8822,22 +8822,22 @@
         <v>17.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR43" t="n">
         <v>18</v>
       </c>
       <c r="AS43" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT43" t="n">
         <v>9.4</v>
       </c>
       <c r="AU43" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV43" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW43" t="n">
         <v>10.5</v>
@@ -8852,10 +8852,10 @@
         <v>15.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC43" t="n">
         <v>15</v>
@@ -8867,14 +8867,14 @@
         <v>21</v>
       </c>
       <c r="BF43" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG43" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>2.88</v>
       </c>
       <c r="G44" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H44" t="n">
         <v>2.58</v>
@@ -8917,25 +8917,25 @@
         <v>2.8</v>
       </c>
       <c r="J44" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="K44" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N44" t="n">
         <v>3.35</v>
       </c>
       <c r="O44" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P44" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q44" t="n">
         <v>2.16</v>
@@ -8956,10 +8956,10 @@
         <v>1.55</v>
       </c>
       <c r="W44" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X44" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y44" t="n">
         <v>11</v>
@@ -8989,7 +8989,7 @@
         <v>14</v>
       </c>
       <c r="AH44" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI44" t="n">
         <v>150</v>
@@ -9046,29 +9046,29 @@
         <v>15</v>
       </c>
       <c r="BA44" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB44" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC44" t="n">
         <v>16</v>
       </c>
       <c r="BD44" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG44" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
         <v>3.3</v>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J45" t="n">
         <v>3.5</v>
@@ -9117,7 +9117,7 @@
         <v>3.65</v>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M45" t="n">
         <v>1.07</v>
@@ -9132,13 +9132,13 @@
         <v>1.94</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R45" t="n">
         <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
         <v>1.78</v>
@@ -9162,13 +9162,13 @@
         <v>24</v>
       </c>
       <c r="AA45" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AB45" t="n">
         <v>10.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD45" t="n">
         <v>14</v>
@@ -9207,7 +9207,7 @@
         <v>44</v>
       </c>
       <c r="AP45" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ45" t="n">
         <v>12</v>
@@ -9228,7 +9228,7 @@
         <v>13</v>
       </c>
       <c r="AW45" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AX45" t="n">
         <v>13.5</v>
@@ -9252,7 +9252,7 @@
         <v>34</v>
       </c>
       <c r="BE45" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF45" t="n">
         <v>18</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9293,58 +9293,58 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="H46" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="I46" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="K46" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="L46" t="n">
         <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N46" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O46" t="n">
         <v>1.58</v>
       </c>
       <c r="P46" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Q46" t="n">
         <v>2.74</v>
       </c>
       <c r="R46" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S46" t="n">
         <v>5.7</v>
       </c>
       <c r="T46" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="U46" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V46" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W46" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X46" t="n">
         <v>970</v>
@@ -9353,7 +9353,7 @@
         <v>11</v>
       </c>
       <c r="Z46" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA46" t="n">
         <v>110</v>
@@ -9362,7 +9362,7 @@
         <v>970</v>
       </c>
       <c r="AC46" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD46" t="n">
         <v>970</v>
@@ -9371,7 +9371,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG46" t="n">
         <v>970</v>
@@ -9383,80 +9383,80 @@
         <v>120</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM46" t="n">
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO46" t="n">
         <v>130</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="AQ46" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA46" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU46" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BB46" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.56</v>
+        <v>5.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.56</v>
+        <v>5.7</v>
       </c>
       <c r="BF46" t="n">
-        <v>2.56</v>
+        <v>5.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>2.52</v>
+        <v>5.6</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9487,19 +9487,19 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="G47" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H47" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="J47" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K47" t="n">
         <v>7</v>
@@ -9511,34 +9511,34 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="O47" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P47" t="n">
-        <v>1.27</v>
+        <v>2.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="R47" t="n">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="S47" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="T47" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U47" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="V47" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W47" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X47" t="n">
         <v>950</v>
@@ -9550,10 +9550,10 @@
         <v>500</v>
       </c>
       <c r="AA47" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB47" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC47" t="n">
         <v>42</v>
@@ -9571,16 +9571,16 @@
         <v>9.6</v>
       </c>
       <c r="AH47" t="n">
-        <v>210</v>
+        <v>970</v>
       </c>
       <c r="AI47" t="n">
         <v>500</v>
       </c>
       <c r="AJ47" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AL47" t="n">
         <v>500</v>
@@ -9595,62 +9595,62 @@
         <v>500</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.76</v>
+        <v>2.14</v>
       </c>
       <c r="AX47" t="n">
-        <v>2.96</v>
+        <v>2.12</v>
       </c>
       <c r="AY47" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="BA47" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.25</v>
+        <v>2.04</v>
       </c>
       <c r="BE47" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.46</v>
+        <v>4.1</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
         <v>2.98</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J48" t="n">
         <v>3.6</v>
@@ -9705,13 +9705,13 @@
         <v>1.06</v>
       </c>
       <c r="N48" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O48" t="n">
         <v>1.27</v>
       </c>
       <c r="P48" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q48" t="n">
         <v>1.82</v>
@@ -9723,13 +9723,13 @@
         <v>3.05</v>
       </c>
       <c r="T48" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U48" t="n">
         <v>2.42</v>
       </c>
       <c r="V48" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W48" t="n">
         <v>1.64</v>
@@ -9738,13 +9738,13 @@
         <v>16</v>
       </c>
       <c r="Y48" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z48" t="n">
         <v>21</v>
       </c>
       <c r="AA48" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB48" t="n">
         <v>12</v>
@@ -9756,10 +9756,10 @@
         <v>12.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF48" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG48" t="n">
         <v>11.5</v>
@@ -9777,7 +9777,7 @@
         <v>25</v>
       </c>
       <c r="AL48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM48" t="n">
         <v>75</v>
@@ -9786,10 +9786,10 @@
         <v>18</v>
       </c>
       <c r="AO48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP48" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ48" t="n">
         <v>12.5</v>
@@ -9798,7 +9798,7 @@
         <v>19.5</v>
       </c>
       <c r="AS48" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AT48" t="n">
         <v>11.5</v>
@@ -9819,13 +9819,13 @@
         <v>11</v>
       </c>
       <c r="AZ48" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA48" t="n">
         <v>34</v>
       </c>
       <c r="BB48" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC48" t="n">
         <v>23</v>
@@ -9840,11 +9840,11 @@
         <v>17</v>
       </c>
       <c r="BG48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
         <v>3.8</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J49" t="n">
         <v>3.25</v>
@@ -9899,28 +9899,28 @@
         <v>1.09</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
         <v>1.4</v>
       </c>
       <c r="P49" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R49" t="n">
         <v>1.28</v>
       </c>
       <c r="S49" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="U49" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V49" t="n">
         <v>1.33</v>
@@ -9932,10 +9932,10 @@
         <v>12</v>
       </c>
       <c r="Y49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z49" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA49" t="n">
         <v>170</v>
@@ -9947,7 +9947,7 @@
         <v>7.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE49" t="n">
         <v>130</v>
@@ -9965,19 +9965,19 @@
         <v>160</v>
       </c>
       <c r="AJ49" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK49" t="n">
         <v>29</v>
       </c>
       <c r="AL49" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM49" t="n">
         <v>580</v>
       </c>
       <c r="AN49" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO49" t="n">
         <v>150</v>
@@ -9992,10 +9992,10 @@
         <v>11.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT49" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU49" t="n">
         <v>6.4</v>
@@ -10004,7 +10004,7 @@
         <v>14</v>
       </c>
       <c r="AW49" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX49" t="n">
         <v>11</v>
@@ -10016,7 +10016,7 @@
         <v>17</v>
       </c>
       <c r="BA49" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB49" t="n">
         <v>13</v>
@@ -10025,20 +10025,20 @@
         <v>13</v>
       </c>
       <c r="BD49" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE49" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF49" t="n">
         <v>19</v>
       </c>
       <c r="BG49" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10099,10 +10099,10 @@
         <v>1.29</v>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R50" t="n">
         <v>1.42</v>
@@ -10159,7 +10159,7 @@
         <v>40</v>
       </c>
       <c r="AJ50" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK50" t="n">
         <v>26</v>
@@ -10186,7 +10186,7 @@
         <v>18</v>
       </c>
       <c r="AS50" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AT50" t="n">
         <v>11</v>
@@ -10207,7 +10207,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ50" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA50" t="n">
         <v>36</v>
@@ -10222,7 +10222,7 @@
         <v>32</v>
       </c>
       <c r="BE50" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BF50" t="n">
         <v>18.5</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>1.97</v>
       </c>
       <c r="G51" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="H51" t="n">
         <v>3.25</v>
@@ -10287,7 +10287,7 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
         <v>1.32</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10472,34 +10472,34 @@
         <v>3.4</v>
       </c>
       <c r="K52" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L52" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M52" t="n">
         <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O52" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P52" t="n">
         <v>1.68</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="R52" t="n">
         <v>1.27</v>
       </c>
       <c r="S52" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T52" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U52" t="n">
         <v>1.83</v>
@@ -10511,7 +10511,7 @@
         <v>2.08</v>
       </c>
       <c r="X52" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y52" t="n">
         <v>17</v>
@@ -10568,13 +10568,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AR52" t="n">
         <v>7.2</v>
       </c>
       <c r="AS52" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT52" t="n">
         <v>4.4</v>
@@ -10583,10 +10583,10 @@
         <v>4.4</v>
       </c>
       <c r="AV52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW52" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX52" t="n">
         <v>5.6</v>
@@ -10595,32 +10595,32 @@
         <v>5.8</v>
       </c>
       <c r="AZ52" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB52" t="n">
         <v>6.2</v>
       </c>
-      <c r="BA52" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>6</v>
-      </c>
       <c r="BC52" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD52" t="n">
         <v>7.2</v>
       </c>
       <c r="BE52" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG52" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
         <v>3.45</v>
       </c>
       <c r="I53" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>3.1</v>
@@ -10681,7 +10681,7 @@
         <v>1.55</v>
       </c>
       <c r="P53" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="Q53" t="n">
         <v>2.6</v>
@@ -10714,19 +10714,19 @@
         <v>23</v>
       </c>
       <c r="AA53" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB53" t="n">
         <v>7.6</v>
       </c>
       <c r="AC53" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD53" t="n">
         <v>15.5</v>
       </c>
       <c r="AE53" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF53" t="n">
         <v>15</v>
@@ -10753,13 +10753,13 @@
         <v>580</v>
       </c>
       <c r="AN53" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO53" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.96</v>
+        <v>8</v>
       </c>
       <c r="AQ53" t="n">
         <v>8.6</v>
@@ -10768,7 +10768,7 @@
         <v>19.5</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AT53" t="n">
         <v>6.8</v>
@@ -10780,7 +10780,7 @@
         <v>13.5</v>
       </c>
       <c r="AW53" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX53" t="n">
         <v>13</v>
@@ -10792,29 +10792,29 @@
         <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB53" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="BC53" t="n">
-        <v>3.95</v>
+        <v>8.4</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BG53" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10854,13 +10854,13 @@
         <v>3.5</v>
       </c>
       <c r="I54" t="n">
-        <v>990</v>
+        <v>100</v>
       </c>
       <c r="J54" t="n">
         <v>3.6</v>
       </c>
       <c r="K54" t="n">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -10935,7 +10935,7 @@
         <v>700</v>
       </c>
       <c r="AJ54" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK54" t="n">
         <v>500</v>
@@ -10953,25 +10953,25 @@
         <v>700</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS54" t="n">
         <v>1.23</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AW54" t="n">
         <v>1.23</v>
@@ -10983,7 +10983,7 @@
         <v>1.19</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BA54" t="n">
         <v>1.23</v>
@@ -10998,17 +10998,17 @@
         <v>1.22</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG54" t="n">
         <v>1.55</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G55" t="n">
         <v>2.46</v>
@@ -11048,7 +11048,7 @@
         <v>3.75</v>
       </c>
       <c r="I55" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
@@ -11111,7 +11111,7 @@
         <v>7.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AE55" t="n">
         <v>240</v>
@@ -11177,7 +11177,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ55" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA55" t="n">
         <v>11</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11239,16 +11239,16 @@
         <v>1.49</v>
       </c>
       <c r="H56" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J56" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K56" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -11257,13 +11257,13 @@
         <v>1.06</v>
       </c>
       <c r="N56" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
         <v>1.27</v>
       </c>
       <c r="P56" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q56" t="n">
         <v>1.8</v>
@@ -11281,7 +11281,7 @@
         <v>1.81</v>
       </c>
       <c r="V56" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W56" t="n">
         <v>3</v>
@@ -11311,10 +11311,10 @@
         <v>180</v>
       </c>
       <c r="AF56" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH56" t="n">
         <v>32</v>
@@ -11326,10 +11326,10 @@
         <v>15</v>
       </c>
       <c r="AK56" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM56" t="n">
         <v>190</v>
@@ -11344,13 +11344,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.38</v>
+        <v>4.9</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.44</v>
+        <v>5.1</v>
       </c>
       <c r="AT56" t="n">
         <v>7.2</v>
@@ -11359,10 +11359,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="AW56" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="AX56" t="n">
         <v>7.6</v>
@@ -11371,10 +11371,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ56" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA56" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="BB56" t="n">
         <v>10.5</v>
@@ -11383,20 +11383,20 @@
         <v>14</v>
       </c>
       <c r="BD56" t="n">
-        <v>2.68</v>
+        <v>4.7</v>
       </c>
       <c r="BE56" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="BF56" t="n">
         <v>6.2</v>
       </c>
       <c r="BG56" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11624,10 +11624,10 @@
         <v>1.04</v>
       </c>
       <c r="G58" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H58" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I58" t="n">
         <v>990</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="G59" t="n">
         <v>990</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G60" t="n">
         <v>1.98</v>
@@ -12024,37 +12024,37 @@
         <v>3.15</v>
       </c>
       <c r="K60" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M60" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N60" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O60" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="P60" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="R60" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S60" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T60" t="n">
         <v>2.38</v>
       </c>
       <c r="U60" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V60" t="n">
         <v>1.22</v>
@@ -12063,7 +12063,7 @@
         <v>2.02</v>
       </c>
       <c r="X60" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y60" t="n">
         <v>12.5</v>
@@ -12075,10 +12075,10 @@
         <v>190</v>
       </c>
       <c r="AB60" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC60" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD60" t="n">
         <v>24</v>
@@ -12096,7 +12096,7 @@
         <v>32</v>
       </c>
       <c r="AI60" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ60" t="n">
         <v>25</v>
@@ -12108,22 +12108,22 @@
         <v>75</v>
       </c>
       <c r="AM60" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN60" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO60" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP60" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ60" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR60" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AS60" t="n">
         <v>44</v>
@@ -12132,10 +12132,10 @@
         <v>5.5</v>
       </c>
       <c r="AU60" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW60" t="n">
         <v>38</v>
@@ -12144,10 +12144,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY60" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ60" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BA60" t="n">
         <v>44</v>
@@ -12159,7 +12159,7 @@
         <v>19</v>
       </c>
       <c r="BD60" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BE60" t="n">
         <v>55</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12203,10 +12203,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G61" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H61" t="n">
         <v>3.7</v>
@@ -12218,7 +12218,7 @@
         <v>3.25</v>
       </c>
       <c r="K61" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12227,16 +12227,16 @@
         <v>1.09</v>
       </c>
       <c r="N61" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
         <v>1.41</v>
       </c>
       <c r="P61" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R61" t="n">
         <v>1.25</v>
@@ -12248,13 +12248,13 @@
         <v>1.91</v>
       </c>
       <c r="U61" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V61" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W61" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X61" t="n">
         <v>13.5</v>
@@ -12350,7 +12350,7 @@
         <v>4.2</v>
       </c>
       <c r="BC61" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="BD61" t="n">
         <v>4.1</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-12.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.26</v>
+        <v>1.16</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4</v>
+        <v>1.19</v>
       </c>
       <c r="H2" t="n">
-        <v>2.62</v>
+        <v>17.5</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>190</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.01</v>
       </c>
-      <c r="N2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="S2" t="n">
-        <v>15</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.17</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>4.8</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,19 +826,19 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
         <v>1000</v>
@@ -853,13 +853,13 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>1.29</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -877,50 +877,50 @@
         <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1000</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="G3" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="H3" t="n">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N3" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="O3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.64</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.71</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
         <v>110</v>
       </c>
       <c r="AM3" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AN3" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AO3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS3" t="n">
         <v>55</v>
       </c>
-      <c r="AP3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AT3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BB3" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BC3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>200</v>
+      </c>
+      <c r="BF3" t="n">
         <v>50</v>
       </c>
-      <c r="BD3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>170</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>75</v>
-      </c>
       <c r="BG3" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>990</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
         <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>160</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG4" t="n">
         <v>50</v>
       </c>
-      <c r="BB4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>42</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="H5" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X5" t="n">
         <v>18</v>
       </c>
-      <c r="J5" t="n">
+      <c r="Y5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>650</v>
+      </c>
+      <c r="AB5" t="n">
         <v>7.6</v>
       </c>
-      <c r="K5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI5" t="n">
         <v>230</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AJ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM5" t="n">
         <v>300</v>
       </c>
-      <c r="AF5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>210</v>
-      </c>
       <c r="AN5" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>360</v>
+        <v>520</v>
       </c>
       <c r="AP5" t="n">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>25</v>
       </c>
       <c r="AR5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU5" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>12</v>
       </c>
-      <c r="BD5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1533,139 +1533,139 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.14</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.08</v>
       </c>
       <c r="U6" t="n">
         <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AA6" t="n">
-        <v>310</v>
+        <v>700</v>
       </c>
       <c r="AB6" t="n">
         <v>7.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
         <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AI6" t="n">
         <v>230</v>
       </c>
       <c r="AJ6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
@@ -1674,29 +1674,29 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE6" t="n">
         <v>130</v>
       </c>
       <c r="BF6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I7" t="n">
         <v>2.52</v>
       </c>
       <c r="J7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="T7" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
         <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AB7" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="BA7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
         <v>1.38</v>
@@ -1930,85 +1930,85 @@
         <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J8" t="n">
         <v>5.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
         <v>3.6</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="n">
         <v>40</v>
       </c>
       <c r="Z8" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA8" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE8" t="n">
         <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG8" t="n">
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
         <v>11</v>
@@ -2017,55 +2017,55 @@
         <v>14</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AP8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR8" t="n">
         <v>65</v>
       </c>
       <c r="AS8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV8" t="n">
         <v>30</v>
       </c>
       <c r="AW8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8" t="n">
         <v>12.5</v>
@@ -2074,17 +2074,17 @@
         <v>29</v>
       </c>
       <c r="BE8" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
         <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>120</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO9" t="n">
         <v>60</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>40</v>
-      </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AU9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>6</v>
       </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BA9" t="n">
-        <v>27</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>100</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2309,118 +2309,118 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.02</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.08</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
         <v>85</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>27</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>25</v>
@@ -2429,50 +2429,50 @@
         <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG10" t="n">
         <v>38</v>
       </c>
-      <c r="BB10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>34</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2503,139 +2503,139 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
         <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
       </c>
       <c r="Y11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
         <v>13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>14</v>
       </c>
       <c r="AG11" t="n">
         <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
         <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AX11" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2647,26 +2647,26 @@
         <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BC11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BE11" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="BF11" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2700,58 +2700,58 @@
         <v>2.78</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
         <v>1.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
@@ -2784,7 +2784,7 @@
         <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ12" t="n">
         <v>44</v>
@@ -2796,10 +2796,10 @@
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
@@ -2808,10 +2808,10 @@
         <v>15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS12" t="n">
         <v>32</v>
@@ -2829,7 +2829,7 @@
         <v>23</v>
       </c>
       <c r="AX12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
         <v>11.5</v>
@@ -2841,26 +2841,26 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BG12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>2.04</v>
@@ -2906,7 +2906,7 @@
         <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.36</v>
@@ -2924,7 +2924,7 @@
         <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
@@ -2933,13 +2933,13 @@
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
         <v>1.96</v>
@@ -2951,7 +2951,7 @@
         <v>16.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
         <v>85</v>
@@ -3044,7 +3044,7 @@
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF13" t="n">
         <v>11.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H14" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>3.25</v>
@@ -3109,40 +3109,40 @@
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
         <v>2.44</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
         <v>24</v>
@@ -3163,13 +3163,13 @@
         <v>70</v>
       </c>
       <c r="AF14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>150</v>
@@ -3187,13 +3187,13 @@
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AO14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.6</v>
@@ -3202,7 +3202,7 @@
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -3211,7 +3211,7 @@
         <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>19.5</v>
@@ -3220,7 +3220,7 @@
         <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>18</v>
@@ -3229,26 +3229,26 @@
         <v>28</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BE14" t="n">
         <v>34</v>
       </c>
       <c r="BF14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG14" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BG14" t="n">
-        <v>10</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
         <v>3.9</v>
@@ -3306,25 +3306,25 @@
         <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
         <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
         <v>1.7</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
         <v>1.4</v>
@@ -3387,16 +3387,16 @@
         <v>32</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
         <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT15" t="n">
         <v>9.6</v>
@@ -3408,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX15" t="n">
         <v>12</v>
@@ -3429,7 +3429,7 @@
         <v>18.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE15" t="n">
         <v>27</v>
@@ -3438,11 +3438,11 @@
         <v>13.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
         <v>1.47</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
         <v>2.42</v>
@@ -3518,7 +3518,7 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V16" t="n">
         <v>1.37</v>
@@ -3551,7 +3551,7 @@
         <v>130</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -3581,7 +3581,7 @@
         <v>75</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
@@ -3685,55 +3685,55 @@
         <v>3.45</v>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
         <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17" t="n">
         <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA17" t="n">
         <v>150</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC17" t="n">
         <v>7.8</v>
@@ -3745,16 +3745,16 @@
         <v>90</v>
       </c>
       <c r="AF17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG17" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ17" t="n">
         <v>25</v>
@@ -3763,10 +3763,10 @@
         <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>22</v>
@@ -3775,19 +3775,19 @@
         <v>140</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS17" t="n">
         <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU17" t="n">
         <v>7.2</v>
@@ -3796,7 +3796,7 @@
         <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AX17" t="n">
         <v>9</v>
@@ -3814,7 +3814,7 @@
         <v>21</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>46</v>
@@ -3823,14 +3823,14 @@
         <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG17" t="n">
         <v>70</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G18" t="n">
         <v>2.42</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.46</v>
-      </c>
       <c r="H18" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.45</v>
@@ -3888,13 +3888,13 @@
         <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
         <v>1.32</v>
@@ -3903,16 +3903,16 @@
         <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -3924,13 +3924,13 @@
         <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB18" t="n">
         <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
         <v>14.5</v>
@@ -3951,22 +3951,22 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
         <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -3981,7 +3981,7 @@
         <v>38</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3993,7 +3993,7 @@
         <v>36</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
         <v>10.5</v>
@@ -4002,16 +4002,16 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC18" t="n">
         <v>23</v>
       </c>
       <c r="BD18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE18" t="n">
         <v>29</v>
@@ -4020,11 +4020,11 @@
         <v>20</v>
       </c>
       <c r="BG18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4064,16 +4064,16 @@
         <v>6.4</v>
       </c>
       <c r="I19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
@@ -4085,16 +4085,16 @@
         <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
         <v>1.63</v>
       </c>
       <c r="S19" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T19" t="n">
         <v>1.67</v>
@@ -4103,13 +4103,13 @@
         <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
         <v>2.68</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="Y19" t="n">
         <v>950</v>
@@ -4121,7 +4121,7 @@
         <v>700</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
         <v>17</v>
@@ -4139,7 +4139,7 @@
         <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AI19" t="n">
         <v>700</v>
@@ -4151,40 +4151,40 @@
         <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AM19" t="n">
         <v>700</v>
       </c>
       <c r="AN19" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO19" t="n">
         <v>700</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>28</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV19" t="n">
         <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19" t="n">
         <v>9</v>
@@ -4193,7 +4193,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
         <v>8</v>
@@ -4205,20 +4205,20 @@
         <v>8</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
         <v>5.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G20" t="n">
         <v>1.72</v>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
         <v>4.1</v>
@@ -4267,34 +4267,34 @@
         <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V20" t="n">
         <v>1.21</v>
@@ -4303,19 +4303,19 @@
         <v>2.38</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC20" t="n">
         <v>9.4</v>
@@ -4324,7 +4324,7 @@
         <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
         <v>10.5</v>
@@ -4333,13 +4333,13 @@
         <v>9.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK20" t="n">
         <v>16.5</v>
@@ -4351,68 +4351,68 @@
         <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>110</v>
       </c>
       <c r="AP20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU20" t="n">
         <v>8.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BB20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G21" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
         <v>3.2</v>
@@ -4476,34 +4476,34 @@
         <v>1.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R21" t="n">
         <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T21" t="n">
         <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X21" t="n">
         <v>9</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
         <v>90</v>
@@ -4533,7 +4533,7 @@
         <v>85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK21" t="n">
         <v>30</v>
@@ -4545,25 +4545,25 @@
         <v>170</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO21" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS21" t="n">
         <v>70</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
@@ -4593,20 +4593,20 @@
         <v>27</v>
       </c>
       <c r="BD21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BE21" t="n">
         <v>80</v>
       </c>
       <c r="BF21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BG21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4637,85 +4637,85 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="X22" t="n">
         <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA22" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4724,13 +4724,13 @@
         <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>38</v>
@@ -4739,16 +4739,16 @@
         <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AP22" t="n">
         <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>23</v>
@@ -4757,34 +4757,34 @@
         <v>50</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD22" t="n">
         <v>32</v>
@@ -4793,14 +4793,14 @@
         <v>75</v>
       </c>
       <c r="BF22" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BG22" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G23" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="H23" t="n">
         <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
         <v>3.25</v>
       </c>
       <c r="K23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.56</v>
@@ -4855,13 +4855,13 @@
         <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
         <v>1.51</v>
       </c>
       <c r="P23" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q23" t="n">
         <v>2.6</v>
@@ -4873,19 +4873,19 @@
         <v>5.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y23" t="n">
         <v>15.5</v>
@@ -4897,10 +4897,10 @@
         <v>900</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD23" t="n">
         <v>24</v>
@@ -4921,10 +4921,10 @@
         <v>700</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AL23" t="n">
         <v>130</v>
@@ -4948,25 +4948,25 @@
         <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
         <v>21</v>
@@ -4975,10 +4975,10 @@
         <v>11</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BD23" t="n">
         <v>25</v>
@@ -4987,14 +4987,14 @@
         <v>11.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G24" t="n">
         <v>1.47</v>
@@ -5040,10 +5040,10 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
@@ -5061,16 +5061,16 @@
         <v>1.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
         <v>2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>1.13</v>
@@ -5079,10 +5079,10 @@
         <v>3.1</v>
       </c>
       <c r="X24" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y24" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
         <v>420</v>
@@ -5094,7 +5094,7 @@
         <v>16</v>
       </c>
       <c r="AC24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AD24" t="n">
         <v>60</v>
@@ -5121,13 +5121,13 @@
         <v>25</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="n">
         <v>790</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AO24" t="n">
         <v>130</v>
@@ -5136,16 +5136,16 @@
         <v>14.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AU24" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
         <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX24" t="n">
         <v>5.9</v>
@@ -5166,10 +5166,10 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
         <v>7.8</v>
@@ -5178,17 +5178,17 @@
         <v>14</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="H25" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L25" t="n">
         <v>1.48</v>
@@ -5243,76 +5243,76 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W25" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="X25" t="n">
         <v>12</v>
       </c>
       <c r="Y25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
       </c>
       <c r="AI25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK25" t="n">
         <v>55</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>48</v>
       </c>
       <c r="AL25" t="n">
         <v>65</v>
@@ -5321,34 +5321,34 @@
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO25" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV25" t="n">
         <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AX25" t="n">
         <v>19</v>
@@ -5357,32 +5357,32 @@
         <v>12</v>
       </c>
       <c r="AZ25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD25" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>8</v>
-      </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G26" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="H26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I26" t="n">
         <v>4.4</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.5</v>
       </c>
       <c r="J26" t="n">
         <v>3.9</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
         <v>1.39</v>
@@ -5455,28 +5455,28 @@
         <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U26" t="n">
         <v>2.26</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB26" t="n">
         <v>9.6</v>
@@ -5497,10 +5497,10 @@
         <v>9.6</v>
       </c>
       <c r="AH26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
@@ -5518,7 +5518,7 @@
         <v>12</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
@@ -5530,7 +5530,7 @@
         <v>30</v>
       </c>
       <c r="AS26" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AT26" t="n">
         <v>9.4</v>
@@ -5542,7 +5542,7 @@
         <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX26" t="n">
         <v>11</v>
@@ -5560,7 +5560,7 @@
         <v>20</v>
       </c>
       <c r="BC26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>29</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
         <v>2.14</v>
@@ -5649,7 +5649,7 @@
         <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U27" t="n">
         <v>2.24</v>
@@ -5676,7 +5676,7 @@
         <v>10.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
         <v>15.5</v>
@@ -5697,7 +5697,7 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
         <v>21</v>
@@ -5712,7 +5712,7 @@
         <v>14.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP27" t="n">
         <v>14</v>
@@ -5721,7 +5721,7 @@
         <v>13.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
         <v>50</v>
@@ -5742,7 +5742,7 @@
         <v>12</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
         <v>16</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="G28" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H28" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>3.15</v>
       </c>
       <c r="K28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
@@ -5840,7 +5840,7 @@
         <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T28" t="n">
         <v>1.79</v>
@@ -5849,10 +5849,10 @@
         <v>2.12</v>
       </c>
       <c r="V28" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="X28" t="n">
         <v>12</v>
@@ -5861,28 +5861,28 @@
         <v>12.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
         <v>17</v>
@@ -5891,19 +5891,19 @@
         <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AM28" t="n">
         <v>110</v>
       </c>
       <c r="AN28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO28" t="n">
         <v>48</v>
@@ -5915,56 +5915,56 @@
         <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW28" t="n">
         <v>34</v>
       </c>
-      <c r="AT28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>27</v>
-      </c>
       <c r="AX28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA28" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BB28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD28" t="n">
         <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BF28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG28" t="n">
         <v>32</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="I29" t="n">
         <v>1.4</v>
@@ -6010,7 +6010,7 @@
         <v>4.8</v>
       </c>
       <c r="K29" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.42</v>
@@ -6022,19 +6022,19 @@
         <v>3.65</v>
       </c>
       <c r="O29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T29" t="n">
         <v>2.36</v>
@@ -6049,13 +6049,13 @@
         <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="AA29" t="n">
         <v>21</v>
@@ -6100,7 +6100,7 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AP29" t="n">
         <v>12</v>
@@ -6121,44 +6121,44 @@
         <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW29" t="n">
         <v>9</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
         <v>16</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BG29" t="n">
         <v>6.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6195,13 +6195,13 @@
         <v>2.9</v>
       </c>
       <c r="H30" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I30" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
         <v>4.1</v>
@@ -6216,7 +6216,7 @@
         <v>5.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P30" t="n">
         <v>2.66</v>
@@ -6234,7 +6234,7 @@
         <v>1.51</v>
       </c>
       <c r="U30" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V30" t="n">
         <v>1.58</v>
@@ -6261,7 +6261,7 @@
         <v>9.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE30" t="n">
         <v>500</v>
@@ -6297,7 +6297,7 @@
         <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>13</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6383,28 +6383,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="G31" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="H31" t="n">
         <v>23</v>
       </c>
       <c r="I31" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="J31" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N31" t="n">
         <v>5.3</v>
@@ -6413,37 +6413,37 @@
         <v>1.2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R31" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S31" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="X31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y31" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z31" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -6452,7 +6452,7 @@
         <v>10</v>
       </c>
       <c r="AC31" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AD31" t="n">
         <v>950</v>
@@ -6461,10 +6461,10 @@
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AH31" t="n">
         <v>950</v>
@@ -6473,80 +6473,80 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AM31" t="n">
-        <v>570</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>29</v>
+        <v>3.65</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT31" t="n">
         <v>7.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB31" t="n">
         <v>5.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>6.2</v>
       </c>
       <c r="BC31" t="n">
         <v>14.5</v>
       </c>
       <c r="BD31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF31" t="n">
         <v>3.1</v>
       </c>
-      <c r="BE31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BG31" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6589,10 +6589,10 @@
         <v>3.5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.38</v>
@@ -6601,16 +6601,16 @@
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O32" t="n">
         <v>1.27</v>
       </c>
       <c r="P32" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R32" t="n">
         <v>1.44</v>
@@ -6622,22 +6622,22 @@
         <v>1.71</v>
       </c>
       <c r="U32" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
         <v>1.75</v>
       </c>
       <c r="X32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y32" t="n">
         <v>15</v>
       </c>
       <c r="Z32" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA32" t="n">
         <v>280</v>
@@ -6655,7 +6655,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AG32" t="n">
         <v>11.5</v>
@@ -6679,7 +6679,7 @@
         <v>200</v>
       </c>
       <c r="AN32" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AO32" t="n">
         <v>46</v>
@@ -6724,13 +6724,13 @@
         <v>22</v>
       </c>
       <c r="BC32" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BE32" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BF32" t="n">
         <v>14</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G33" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H33" t="n">
         <v>3</v>
@@ -6783,13 +6783,13 @@
         <v>3.1</v>
       </c>
       <c r="J33" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L33" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
@@ -6801,16 +6801,16 @@
         <v>1.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S33" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T33" t="n">
         <v>1.48</v>
@@ -6822,10 +6822,10 @@
         <v>1.47</v>
       </c>
       <c r="W33" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y33" t="n">
         <v>21</v>
@@ -6834,28 +6834,28 @@
         <v>27</v>
       </c>
       <c r="AA33" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AB33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
         <v>28</v>
       </c>
       <c r="AF33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG33" t="n">
         <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI33" t="n">
         <v>30</v>
@@ -6867,43 +6867,43 @@
         <v>22</v>
       </c>
       <c r="AL33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN33" t="n">
         <v>11.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP33" t="n">
         <v>24</v>
       </c>
       <c r="AQ33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR33" t="n">
         <v>23</v>
       </c>
       <c r="AS33" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT33" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV33" t="n">
         <v>12.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX33" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY33" t="n">
         <v>10.5</v>
@@ -6924,7 +6924,7 @@
         <v>23</v>
       </c>
       <c r="BE33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF33" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6977,10 +6977,10 @@
         <v>6</v>
       </c>
       <c r="J34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K34" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.33</v>
@@ -7007,7 +7007,7 @@
         <v>2.74</v>
       </c>
       <c r="T34" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U34" t="n">
         <v>2.26</v>
@@ -7016,13 +7016,13 @@
         <v>1.2</v>
       </c>
       <c r="W34" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X34" t="n">
         <v>21</v>
       </c>
       <c r="Y34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z34" t="n">
         <v>48</v>
@@ -7034,10 +7034,10 @@
         <v>10.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE34" t="n">
         <v>70</v>
@@ -7070,7 +7070,7 @@
         <v>7.4</v>
       </c>
       <c r="AO34" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP34" t="n">
         <v>20</v>
@@ -7082,10 +7082,10 @@
         <v>44</v>
       </c>
       <c r="AS34" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AT34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU34" t="n">
         <v>9.6</v>
@@ -7118,17 +7118,17 @@
         <v>26</v>
       </c>
       <c r="BE34" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF34" t="n">
         <v>7</v>
       </c>
       <c r="BG34" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7159,16 +7159,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G35" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H35" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I35" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>3.5</v>
@@ -7207,10 +7207,10 @@
         <v>2.14</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W35" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X35" t="n">
         <v>13</v>
@@ -7222,22 +7222,22 @@
         <v>25</v>
       </c>
       <c r="AA35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB35" t="n">
         <v>9.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE35" t="n">
         <v>40</v>
       </c>
       <c r="AF35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG35" t="n">
         <v>11.5</v>
@@ -7246,13 +7246,13 @@
         <v>18</v>
       </c>
       <c r="AI35" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AJ35" t="n">
         <v>32</v>
       </c>
       <c r="AK35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL35" t="n">
         <v>40</v>
@@ -7276,10 +7276,10 @@
         <v>20</v>
       </c>
       <c r="AS35" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AT35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU35" t="n">
         <v>7.2</v>
@@ -7300,29 +7300,29 @@
         <v>15</v>
       </c>
       <c r="BA35" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BB35" t="n">
         <v>27</v>
       </c>
       <c r="BC35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD35" t="n">
         <v>32</v>
       </c>
       <c r="BE35" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF35" t="n">
         <v>19.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
         <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R36" t="n">
         <v>1.6</v>
@@ -7404,13 +7404,13 @@
         <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z36" t="n">
         <v>28</v>
@@ -7419,7 +7419,7 @@
         <v>500</v>
       </c>
       <c r="AB36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC36" t="n">
         <v>9.199999999999999</v>
@@ -7470,7 +7470,7 @@
         <v>20</v>
       </c>
       <c r="AS36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT36" t="n">
         <v>12</v>
@@ -7482,7 +7482,7 @@
         <v>13</v>
       </c>
       <c r="AW36" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX36" t="n">
         <v>14</v>
@@ -7509,14 +7509,14 @@
         <v>17.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG36" t="n">
         <v>21</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
         <v>5.2</v>
       </c>
       <c r="K37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L37" t="n">
         <v>1.24</v>
@@ -7571,7 +7571,7 @@
         <v>1.02</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O37" t="n">
         <v>1.13</v>
@@ -7583,7 +7583,7 @@
         <v>1.41</v>
       </c>
       <c r="R37" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S37" t="n">
         <v>2.04</v>
@@ -7598,7 +7598,7 @@
         <v>1.16</v>
       </c>
       <c r="W37" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="X37" t="n">
         <v>36</v>
@@ -7616,7 +7616,7 @@
         <v>15.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD37" t="n">
         <v>26</v>
@@ -7628,7 +7628,7 @@
         <v>13</v>
       </c>
       <c r="AG37" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH37" t="n">
         <v>18</v>
@@ -7655,16 +7655,16 @@
         <v>55</v>
       </c>
       <c r="AP37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ37" t="n">
         <v>34</v>
       </c>
       <c r="AR37" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AS37" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AT37" t="n">
         <v>14</v>
@@ -7688,7 +7688,7 @@
         <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BB37" t="n">
         <v>13.5</v>
@@ -7700,17 +7700,17 @@
         <v>21</v>
       </c>
       <c r="BE37" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G38" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L38" t="n">
         <v>1.3</v>
@@ -7768,10 +7768,10 @@
         <v>5.8</v>
       </c>
       <c r="O38" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P38" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q38" t="n">
         <v>1.61</v>
@@ -7783,16 +7783,16 @@
         <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U38" t="n">
         <v>2.58</v>
       </c>
       <c r="V38" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W38" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X38" t="n">
         <v>23</v>
@@ -7804,16 +7804,16 @@
         <v>34</v>
       </c>
       <c r="AA38" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB38" t="n">
         <v>13.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD38" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE38" t="n">
         <v>40</v>
@@ -7828,22 +7828,22 @@
         <v>15.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ38" t="n">
         <v>23</v>
       </c>
       <c r="AK38" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL38" t="n">
         <v>26</v>
       </c>
       <c r="AM38" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN38" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO38" t="n">
         <v>29</v>
@@ -7858,10 +7858,10 @@
         <v>30</v>
       </c>
       <c r="AS38" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AT38" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU38" t="n">
         <v>9</v>
@@ -7882,7 +7882,7 @@
         <v>13.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB38" t="n">
         <v>21</v>
@@ -7891,20 +7891,20 @@
         <v>16</v>
       </c>
       <c r="BD38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE38" t="n">
         <v>28</v>
       </c>
       <c r="BF38" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG38" t="n">
         <v>26</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
         <v>1.38</v>
       </c>
       <c r="P39" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
         <v>2.14</v>
@@ -7977,13 +7977,13 @@
         <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U39" t="n">
         <v>2.08</v>
       </c>
       <c r="V39" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W39" t="n">
         <v>1.5</v>
@@ -7992,7 +7992,7 @@
         <v>13.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z39" t="n">
         <v>19.5</v>
@@ -8004,7 +8004,7 @@
         <v>11.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD39" t="n">
         <v>12.5</v>
@@ -8037,7 +8037,7 @@
         <v>200</v>
       </c>
       <c r="AN39" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AO39" t="n">
         <v>32</v>
@@ -8046,7 +8046,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR39" t="n">
         <v>15</v>
@@ -8055,7 +8055,7 @@
         <v>25</v>
       </c>
       <c r="AT39" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU39" t="n">
         <v>7.2</v>
@@ -8067,7 +8067,7 @@
         <v>19.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY39" t="n">
         <v>11</v>
@@ -8088,17 +8088,17 @@
         <v>28</v>
       </c>
       <c r="BE39" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BF39" t="n">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="BG39" t="n">
         <v>20</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G40" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H40" t="n">
         <v>3.35</v>
@@ -8141,7 +8141,7 @@
         <v>3.45</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K40" t="n">
         <v>3.6</v>
@@ -8171,16 +8171,16 @@
         <v>3.55</v>
       </c>
       <c r="T40" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U40" t="n">
         <v>2.2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W40" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X40" t="n">
         <v>15</v>
@@ -8207,7 +8207,7 @@
         <v>38</v>
       </c>
       <c r="AF40" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG40" t="n">
         <v>11</v>
@@ -8222,7 +8222,7 @@
         <v>30</v>
       </c>
       <c r="AK40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL40" t="n">
         <v>38</v>
@@ -8258,10 +8258,10 @@
         <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY40" t="n">
         <v>10</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.91</v>
       </c>
-      <c r="G41" t="n">
-        <v>1.93</v>
-      </c>
       <c r="H41" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I41" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>3.9</v>
@@ -8356,37 +8356,37 @@
         <v>2.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R41" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S41" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T41" t="n">
         <v>1.72</v>
       </c>
       <c r="U41" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V41" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W41" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X41" t="n">
         <v>18</v>
       </c>
       <c r="Y41" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA41" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AB41" t="n">
         <v>11</v>
@@ -8395,10 +8395,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE41" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF41" t="n">
         <v>13</v>
@@ -8419,10 +8419,10 @@
         <v>18.5</v>
       </c>
       <c r="AL41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM41" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN41" t="n">
         <v>11</v>
@@ -8434,7 +8434,7 @@
         <v>17</v>
       </c>
       <c r="AQ41" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR41" t="n">
         <v>29</v>
@@ -8467,26 +8467,26 @@
         <v>46</v>
       </c>
       <c r="BB41" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC41" t="n">
         <v>16.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE41" t="n">
         <v>60</v>
       </c>
       <c r="BF41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG41" t="n">
         <v>38</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G42" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="H42" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K42" t="n">
         <v>4.2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.4</v>
       </c>
       <c r="L42" t="n">
         <v>1.33</v>
@@ -8553,22 +8553,22 @@
         <v>1.71</v>
       </c>
       <c r="R42" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S42" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T42" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U42" t="n">
         <v>2.3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="X42" t="n">
         <v>21</v>
@@ -8577,10 +8577,10 @@
         <v>22</v>
       </c>
       <c r="Z42" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA42" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB42" t="n">
         <v>11</v>
@@ -8589,25 +8589,25 @@
         <v>9.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF42" t="n">
         <v>12</v>
       </c>
       <c r="AG42" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI42" t="n">
         <v>55</v>
       </c>
       <c r="AJ42" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK42" t="n">
         <v>16.5</v>
@@ -8619,22 +8619,22 @@
         <v>80</v>
       </c>
       <c r="AN42" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO42" t="n">
         <v>55</v>
       </c>
       <c r="AP42" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>20</v>
       </c>
       <c r="AR42" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS42" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AT42" t="n">
         <v>10</v>
@@ -8643,10 +8643,10 @@
         <v>9</v>
       </c>
       <c r="AV42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX42" t="n">
         <v>11</v>
@@ -8655,10 +8655,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ42" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB42" t="n">
         <v>17</v>
@@ -8673,14 +8673,14 @@
         <v>55</v>
       </c>
       <c r="BF42" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG42" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G43" t="n">
         <v>2.56</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2.58</v>
       </c>
       <c r="H43" t="n">
         <v>2.78</v>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L43" t="n">
         <v>1.27</v>
@@ -8741,7 +8741,7 @@
         <v>1.17</v>
       </c>
       <c r="P43" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q43" t="n">
         <v>1.52</v>
@@ -8750,16 +8750,16 @@
         <v>1.71</v>
       </c>
       <c r="S43" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T43" t="n">
         <v>1.44</v>
       </c>
       <c r="U43" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="V43" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W43" t="n">
         <v>1.64</v>
@@ -8768,37 +8768,37 @@
         <v>26</v>
       </c>
       <c r="Y43" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB43" t="n">
         <v>21</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>19</v>
       </c>
       <c r="AC43" t="n">
         <v>9.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE43" t="n">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="AF43" t="n">
         <v>22</v>
       </c>
       <c r="AG43" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH43" t="n">
         <v>13.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="AJ43" t="n">
         <v>38</v>
@@ -8807,7 +8807,7 @@
         <v>23</v>
       </c>
       <c r="AL43" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AM43" t="n">
         <v>50</v>
@@ -8816,25 +8816,25 @@
         <v>13.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AP43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ43" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="AR43" t="n">
         <v>20</v>
       </c>
       <c r="AS43" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AT43" t="n">
         <v>16.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV43" t="n">
         <v>11.5</v>
@@ -8843,22 +8843,22 @@
         <v>20</v>
       </c>
       <c r="AX43" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="AY43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ43" t="n">
         <v>11.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BB43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC43" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD43" t="n">
         <v>12.5</v>
@@ -8867,14 +8867,14 @@
         <v>22</v>
       </c>
       <c r="BF43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8908,13 +8908,13 @@
         <v>2.04</v>
       </c>
       <c r="G44" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H44" t="n">
         <v>4.5</v>
       </c>
       <c r="I44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J44" t="n">
         <v>3.35</v>
@@ -8929,10 +8929,10 @@
         <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P44" t="n">
         <v>1.72</v>
@@ -8941,22 +8941,22 @@
         <v>2.34</v>
       </c>
       <c r="R44" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S44" t="n">
         <v>4.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X44" t="n">
         <v>10.5</v>
@@ -9004,7 +9004,7 @@
         <v>48</v>
       </c>
       <c r="AM44" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AN44" t="n">
         <v>21</v>
@@ -9028,16 +9028,16 @@
         <v>7</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV44" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW44" t="n">
         <v>60</v>
       </c>
       <c r="AX44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY44" t="n">
         <v>10</v>
@@ -9055,7 +9055,7 @@
         <v>22</v>
       </c>
       <c r="BD44" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE44" t="n">
         <v>30</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>4.6</v>
       </c>
       <c r="J45" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K45" t="n">
         <v>3.2</v>
@@ -9126,7 +9126,7 @@
         <v>2.58</v>
       </c>
       <c r="O45" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="P45" t="n">
         <v>1.49</v>
@@ -9144,7 +9144,7 @@
         <v>2.1</v>
       </c>
       <c r="U45" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V45" t="n">
         <v>1.28</v>
@@ -9168,10 +9168,10 @@
         <v>7.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE45" t="n">
         <v>75</v>
@@ -9189,13 +9189,13 @@
         <v>540</v>
       </c>
       <c r="AJ45" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK45" t="n">
         <v>65</v>
       </c>
       <c r="AL45" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM45" t="n">
         <v>500</v>
@@ -9210,19 +9210,19 @@
         <v>6.6</v>
       </c>
       <c r="AQ45" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR45" t="n">
         <v>23</v>
       </c>
       <c r="AS45" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU45" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV45" t="n">
         <v>15</v>
@@ -9231,7 +9231,7 @@
         <v>48</v>
       </c>
       <c r="AX45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY45" t="n">
         <v>10</v>
@@ -9240,29 +9240,29 @@
         <v>20</v>
       </c>
       <c r="BA45" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB45" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BC45" t="n">
         <v>21</v>
       </c>
       <c r="BD45" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE45" t="n">
         <v>9</v>
       </c>
-      <c r="BE45" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF45" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9323,10 +9323,10 @@
         <v>1.27</v>
       </c>
       <c r="P46" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R46" t="n">
         <v>1.47</v>
@@ -9335,7 +9335,7 @@
         <v>3.05</v>
       </c>
       <c r="T46" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U46" t="n">
         <v>2.42</v>
@@ -9365,7 +9365,7 @@
         <v>7.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE46" t="n">
         <v>30</v>
@@ -9395,7 +9395,7 @@
         <v>65</v>
       </c>
       <c r="AN46" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO46" t="n">
         <v>26</v>
@@ -9431,7 +9431,7 @@
         <v>11</v>
       </c>
       <c r="AZ46" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA46" t="n">
         <v>34</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="F47" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G47" t="n">
         <v>2.7</v>
       </c>
-      <c r="G47" t="n">
-        <v>2.72</v>
-      </c>
       <c r="H47" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I47" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>3.7</v>
@@ -9511,31 +9511,31 @@
         <v>1.06</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O47" t="n">
         <v>1.28</v>
       </c>
       <c r="P47" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S47" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T47" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U47" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V47" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W47" t="n">
         <v>1.58</v>
@@ -9547,7 +9547,7 @@
         <v>13</v>
       </c>
       <c r="Z47" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="n">
         <v>40</v>
@@ -9592,7 +9592,7 @@
         <v>21</v>
       </c>
       <c r="AO47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP47" t="n">
         <v>15.5</v>
@@ -9607,13 +9607,13 @@
         <v>36</v>
       </c>
       <c r="AT47" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU47" t="n">
         <v>7.8</v>
       </c>
       <c r="AV47" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW47" t="n">
         <v>26</v>
@@ -9625,16 +9625,16 @@
         <v>11</v>
       </c>
       <c r="AZ47" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB47" t="n">
         <v>36</v>
       </c>
       <c r="BC47" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD47" t="n">
         <v>32</v>
@@ -9643,14 +9643,14 @@
         <v>60</v>
       </c>
       <c r="BF47" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G48" t="n">
         <v>2.22</v>
@@ -9732,7 +9732,7 @@
         <v>1.34</v>
       </c>
       <c r="W48" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X48" t="n">
         <v>20</v>
@@ -9747,25 +9747,25 @@
         <v>900</v>
       </c>
       <c r="AB48" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AC48" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD48" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="AE48" t="n">
         <v>500</v>
       </c>
       <c r="AF48" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG48" t="n">
         <v>12</v>
       </c>
       <c r="AH48" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI48" t="n">
         <v>500</v>
@@ -9795,7 +9795,7 @@
         <v>10.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS48" t="n">
         <v>8.4</v>
@@ -9807,7 +9807,7 @@
         <v>6.8</v>
       </c>
       <c r="AV48" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW48" t="n">
         <v>8</v>
@@ -9816,7 +9816,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY48" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ48" t="n">
         <v>11.5</v>
@@ -9825,7 +9825,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB48" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC48" t="n">
         <v>11.5</v>
@@ -9834,17 +9834,17 @@
         <v>20</v>
       </c>
       <c r="BE48" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF48" t="n">
         <v>6.6</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
         <v>5.8</v>
       </c>
       <c r="T49" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U49" t="n">
         <v>1.8</v>
@@ -9926,7 +9926,7 @@
         <v>1.4</v>
       </c>
       <c r="W49" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X49" t="n">
         <v>8.6</v>
@@ -9953,7 +9953,7 @@
         <v>160</v>
       </c>
       <c r="AF49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG49" t="n">
         <v>12.5</v>
@@ -9962,13 +9962,13 @@
         <v>25</v>
       </c>
       <c r="AI49" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AJ49" t="n">
         <v>42</v>
       </c>
       <c r="AK49" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AL49" t="n">
         <v>70</v>
@@ -9980,7 +9980,7 @@
         <v>42</v>
       </c>
       <c r="AO49" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP49" t="n">
         <v>7.8</v>
@@ -9995,7 +9995,7 @@
         <v>42</v>
       </c>
       <c r="AT49" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU49" t="n">
         <v>6.4</v>
@@ -10016,10 +10016,10 @@
         <v>20</v>
       </c>
       <c r="BA49" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BB49" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC49" t="n">
         <v>29</v>
@@ -10031,14 +10031,14 @@
         <v>70</v>
       </c>
       <c r="BF49" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BG49" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
         <v>1.54</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I50" t="n">
         <v>7.2</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
         <v>24</v>
       </c>
       <c r="AE51" t="n">
-        <v>700</v>
+        <v>470</v>
       </c>
       <c r="AF51" t="n">
         <v>10.5</v>
@@ -10359,7 +10359,7 @@
         <v>22</v>
       </c>
       <c r="AL51" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AM51" t="n">
         <v>580</v>
@@ -10377,7 +10377,7 @@
         <v>13.5</v>
       </c>
       <c r="AR51" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AS51" t="n">
         <v>8.800000000000001</v>
@@ -10392,7 +10392,7 @@
         <v>18.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AX51" t="n">
         <v>8.4</v>
@@ -10404,7 +10404,7 @@
         <v>19</v>
       </c>
       <c r="BA51" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB51" t="n">
         <v>16</v>
@@ -10413,7 +10413,7 @@
         <v>17.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BE51" t="n">
         <v>11</v>
@@ -10422,11 +10422,11 @@
         <v>6</v>
       </c>
       <c r="BG51" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G52" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H52" t="n">
         <v>3.9</v>
@@ -10472,67 +10472,67 @@
         <v>3.05</v>
       </c>
       <c r="K52" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L52" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M52" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N52" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O52" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P52" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S52" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="T52" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="V52" t="n">
         <v>1.33</v>
       </c>
       <c r="W52" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X52" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y52" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z52" t="n">
         <v>26</v>
       </c>
       <c r="AA52" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB52" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC52" t="n">
         <v>7</v>
       </c>
       <c r="AD52" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF52" t="n">
         <v>14</v>
@@ -10541,10 +10541,10 @@
         <v>11.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI52" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AJ52" t="n">
         <v>32</v>
@@ -10553,19 +10553,19 @@
         <v>30</v>
       </c>
       <c r="AL52" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM52" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN52" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AO52" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AP52" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ52" t="n">
         <v>10.5</v>
@@ -10577,13 +10577,13 @@
         <v>70</v>
       </c>
       <c r="AT52" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU52" t="n">
         <v>6.4</v>
       </c>
       <c r="AV52" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW52" t="n">
         <v>34</v>
@@ -10595,13 +10595,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA52" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BB52" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC52" t="n">
         <v>27</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10675,19 +10675,19 @@
         <v>1.05</v>
       </c>
       <c r="N53" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O53" t="n">
         <v>1.26</v>
       </c>
       <c r="P53" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q53" t="n">
         <v>1.8</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -10696,7 +10696,7 @@
         <v>1.98</v>
       </c>
       <c r="U53" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V53" t="n">
         <v>1.13</v>
@@ -10762,13 +10762,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="AR53" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS53" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT53" t="n">
         <v>7.2</v>
@@ -10777,10 +10777,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV53" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW53" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX53" t="n">
         <v>7.6</v>
@@ -10792,7 +10792,7 @@
         <v>21</v>
       </c>
       <c r="BA53" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB53" t="n">
         <v>10.5</v>
@@ -10804,17 +10804,17 @@
         <v>5.9</v>
       </c>
       <c r="BE53" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF53" t="n">
         <v>6</v>
       </c>
       <c r="BG53" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10863,34 +10863,34 @@
         <v>3.5</v>
       </c>
       <c r="L54" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M54" t="n">
         <v>1.08</v>
       </c>
       <c r="N54" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O54" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P54" t="n">
         <v>1.86</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R54" t="n">
         <v>1.32</v>
       </c>
       <c r="S54" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T54" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U54" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V54" t="n">
         <v>1.52</v>
@@ -10899,7 +10899,7 @@
         <v>1.5</v>
       </c>
       <c r="X54" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y54" t="n">
         <v>11.5</v>
@@ -10962,7 +10962,7 @@
         <v>16</v>
       </c>
       <c r="AS54" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT54" t="n">
         <v>9.199999999999999</v>
@@ -10989,7 +10989,7 @@
         <v>7</v>
       </c>
       <c r="BB54" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC54" t="n">
         <v>7.2</v>
@@ -10998,7 +10998,7 @@
         <v>7</v>
       </c>
       <c r="BE54" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF54" t="n">
         <v>23</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11039,58 +11039,58 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G55" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H55" t="n">
         <v>2.36</v>
       </c>
       <c r="I55" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K55" t="n">
         <v>4.4</v>
       </c>
       <c r="L55" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M55" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N55" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O55" t="n">
         <v>1.25</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="R55" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S55" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="T55" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U55" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V55" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W55" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X55" t="n">
         <v>950</v>
@@ -11144,13 +11144,13 @@
         <v>22</v>
       </c>
       <c r="AO55" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AR55" t="n">
         <v>14</v>
@@ -11174,13 +11174,13 @@
         <v>4.2</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB55" t="n">
         <v>4.6</v>
@@ -11192,7 +11192,7 @@
         <v>4.5</v>
       </c>
       <c r="BE55" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF55" t="n">
         <v>4.1</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G56" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="H56" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I56" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K56" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L56" t="n">
         <v>1.22</v>
@@ -11266,7 +11266,7 @@
         <v>3.35</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R56" t="n">
         <v>1.96</v>
@@ -11278,13 +11278,13 @@
         <v>1.56</v>
       </c>
       <c r="U56" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V56" t="n">
         <v>1.2</v>
       </c>
       <c r="W56" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="X56" t="n">
         <v>48</v>
@@ -11308,25 +11308,25 @@
         <v>26</v>
       </c>
       <c r="AE56" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF56" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG56" t="n">
         <v>13</v>
       </c>
       <c r="AH56" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI56" t="n">
         <v>50</v>
       </c>
       <c r="AJ56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL56" t="n">
         <v>26</v>
@@ -11341,16 +11341,16 @@
         <v>40</v>
       </c>
       <c r="AP56" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS56" t="n">
         <v>6</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>6.4</v>
       </c>
       <c r="AT56" t="n">
         <v>15</v>
@@ -11362,41 +11362,41 @@
         <v>20</v>
       </c>
       <c r="AW56" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX56" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY56" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ56" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BB56" t="n">
         <v>14.5</v>
       </c>
       <c r="BC56" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD56" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE56" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BF56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG56" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
         <v>1.96</v>
       </c>
       <c r="G57" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
         <v>5.2</v>
@@ -11439,10 +11439,10 @@
         <v>5.5</v>
       </c>
       <c r="J57" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K57" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L57" t="n">
         <v>1.66</v>
@@ -11478,7 +11478,7 @@
         <v>1.22</v>
       </c>
       <c r="W57" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X57" t="n">
         <v>7.8</v>
@@ -11556,7 +11556,7 @@
         <v>20</v>
       </c>
       <c r="AW57" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX57" t="n">
         <v>9</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11621,16 +11621,16 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G58" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H58" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I58" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>3.25</v>
@@ -11651,10 +11651,10 @@
         <v>1.44</v>
       </c>
       <c r="P58" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R58" t="n">
         <v>1.27</v>
@@ -11663,16 +11663,16 @@
         <v>4.5</v>
       </c>
       <c r="T58" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U58" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V58" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W58" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X58" t="n">
         <v>13</v>
@@ -11690,7 +11690,7 @@
         <v>9.6</v>
       </c>
       <c r="AC58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD58" t="n">
         <v>20</v>
@@ -11738,7 +11738,7 @@
         <v>20</v>
       </c>
       <c r="AS58" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT58" t="n">
         <v>6.8</v>
@@ -11750,7 +11750,7 @@
         <v>14</v>
       </c>
       <c r="AW58" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX58" t="n">
         <v>11</v>
@@ -11771,20 +11771,20 @@
         <v>19.5</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE58" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF58" t="n">
         <v>19.5</v>
       </c>
       <c r="BG58" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11818,16 +11818,16 @@
         <v>1.04</v>
       </c>
       <c r="G59" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H59" t="n">
         <v>1.04</v>
       </c>
       <c r="I59" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K59" t="n">
         <v>950</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
